--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -3045,32 +3045,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129566021</v>
+        <v>129565942</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443030</v>
+        <v>442719</v>
       </c>
       <c r="R24" t="n">
-        <v>6765092</v>
+        <v>6764829</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,50 +3152,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129565782</v>
+        <v>129565898</v>
       </c>
       <c r="B25" t="n">
-        <v>56917</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442771</v>
+        <v>443095</v>
       </c>
       <c r="R25" t="n">
-        <v>6764923</v>
+        <v>6765057</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,7 +3222,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3237,7 +3232,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3264,57 +3259,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129565783</v>
+        <v>129565998</v>
       </c>
       <c r="B26" t="n">
-        <v>56917</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442977</v>
+        <v>443044</v>
       </c>
       <c r="R26" t="n">
-        <v>6765352</v>
+        <v>6765344</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3346,7 +3329,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3356,7 +3339,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,10 +3366,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129565860</v>
+        <v>129566015</v>
       </c>
       <c r="B27" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3394,21 +3377,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3418,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442861</v>
+        <v>442816</v>
       </c>
       <c r="R27" t="n">
-        <v>6764907</v>
+        <v>6764845</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3453,7 +3436,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3463,12 +3446,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt, 100-tal fruktkroppar på minst 300 år gammal gran.</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,10 +3473,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129565942</v>
+        <v>129565818</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92873</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,21 +3484,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3530,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442719</v>
+        <v>443118</v>
       </c>
       <c r="R28" t="n">
-        <v>6764829</v>
+        <v>6765378</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3565,7 +3543,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3575,7 +3553,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3602,7 +3580,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129565898</v>
+        <v>129565923</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3637,10 +3615,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443095</v>
+        <v>442732</v>
       </c>
       <c r="R29" t="n">
-        <v>6765057</v>
+        <v>6765250</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3672,7 +3650,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3682,7 +3660,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3709,45 +3687,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129565998</v>
+        <v>129565783</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>56917</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443044</v>
+        <v>442977</v>
       </c>
       <c r="R30" t="n">
-        <v>6765344</v>
+        <v>6765352</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3779,7 +3769,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3789,7 +3779,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3816,45 +3806,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129566015</v>
+        <v>129565782</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>56917</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442816</v>
+        <v>442771</v>
       </c>
       <c r="R31" t="n">
-        <v>6764845</v>
+        <v>6764923</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,7 +3881,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3896,7 +3891,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3923,10 +3918,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129565818</v>
+        <v>129565860</v>
       </c>
       <c r="B32" t="n">
-        <v>92873</v>
+        <v>82878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,21 +3929,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3958,10 +3953,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443118</v>
+        <v>442861</v>
       </c>
       <c r="R32" t="n">
-        <v>6765378</v>
+        <v>6764907</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3993,7 +3988,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4003,7 +3998,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt, 100-tal fruktkroppar på minst 300 år gammal gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4030,10 +4030,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129565923</v>
+        <v>129565757</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,21 +4041,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442732</v>
+        <v>443135</v>
       </c>
       <c r="R33" t="n">
-        <v>6765250</v>
+        <v>6765214</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129565757</v>
+        <v>129565853</v>
       </c>
       <c r="B34" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,21 +4148,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443135</v>
+        <v>443296</v>
       </c>
       <c r="R34" t="n">
-        <v>6765214</v>
+        <v>6765502</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129565853</v>
+        <v>129565759</v>
       </c>
       <c r="B35" t="n">
-        <v>78801</v>
+        <v>83012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443296</v>
+        <v>442678</v>
       </c>
       <c r="R35" t="n">
-        <v>6765502</v>
+        <v>6764817</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4351,32 +4351,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129565759</v>
+        <v>129566021</v>
       </c>
       <c r="B36" t="n">
-        <v>83012</v>
+        <v>92835</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>442678</v>
+        <v>443030</v>
       </c>
       <c r="R36" t="n">
-        <v>6764817</v>
+        <v>6765092</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5100,7 +5100,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129565964</v>
+        <v>129565983</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443407</v>
+        <v>443363</v>
       </c>
       <c r="R43" t="n">
-        <v>6765308</v>
+        <v>6765473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5207,7 +5207,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129565954</v>
+        <v>129565904</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5242,10 +5242,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443345</v>
+        <v>443044</v>
       </c>
       <c r="R44" t="n">
-        <v>6765155</v>
+        <v>6765238</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5314,7 +5314,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129565983</v>
+        <v>129565974</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443363</v>
+        <v>443350</v>
       </c>
       <c r="R45" t="n">
-        <v>6765473</v>
+        <v>6765366</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,10 +5421,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129565904</v>
+        <v>129565758</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5432,21 +5432,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443044</v>
+        <v>443250</v>
       </c>
       <c r="R46" t="n">
-        <v>6765238</v>
+        <v>6765208</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,7 +5528,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129565974</v>
+        <v>129565964</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443350</v>
+        <v>443407</v>
       </c>
       <c r="R47" t="n">
-        <v>6765366</v>
+        <v>6765308</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129565758</v>
+        <v>129565954</v>
       </c>
       <c r="B48" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5646,21 +5646,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443250</v>
+        <v>443345</v>
       </c>
       <c r="R48" t="n">
-        <v>6765208</v>
+        <v>6765155</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5854,10 +5854,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129565957</v>
+        <v>129565767</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443383</v>
+        <v>443318</v>
       </c>
       <c r="R50" t="n">
-        <v>6765197</v>
+        <v>6765387</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5961,7 +5961,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129565917</v>
+        <v>129565957</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442736</v>
+        <v>443383</v>
       </c>
       <c r="R51" t="n">
-        <v>6765272</v>
+        <v>6765197</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6282,7 +6282,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129565880</v>
+        <v>129565969</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442751</v>
+        <v>443402</v>
       </c>
       <c r="R54" t="n">
-        <v>6764908</v>
+        <v>6765392</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6389,10 +6389,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129565969</v>
+        <v>129565804</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6400,34 +6400,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443402</v>
+        <v>442847</v>
       </c>
       <c r="R55" t="n">
-        <v>6765392</v>
+        <v>6765272</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6459,7 +6464,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6469,7 +6474,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6496,50 +6501,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129565804</v>
+        <v>129565812</v>
       </c>
       <c r="B56" t="n">
-        <v>57724</v>
+        <v>97598</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442847</v>
+        <v>443420</v>
       </c>
       <c r="R56" t="n">
-        <v>6765272</v>
+        <v>6765417</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6608,10 +6608,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129565767</v>
+        <v>129565772</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79634</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443318</v>
+        <v>443016</v>
       </c>
       <c r="R57" t="n">
-        <v>6765387</v>
+        <v>6765122</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6715,32 +6715,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129565812</v>
+        <v>129565845</v>
       </c>
       <c r="B58" t="n">
-        <v>97598</v>
+        <v>78802</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6750,10 +6750,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443420</v>
+        <v>443296</v>
       </c>
       <c r="R58" t="n">
-        <v>6765417</v>
+        <v>6765499</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6822,10 +6822,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129565772</v>
+        <v>129565917</v>
       </c>
       <c r="B59" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443016</v>
+        <v>442736</v>
       </c>
       <c r="R59" t="n">
-        <v>6765122</v>
+        <v>6765272</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6929,10 +6929,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129565845</v>
+        <v>129565880</v>
       </c>
       <c r="B60" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443296</v>
+        <v>442751</v>
       </c>
       <c r="R60" t="n">
-        <v>6765499</v>
+        <v>6764908</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7036,10 +7036,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129565788</v>
+        <v>129565865</v>
       </c>
       <c r="B61" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7047,21 +7047,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7071,10 +7071,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442726</v>
+        <v>442669</v>
       </c>
       <c r="R61" t="n">
-        <v>6764799</v>
+        <v>6764828</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7143,10 +7143,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129566003</v>
+        <v>129565788</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7154,21 +7154,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443142</v>
+        <v>442726</v>
       </c>
       <c r="R62" t="n">
-        <v>6765165</v>
+        <v>6764799</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7250,7 +7250,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129565882</v>
+        <v>129566003</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442762</v>
+        <v>443142</v>
       </c>
       <c r="R63" t="n">
-        <v>6764920</v>
+        <v>6765165</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7357,7 +7357,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129565865</v>
+        <v>129565882</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442669</v>
+        <v>442762</v>
       </c>
       <c r="R64" t="n">
-        <v>6764828</v>
+        <v>6764920</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7802,10 +7802,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129565801</v>
+        <v>129565847</v>
       </c>
       <c r="B68" t="n">
-        <v>57724</v>
+        <v>81029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7813,39 +7813,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443258</v>
+        <v>443068</v>
       </c>
       <c r="R68" t="n">
-        <v>6765343</v>
+        <v>6765019</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7877,7 +7872,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7887,7 +7882,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7914,10 +7909,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129565847</v>
+        <v>129566017</v>
       </c>
       <c r="B69" t="n">
-        <v>81029</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7925,21 +7920,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7949,10 +7944,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443068</v>
+        <v>442707</v>
       </c>
       <c r="R69" t="n">
-        <v>6765019</v>
+        <v>6764791</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7984,7 +7979,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7994,7 +7989,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8021,7 +8016,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129566017</v>
+        <v>129565866</v>
       </c>
       <c r="B70" t="n">
         <v>79044</v>
@@ -8056,10 +8051,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>442707</v>
+        <v>442685</v>
       </c>
       <c r="R70" t="n">
-        <v>6764791</v>
+        <v>6764827</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8091,7 +8086,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8101,7 +8096,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8128,7 +8123,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129565911</v>
+        <v>129565994</v>
       </c>
       <c r="B71" t="n">
         <v>79044</v>
@@ -8163,10 +8158,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>442817</v>
+        <v>443076</v>
       </c>
       <c r="R71" t="n">
-        <v>6765276</v>
+        <v>6765364</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8198,7 +8193,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8208,7 +8203,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8235,7 +8230,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129565866</v>
+        <v>129565978</v>
       </c>
       <c r="B72" t="n">
         <v>79044</v>
@@ -8270,10 +8265,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>442685</v>
+        <v>443303</v>
       </c>
       <c r="R72" t="n">
-        <v>6764827</v>
+        <v>6765447</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8305,7 +8300,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8315,7 +8310,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8342,7 +8337,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129565994</v>
+        <v>129565903</v>
       </c>
       <c r="B73" t="n">
         <v>79044</v>
@@ -8377,10 +8372,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443076</v>
+        <v>443051</v>
       </c>
       <c r="R73" t="n">
-        <v>6765364</v>
+        <v>6765229</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8412,7 +8407,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8422,7 +8417,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8449,7 +8444,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129565978</v>
+        <v>129565993</v>
       </c>
       <c r="B74" t="n">
         <v>79044</v>
@@ -8484,10 +8479,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443303</v>
+        <v>443126</v>
       </c>
       <c r="R74" t="n">
-        <v>6765447</v>
+        <v>6765359</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8519,7 +8514,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8529,7 +8524,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8556,7 +8551,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129565903</v>
+        <v>129565911</v>
       </c>
       <c r="B75" t="n">
         <v>79044</v>
@@ -8591,10 +8586,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443051</v>
+        <v>442817</v>
       </c>
       <c r="R75" t="n">
-        <v>6765229</v>
+        <v>6765276</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8626,7 +8621,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8636,7 +8631,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8663,10 +8658,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129565993</v>
+        <v>129565801</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8674,34 +8669,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443126</v>
+        <v>443258</v>
       </c>
       <c r="R76" t="n">
-        <v>6765359</v>
+        <v>6765343</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8770,45 +8770,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129565953</v>
+        <v>129565820</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443326</v>
+        <v>443109</v>
       </c>
       <c r="R77" t="n">
-        <v>6765167</v>
+        <v>6765024</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8840,7 +8845,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8850,7 +8855,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8877,7 +8882,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129565883</v>
+        <v>129565953</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8912,10 +8917,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>442773</v>
+        <v>443326</v>
       </c>
       <c r="R78" t="n">
-        <v>6764941</v>
+        <v>6765167</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8947,7 +8952,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8957,7 +8962,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8984,7 +8989,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129565941</v>
+        <v>129565883</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -9019,10 +9024,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442718</v>
+        <v>442773</v>
       </c>
       <c r="R79" t="n">
-        <v>6764837</v>
+        <v>6764941</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9054,7 +9059,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9064,7 +9069,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9091,7 +9096,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129565873</v>
+        <v>129565941</v>
       </c>
       <c r="B80" t="n">
         <v>79044</v>
@@ -9126,10 +9131,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>442684</v>
+        <v>442718</v>
       </c>
       <c r="R80" t="n">
-        <v>6764865</v>
+        <v>6764837</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9161,7 +9166,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9171,7 +9176,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9198,7 +9203,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129565979</v>
+        <v>129565873</v>
       </c>
       <c r="B81" t="n">
         <v>79044</v>
@@ -9233,10 +9238,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443306</v>
+        <v>442684</v>
       </c>
       <c r="R81" t="n">
-        <v>6765458</v>
+        <v>6764865</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9268,7 +9273,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9278,7 +9283,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9519,7 +9524,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129565914</v>
+        <v>129565987</v>
       </c>
       <c r="B84" t="n">
         <v>79044</v>
@@ -9554,10 +9559,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>442770</v>
+        <v>443310</v>
       </c>
       <c r="R84" t="n">
-        <v>6765256</v>
+        <v>6765374</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9589,7 +9594,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9599,7 +9604,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9626,7 +9631,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129565987</v>
+        <v>129565979</v>
       </c>
       <c r="B85" t="n">
         <v>79044</v>
@@ -9661,10 +9666,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443310</v>
+        <v>443306</v>
       </c>
       <c r="R85" t="n">
-        <v>6765374</v>
+        <v>6765458</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9696,7 +9701,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9706,7 +9711,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9733,50 +9738,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129565820</v>
+        <v>129565914</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443109</v>
+        <v>442770</v>
       </c>
       <c r="R86" t="n">
-        <v>6765024</v>
+        <v>6765256</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9845,10 +9845,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129566027</v>
+        <v>129565932</v>
       </c>
       <c r="B87" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443043</v>
+        <v>442724</v>
       </c>
       <c r="R87" t="n">
-        <v>6765047</v>
+        <v>6765212</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9952,10 +9952,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129565849</v>
+        <v>129565966</v>
       </c>
       <c r="B88" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9963,21 +9963,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443033</v>
+        <v>443432</v>
       </c>
       <c r="R88" t="n">
-        <v>6765241</v>
+        <v>6765347</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10059,10 +10059,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129565844</v>
+        <v>129565956</v>
       </c>
       <c r="B89" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10070,21 +10070,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443017</v>
+        <v>443366</v>
       </c>
       <c r="R89" t="n">
-        <v>6765118</v>
+        <v>6765190</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129565932</v>
+        <v>129565961</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>442724</v>
+        <v>443405</v>
       </c>
       <c r="R90" t="n">
-        <v>6765212</v>
+        <v>6765244</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10273,7 +10273,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129565966</v>
+        <v>129566005</v>
       </c>
       <c r="B91" t="n">
         <v>79044</v>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443432</v>
+        <v>443160</v>
       </c>
       <c r="R91" t="n">
-        <v>6765347</v>
+        <v>6765086</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10380,7 +10380,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129565902</v>
+        <v>129565899</v>
       </c>
       <c r="B92" t="n">
         <v>79044</v>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443010</v>
+        <v>443088</v>
       </c>
       <c r="R92" t="n">
-        <v>6765160</v>
+        <v>6765090</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10487,10 +10487,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129565976</v>
+        <v>129566027</v>
       </c>
       <c r="B93" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10498,21 +10498,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10522,10 +10522,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443332</v>
+        <v>443043</v>
       </c>
       <c r="R93" t="n">
-        <v>6765403</v>
+        <v>6765047</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10594,10 +10594,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129565956</v>
+        <v>129565849</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10605,21 +10605,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443366</v>
+        <v>443033</v>
       </c>
       <c r="R94" t="n">
-        <v>6765190</v>
+        <v>6765241</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,7 +10701,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129565961</v>
+        <v>129565902</v>
       </c>
       <c r="B95" t="n">
         <v>79044</v>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443405</v>
+        <v>443010</v>
       </c>
       <c r="R95" t="n">
-        <v>6765244</v>
+        <v>6765160</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10808,7 +10808,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129566005</v>
+        <v>129565976</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443160</v>
+        <v>443332</v>
       </c>
       <c r="R96" t="n">
-        <v>6765086</v>
+        <v>6765403</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10915,45 +10915,52 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129565899</v>
+        <v>129565784</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>56917</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443088</v>
+        <v>443093</v>
       </c>
       <c r="R97" t="n">
-        <v>6765090</v>
+        <v>6765290</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10985,7 +10992,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10995,7 +11002,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11022,52 +11029,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129565784</v>
+        <v>129565844</v>
       </c>
       <c r="B98" t="n">
-        <v>56917</v>
+        <v>78802</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443093</v>
+        <v>443017</v>
       </c>
       <c r="R98" t="n">
-        <v>6765290</v>
+        <v>6765118</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11997,10 +11997,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129565876</v>
+        <v>129566023</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12008,21 +12008,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12032,10 +12032,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>442690</v>
+        <v>443207</v>
       </c>
       <c r="R107" t="n">
-        <v>6764884</v>
+        <v>6765081</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12077,7 +12077,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12104,7 +12109,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129565891</v>
+        <v>129565876</v>
       </c>
       <c r="B108" t="n">
         <v>79044</v>
@@ -12139,10 +12144,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>442829</v>
+        <v>442690</v>
       </c>
       <c r="R108" t="n">
-        <v>6764901</v>
+        <v>6764884</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12174,7 +12179,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12184,7 +12189,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12211,7 +12216,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129565960</v>
+        <v>129565891</v>
       </c>
       <c r="B109" t="n">
         <v>79044</v>
@@ -12246,10 +12251,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443403</v>
+        <v>442829</v>
       </c>
       <c r="R109" t="n">
-        <v>6765238</v>
+        <v>6764901</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12281,7 +12286,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12291,7 +12296,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12318,10 +12323,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129566023</v>
+        <v>129565960</v>
       </c>
       <c r="B110" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12329,21 +12334,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12353,10 +12358,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443207</v>
+        <v>443403</v>
       </c>
       <c r="R110" t="n">
-        <v>6765081</v>
+        <v>6765238</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12388,7 +12393,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12398,12 +12403,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12761,10 +12761,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129565892</v>
+        <v>129566030</v>
       </c>
       <c r="B114" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12772,21 +12772,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>442831</v>
+        <v>443283</v>
       </c>
       <c r="R114" t="n">
-        <v>6764873</v>
+        <v>6765488</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12868,7 +12868,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129565992</v>
+        <v>129565892</v>
       </c>
       <c r="B115" t="n">
         <v>79044</v>
@@ -12903,10 +12903,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443143</v>
+        <v>442831</v>
       </c>
       <c r="R115" t="n">
-        <v>6765322</v>
+        <v>6764873</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12975,7 +12975,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129565926</v>
+        <v>129565992</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -13010,10 +13010,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>442748</v>
+        <v>443143</v>
       </c>
       <c r="R116" t="n">
-        <v>6765234</v>
+        <v>6765322</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13082,10 +13082,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129566008</v>
+        <v>129565852</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13093,21 +13093,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13117,10 +13117,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>442968</v>
+        <v>443321</v>
       </c>
       <c r="R117" t="n">
-        <v>6765088</v>
+        <v>6765425</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13189,10 +13189,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129565949</v>
+        <v>129565762</v>
       </c>
       <c r="B118" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13200,21 +13200,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13224,10 +13224,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443110</v>
+        <v>442861</v>
       </c>
       <c r="R118" t="n">
-        <v>6765023</v>
+        <v>6764908</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13296,10 +13296,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129565800</v>
+        <v>129565756</v>
       </c>
       <c r="B119" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13307,39 +13307,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443020</v>
+        <v>443179</v>
       </c>
       <c r="R119" t="n">
-        <v>6764999</v>
+        <v>6765294</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13371,7 +13366,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13381,7 +13376,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13408,10 +13403,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129565852</v>
+        <v>129565926</v>
       </c>
       <c r="B120" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13419,21 +13414,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13443,10 +13438,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443321</v>
+        <v>442748</v>
       </c>
       <c r="R120" t="n">
-        <v>6765425</v>
+        <v>6765234</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13478,7 +13473,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13488,7 +13483,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13515,10 +13510,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129565762</v>
+        <v>129565850</v>
       </c>
       <c r="B121" t="n">
-        <v>83012</v>
+        <v>78801</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13526,21 +13521,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13550,10 +13545,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>442861</v>
+        <v>443017</v>
       </c>
       <c r="R121" t="n">
-        <v>6764908</v>
+        <v>6765114</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13585,7 +13580,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13595,7 +13590,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13622,7 +13617,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129565756</v>
+        <v>129565755</v>
       </c>
       <c r="B122" t="n">
         <v>79663</v>
@@ -13657,10 +13652,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443179</v>
+        <v>443282</v>
       </c>
       <c r="R122" t="n">
-        <v>6765294</v>
+        <v>6765487</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13692,7 +13687,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13702,7 +13697,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13729,10 +13724,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129565850</v>
+        <v>129565775</v>
       </c>
       <c r="B123" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13740,21 +13735,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13764,10 +13759,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443017</v>
+        <v>443250</v>
       </c>
       <c r="R123" t="n">
-        <v>6765114</v>
+        <v>6765209</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13799,7 +13794,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13809,7 +13804,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13836,10 +13831,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129565755</v>
+        <v>129566008</v>
       </c>
       <c r="B124" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13847,21 +13842,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13871,10 +13866,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443282</v>
+        <v>442968</v>
       </c>
       <c r="R124" t="n">
-        <v>6765487</v>
+        <v>6765088</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13906,7 +13901,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13916,7 +13911,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13943,10 +13938,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129566030</v>
+        <v>129565949</v>
       </c>
       <c r="B125" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13954,21 +13949,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13978,10 +13973,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443283</v>
+        <v>443110</v>
       </c>
       <c r="R125" t="n">
-        <v>6765488</v>
+        <v>6765023</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14013,7 +14008,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14023,7 +14018,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14050,10 +14045,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129565775</v>
+        <v>129565800</v>
       </c>
       <c r="B126" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14061,34 +14056,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443250</v>
+        <v>443020</v>
       </c>
       <c r="R126" t="n">
-        <v>6765209</v>
+        <v>6764999</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14271,50 +14271,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129565840</v>
+        <v>129565985</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443118</v>
+        <v>443324</v>
       </c>
       <c r="R128" t="n">
-        <v>6765278</v>
+        <v>6765398</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14346,7 +14341,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14356,7 +14351,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14383,10 +14378,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129565766</v>
+        <v>129565925</v>
       </c>
       <c r="B129" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14394,21 +14389,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14418,10 +14413,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443305</v>
+        <v>442732</v>
       </c>
       <c r="R129" t="n">
-        <v>6765463</v>
+        <v>6765239</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14453,7 +14448,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14463,7 +14458,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14490,10 +14485,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129566025</v>
+        <v>129565951</v>
       </c>
       <c r="B130" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14501,21 +14496,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14525,10 +14520,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>442693</v>
+        <v>443224</v>
       </c>
       <c r="R130" t="n">
-        <v>6764827</v>
+        <v>6765097</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14560,7 +14555,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14570,7 +14565,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14597,10 +14592,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129566032</v>
+        <v>129565920</v>
       </c>
       <c r="B131" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14608,21 +14603,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14632,10 +14627,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443236</v>
+        <v>442734</v>
       </c>
       <c r="R131" t="n">
-        <v>6765316</v>
+        <v>6765264</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14667,7 +14662,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14677,7 +14672,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14704,7 +14699,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129565985</v>
+        <v>129566004</v>
       </c>
       <c r="B132" t="n">
         <v>79044</v>
@@ -14739,10 +14734,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443324</v>
+        <v>443246</v>
       </c>
       <c r="R132" t="n">
-        <v>6765398</v>
+        <v>6765145</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14774,7 +14769,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14784,7 +14779,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14811,7 +14806,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129565925</v>
+        <v>129565959</v>
       </c>
       <c r="B133" t="n">
         <v>79044</v>
@@ -14846,10 +14841,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>442732</v>
+        <v>443414</v>
       </c>
       <c r="R133" t="n">
-        <v>6765239</v>
+        <v>6765221</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14881,7 +14876,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14891,7 +14886,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14918,10 +14913,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129566004</v>
+        <v>129565766</v>
       </c>
       <c r="B134" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14929,21 +14924,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14953,10 +14948,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443246</v>
+        <v>443305</v>
       </c>
       <c r="R134" t="n">
-        <v>6765145</v>
+        <v>6765463</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14988,7 +14983,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14998,7 +14993,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15025,10 +15020,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129565951</v>
+        <v>129566025</v>
       </c>
       <c r="B135" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15036,21 +15031,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15060,10 +15055,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>443224</v>
+        <v>442693</v>
       </c>
       <c r="R135" t="n">
-        <v>6765097</v>
+        <v>6764827</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15095,7 +15090,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15105,7 +15100,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15132,10 +15127,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129565959</v>
+        <v>129566032</v>
       </c>
       <c r="B136" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15143,21 +15138,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15167,10 +15162,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>443414</v>
+        <v>443236</v>
       </c>
       <c r="R136" t="n">
-        <v>6765221</v>
+        <v>6765316</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15202,7 +15197,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15212,7 +15207,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15239,45 +15234,50 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129565920</v>
+        <v>129565840</v>
       </c>
       <c r="B137" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>442734</v>
+        <v>443118</v>
       </c>
       <c r="R137" t="n">
-        <v>6765264</v>
+        <v>6765278</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15346,50 +15346,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129565842</v>
+        <v>129565752</v>
       </c>
       <c r="B138" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>443232</v>
+        <v>443004</v>
       </c>
       <c r="R138" t="n">
-        <v>6765136</v>
+        <v>6765163</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15421,7 +15416,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15431,7 +15426,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15458,50 +15453,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129565827</v>
+        <v>129565893</v>
       </c>
       <c r="B139" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>442998</v>
+        <v>442835</v>
       </c>
       <c r="R139" t="n">
-        <v>6765028</v>
+        <v>6764863</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15533,7 +15523,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15543,7 +15533,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15570,10 +15560,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129566031</v>
+        <v>129566014</v>
       </c>
       <c r="B140" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15581,21 +15571,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15605,10 +15595,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443296</v>
+        <v>442813</v>
       </c>
       <c r="R140" t="n">
-        <v>6765499</v>
+        <v>6764860</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15640,7 +15630,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15650,7 +15640,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15677,10 +15667,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129565764</v>
+        <v>129565770</v>
       </c>
       <c r="B141" t="n">
-        <v>79076</v>
+        <v>79634</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15688,21 +15678,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15712,10 +15702,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443048</v>
+        <v>443068</v>
       </c>
       <c r="R141" t="n">
-        <v>6765235</v>
+        <v>6765020</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15747,7 +15737,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15757,7 +15747,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15784,7 +15774,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129566026</v>
+        <v>129566031</v>
       </c>
       <c r="B142" t="n">
         <v>78710</v>
@@ -15819,10 +15809,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>442684</v>
+        <v>443296</v>
       </c>
       <c r="R142" t="n">
-        <v>6764861</v>
+        <v>6765499</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15854,7 +15844,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15864,7 +15854,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15891,10 +15881,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129565780</v>
+        <v>129565764</v>
       </c>
       <c r="B143" t="n">
-        <v>91553</v>
+        <v>79076</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15902,21 +15892,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15926,10 +15916,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>443405</v>
+        <v>443048</v>
       </c>
       <c r="R143" t="n">
-        <v>6765308</v>
+        <v>6765235</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15961,7 +15951,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15971,7 +15961,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15998,32 +15988,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129565769</v>
+        <v>129566026</v>
       </c>
       <c r="B144" t="n">
-        <v>91517</v>
+        <v>78710</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16033,10 +16023,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>443362</v>
+        <v>442684</v>
       </c>
       <c r="R144" t="n">
-        <v>6765377</v>
+        <v>6764861</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16068,7 +16058,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16078,7 +16068,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16105,10 +16095,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129565752</v>
+        <v>129565780</v>
       </c>
       <c r="B145" t="n">
-        <v>79663</v>
+        <v>91553</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16116,21 +16106,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16140,10 +16130,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>443004</v>
+        <v>443405</v>
       </c>
       <c r="R145" t="n">
-        <v>6765163</v>
+        <v>6765308</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16175,7 +16165,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16185,7 +16175,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16645,7 +16635,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129565893</v>
+        <v>129565990</v>
       </c>
       <c r="B150" t="n">
         <v>79044</v>
@@ -16680,10 +16670,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>442835</v>
+        <v>443229</v>
       </c>
       <c r="R150" t="n">
-        <v>6764863</v>
+        <v>6765319</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16715,7 +16705,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16725,7 +16715,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16752,32 +16742,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129565990</v>
+        <v>129565769</v>
       </c>
       <c r="B151" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16787,10 +16777,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>443229</v>
+        <v>443362</v>
       </c>
       <c r="R151" t="n">
-        <v>6765319</v>
+        <v>6765377</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16822,7 +16812,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16832,7 +16822,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16859,7 +16849,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129566014</v>
+        <v>129565913</v>
       </c>
       <c r="B152" t="n">
         <v>79044</v>
@@ -16894,10 +16884,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>442813</v>
+        <v>442773</v>
       </c>
       <c r="R152" t="n">
-        <v>6764860</v>
+        <v>6765264</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16929,7 +16919,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16939,7 +16929,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16966,7 +16956,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129565913</v>
+        <v>129565871</v>
       </c>
       <c r="B153" t="n">
         <v>79044</v>
@@ -17001,10 +16991,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>442773</v>
+        <v>442690</v>
       </c>
       <c r="R153" t="n">
-        <v>6765264</v>
+        <v>6764850</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17036,7 +17026,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17046,7 +17036,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17073,7 +17063,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129565871</v>
+        <v>129565895</v>
       </c>
       <c r="B154" t="n">
         <v>79044</v>
@@ -17108,10 +17098,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>442690</v>
+        <v>443005</v>
       </c>
       <c r="R154" t="n">
-        <v>6764850</v>
+        <v>6765037</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17143,7 +17133,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17153,7 +17143,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17180,7 +17170,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129565895</v>
+        <v>129565977</v>
       </c>
       <c r="B155" t="n">
         <v>79044</v>
@@ -17215,10 +17205,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443005</v>
+        <v>443313</v>
       </c>
       <c r="R155" t="n">
-        <v>6765037</v>
+        <v>6765439</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17250,7 +17240,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17260,7 +17250,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17287,45 +17277,50 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129565977</v>
+        <v>129565842</v>
       </c>
       <c r="B156" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>443313</v>
+        <v>443232</v>
       </c>
       <c r="R156" t="n">
-        <v>6765439</v>
+        <v>6765136</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17357,7 +17352,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17367,7 +17362,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17394,45 +17389,50 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129565770</v>
+        <v>129565827</v>
       </c>
       <c r="B157" t="n">
-        <v>79634</v>
+        <v>8450</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>443068</v>
+        <v>442998</v>
       </c>
       <c r="R157" t="n">
-        <v>6765020</v>
+        <v>6765028</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17501,38 +17501,38 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129565799</v>
+        <v>129565823</v>
       </c>
       <c r="B158" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -17541,10 +17541,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>443086</v>
+        <v>443008</v>
       </c>
       <c r="R158" t="n">
-        <v>6765106</v>
+        <v>6765154</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18260,7 +18260,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129565975</v>
+        <v>129565980</v>
       </c>
       <c r="B165" t="n">
         <v>79044</v>
@@ -18295,10 +18295,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>443337</v>
+        <v>443299</v>
       </c>
       <c r="R165" t="n">
-        <v>6765385</v>
+        <v>6765469</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18367,7 +18367,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129565980</v>
+        <v>129565928</v>
       </c>
       <c r="B166" t="n">
         <v>79044</v>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>443299</v>
+        <v>442782</v>
       </c>
       <c r="R166" t="n">
-        <v>6765469</v>
+        <v>6765222</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18447,7 +18447,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18474,7 +18474,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129565928</v>
+        <v>129565975</v>
       </c>
       <c r="B167" t="n">
         <v>79044</v>
@@ -18509,10 +18509,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>442782</v>
+        <v>443337</v>
       </c>
       <c r="R167" t="n">
-        <v>6765222</v>
+        <v>6765385</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18554,7 +18554,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18581,38 +18581,38 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129565823</v>
+        <v>129565799</v>
       </c>
       <c r="B168" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -18621,10 +18621,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>443008</v>
+        <v>443086</v>
       </c>
       <c r="R168" t="n">
-        <v>6765154</v>
+        <v>6765106</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18656,7 +18656,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18693,45 +18693,50 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129565968</v>
+        <v>129565829</v>
       </c>
       <c r="B169" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>443400</v>
+        <v>443008</v>
       </c>
       <c r="R169" t="n">
-        <v>6765375</v>
+        <v>6765122</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18763,7 +18768,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18773,7 +18778,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18800,45 +18805,50 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129566012</v>
+        <v>129565822</v>
       </c>
       <c r="B170" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>442827</v>
+        <v>443092</v>
       </c>
       <c r="R170" t="n">
-        <v>6764880</v>
+        <v>6765061</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18870,7 +18880,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18880,7 +18890,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18907,45 +18917,50 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129565929</v>
+        <v>129565830</v>
       </c>
       <c r="B171" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>442823</v>
+        <v>443009</v>
       </c>
       <c r="R171" t="n">
-        <v>6765181</v>
+        <v>6765160</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18977,7 +18992,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18987,7 +19002,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19014,45 +19029,50 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129565910</v>
+        <v>129565828</v>
       </c>
       <c r="B172" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>442825</v>
+        <v>443021</v>
       </c>
       <c r="R172" t="n">
-        <v>6765266</v>
+        <v>6765053</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19084,7 +19104,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19094,7 +19114,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19121,50 +19141,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129565828</v>
+        <v>129565968</v>
       </c>
       <c r="B173" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443021</v>
+        <v>443400</v>
       </c>
       <c r="R173" t="n">
-        <v>6765053</v>
+        <v>6765375</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19196,7 +19211,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19206,7 +19221,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19233,50 +19248,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129565829</v>
+        <v>129566012</v>
       </c>
       <c r="B174" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443008</v>
+        <v>442827</v>
       </c>
       <c r="R174" t="n">
-        <v>6765122</v>
+        <v>6764880</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19308,7 +19318,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19318,7 +19328,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19345,50 +19355,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129565822</v>
+        <v>129565929</v>
       </c>
       <c r="B175" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>443092</v>
+        <v>442823</v>
       </c>
       <c r="R175" t="n">
-        <v>6765061</v>
+        <v>6765181</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19420,7 +19425,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19430,7 +19435,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19457,50 +19462,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129565830</v>
+        <v>129565910</v>
       </c>
       <c r="B176" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>443009</v>
+        <v>442825</v>
       </c>
       <c r="R176" t="n">
-        <v>6765160</v>
+        <v>6765266</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19569,10 +19569,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129566033</v>
+        <v>129565806</v>
       </c>
       <c r="B177" t="n">
-        <v>78710</v>
+        <v>57724</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19580,34 +19580,39 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>443144</v>
+        <v>443430</v>
       </c>
       <c r="R177" t="n">
-        <v>6765199</v>
+        <v>6765200</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19639,7 +19644,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19649,7 +19654,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19676,32 +19681,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129565927</v>
+        <v>129565808</v>
       </c>
       <c r="B178" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19711,10 +19716,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>442770</v>
+        <v>443432</v>
       </c>
       <c r="R178" t="n">
-        <v>6765225</v>
+        <v>6765348</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19746,7 +19751,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19756,7 +19761,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19783,10 +19788,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129565912</v>
+        <v>129566033</v>
       </c>
       <c r="B179" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19794,21 +19799,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19818,10 +19823,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>442776</v>
+        <v>443144</v>
       </c>
       <c r="R179" t="n">
-        <v>6765280</v>
+        <v>6765199</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19853,7 +19858,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19863,7 +19868,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19890,7 +19895,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129565972</v>
+        <v>129565912</v>
       </c>
       <c r="B180" t="n">
         <v>79044</v>
@@ -19925,10 +19930,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>443398</v>
+        <v>442776</v>
       </c>
       <c r="R180" t="n">
-        <v>6765434</v>
+        <v>6765280</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19960,7 +19965,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19970,7 +19975,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19997,7 +20002,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129565971</v>
+        <v>129565972</v>
       </c>
       <c r="B181" t="n">
         <v>79044</v>
@@ -20032,10 +20037,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>443406</v>
+        <v>443398</v>
       </c>
       <c r="R181" t="n">
-        <v>6765450</v>
+        <v>6765434</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20104,7 +20109,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129565984</v>
+        <v>129565971</v>
       </c>
       <c r="B182" t="n">
         <v>79044</v>
@@ -20139,10 +20144,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443338</v>
+        <v>443406</v>
       </c>
       <c r="R182" t="n">
-        <v>6765441</v>
+        <v>6765450</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20174,7 +20179,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20184,7 +20189,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20211,7 +20216,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129565879</v>
+        <v>129565984</v>
       </c>
       <c r="B183" t="n">
         <v>79044</v>
@@ -20246,10 +20251,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>442749</v>
+        <v>443338</v>
       </c>
       <c r="R183" t="n">
-        <v>6764886</v>
+        <v>6765441</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20281,7 +20286,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20291,7 +20296,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20318,7 +20323,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129565973</v>
+        <v>129565879</v>
       </c>
       <c r="B184" t="n">
         <v>79044</v>
@@ -20353,10 +20358,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443383</v>
+        <v>442749</v>
       </c>
       <c r="R184" t="n">
-        <v>6765415</v>
+        <v>6764886</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20388,7 +20393,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20398,7 +20403,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20425,7 +20430,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129566002</v>
+        <v>129565973</v>
       </c>
       <c r="B185" t="n">
         <v>79044</v>
@@ -20460,10 +20465,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>443134</v>
+        <v>443383</v>
       </c>
       <c r="R185" t="n">
-        <v>6765184</v>
+        <v>6765415</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20495,7 +20500,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20505,7 +20510,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20532,10 +20537,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129565806</v>
+        <v>129566002</v>
       </c>
       <c r="B186" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20543,39 +20548,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>443430</v>
+        <v>443134</v>
       </c>
       <c r="R186" t="n">
-        <v>6765200</v>
+        <v>6765184</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20607,7 +20607,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20644,10 +20644,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129565787</v>
+        <v>129565927</v>
       </c>
       <c r="B187" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20655,39 +20655,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>443283</v>
+        <v>442770</v>
       </c>
       <c r="R187" t="n">
-        <v>6765488</v>
+        <v>6765225</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20719,7 +20714,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20729,7 +20724,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20756,38 +20751,38 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129565833</v>
+        <v>129565787</v>
       </c>
       <c r="B188" t="n">
-        <v>8450</v>
+        <v>57887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="M188" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -20796,10 +20791,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>442775</v>
+        <v>443283</v>
       </c>
       <c r="R188" t="n">
-        <v>6765271</v>
+        <v>6765488</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20831,7 +20826,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20841,7 +20836,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20868,10 +20863,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129565808</v>
+        <v>129565833</v>
       </c>
       <c r="B189" t="n">
-        <v>97598</v>
+        <v>8450</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20879,34 +20874,39 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>443432</v>
+        <v>442775</v>
       </c>
       <c r="R189" t="n">
-        <v>6765348</v>
+        <v>6765271</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129565771</v>
+        <v>129565963</v>
       </c>
       <c r="B191" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>443081</v>
+        <v>443410</v>
       </c>
       <c r="R191" t="n">
-        <v>6765117</v>
+        <v>6765453</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21194,7 +21194,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129565963</v>
+        <v>129566009</v>
       </c>
       <c r="B192" t="n">
         <v>79044</v>
@@ -21229,10 +21229,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>443410</v>
+        <v>442846</v>
       </c>
       <c r="R192" t="n">
-        <v>6765453</v>
+        <v>6764891</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21301,7 +21301,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129566009</v>
+        <v>129566001</v>
       </c>
       <c r="B193" t="n">
         <v>79044</v>
@@ -21336,10 +21336,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>442846</v>
+        <v>443140</v>
       </c>
       <c r="R193" t="n">
-        <v>6764891</v>
+        <v>6765218</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21408,7 +21408,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129566001</v>
+        <v>129565878</v>
       </c>
       <c r="B194" t="n">
         <v>79044</v>
@@ -21443,10 +21443,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>443140</v>
+        <v>442745</v>
       </c>
       <c r="R194" t="n">
-        <v>6765218</v>
+        <v>6764895</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21478,7 +21478,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21488,7 +21488,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21515,45 +21515,50 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129565878</v>
+        <v>129565826</v>
       </c>
       <c r="B195" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>442745</v>
+        <v>443073</v>
       </c>
       <c r="R195" t="n">
-        <v>6764895</v>
+        <v>6765287</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21585,7 +21590,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21595,7 +21600,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21622,50 +21627,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129565826</v>
+        <v>129565771</v>
       </c>
       <c r="B196" t="n">
-        <v>8450</v>
+        <v>79634</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443073</v>
+        <v>443081</v>
       </c>
       <c r="R196" t="n">
-        <v>6765287</v>
+        <v>6765117</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21697,7 +21697,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21707,7 +21707,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21836,10 +21836,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129565763</v>
+        <v>129565981</v>
       </c>
       <c r="B198" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21847,21 +21847,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21871,10 +21871,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>443051</v>
+        <v>443294</v>
       </c>
       <c r="R198" t="n">
-        <v>6765229</v>
+        <v>6765505</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21916,7 +21916,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21943,7 +21943,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129565981</v>
+        <v>129565955</v>
       </c>
       <c r="B199" t="n">
         <v>79044</v>
@@ -21978,10 +21978,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>443294</v>
+        <v>443351</v>
       </c>
       <c r="R199" t="n">
-        <v>6765505</v>
+        <v>6765163</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22013,7 +22013,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22050,7 +22050,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129565894</v>
+        <v>129565950</v>
       </c>
       <c r="B200" t="n">
         <v>79044</v>
@@ -22085,10 +22085,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>442973</v>
+        <v>443156</v>
       </c>
       <c r="R200" t="n">
-        <v>6764957</v>
+        <v>6765060</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22157,10 +22157,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129565955</v>
+        <v>129565817</v>
       </c>
       <c r="B201" t="n">
-        <v>79044</v>
+        <v>92873</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22168,21 +22168,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22192,10 +22192,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>443351</v>
+        <v>442767</v>
       </c>
       <c r="R201" t="n">
-        <v>6765163</v>
+        <v>6765229</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22227,7 +22227,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22237,7 +22237,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22264,7 +22264,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129565950</v>
+        <v>129565908</v>
       </c>
       <c r="B202" t="n">
         <v>79044</v>
@@ -22299,10 +22299,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>443156</v>
+        <v>442859</v>
       </c>
       <c r="R202" t="n">
-        <v>6765060</v>
+        <v>6765277</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22334,7 +22334,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22371,10 +22371,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129565817</v>
+        <v>129565907</v>
       </c>
       <c r="B203" t="n">
-        <v>92873</v>
+        <v>79044</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22382,21 +22382,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>442767</v>
+        <v>442863</v>
       </c>
       <c r="R203" t="n">
-        <v>6765229</v>
+        <v>6765287</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22441,7 +22441,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22451,7 +22451,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22478,10 +22478,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129565919</v>
+        <v>129565803</v>
       </c>
       <c r="B204" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22489,34 +22489,39 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>442733</v>
+        <v>443250</v>
       </c>
       <c r="R204" t="n">
-        <v>6765274</v>
+        <v>6765211</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22548,7 +22553,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22558,7 +22563,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22585,10 +22590,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129565908</v>
+        <v>129565807</v>
       </c>
       <c r="B205" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22596,34 +22601,39 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>442859</v>
+        <v>442850</v>
       </c>
       <c r="R205" t="n">
-        <v>6765277</v>
+        <v>6764898</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22655,7 +22665,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22665,7 +22675,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22692,10 +22702,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129565907</v>
+        <v>129565763</v>
       </c>
       <c r="B206" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22703,21 +22713,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22727,10 +22737,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>442863</v>
+        <v>443051</v>
       </c>
       <c r="R206" t="n">
-        <v>6765287</v>
+        <v>6765229</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22762,7 +22772,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22772,7 +22782,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22799,10 +22809,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129565803</v>
+        <v>129565894</v>
       </c>
       <c r="B207" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22810,39 +22820,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>443250</v>
+        <v>442973</v>
       </c>
       <c r="R207" t="n">
-        <v>6765211</v>
+        <v>6764957</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22874,7 +22879,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22884,7 +22889,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22911,10 +22916,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129565807</v>
+        <v>129565919</v>
       </c>
       <c r="B208" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22922,39 +22927,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>442850</v>
+        <v>442733</v>
       </c>
       <c r="R208" t="n">
-        <v>6764898</v>
+        <v>6765274</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22986,7 +22986,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23023,10 +23023,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129565798</v>
+        <v>129565848</v>
       </c>
       <c r="B209" t="n">
-        <v>91504</v>
+        <v>81029</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23034,21 +23034,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>112</v>
+        <v>1049</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23058,10 +23058,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>442855</v>
+        <v>443251</v>
       </c>
       <c r="R209" t="n">
-        <v>6764903</v>
+        <v>6765208</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23093,7 +23093,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23130,10 +23130,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129565848</v>
+        <v>129565798</v>
       </c>
       <c r="B210" t="n">
-        <v>81029</v>
+        <v>91504</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23141,21 +23141,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1049</v>
+        <v>112</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23165,10 +23165,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>443251</v>
+        <v>442855</v>
       </c>
       <c r="R210" t="n">
-        <v>6765208</v>
+        <v>6764903</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23200,7 +23200,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24307,45 +24307,50 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129565958</v>
+        <v>129565843</v>
       </c>
       <c r="B221" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>443398</v>
+        <v>443077</v>
       </c>
       <c r="R221" t="n">
-        <v>6765189</v>
+        <v>6765075</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24377,7 +24382,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24387,7 +24392,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24414,45 +24419,50 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129565869</v>
+        <v>129565841</v>
       </c>
       <c r="B222" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>442712</v>
+        <v>443266</v>
       </c>
       <c r="R222" t="n">
-        <v>6764831</v>
+        <v>6765164</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24484,7 +24494,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24494,7 +24504,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24521,45 +24531,50 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129565877</v>
+        <v>129565748</v>
       </c>
       <c r="B223" t="n">
-        <v>79044</v>
+        <v>5197</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>442708</v>
+        <v>443420</v>
       </c>
       <c r="R223" t="n">
-        <v>6764885</v>
+        <v>6765200</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24591,7 +24606,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24601,7 +24616,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24628,45 +24643,50 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129565897</v>
+        <v>129565831</v>
       </c>
       <c r="B224" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>443095</v>
+        <v>443008</v>
       </c>
       <c r="R224" t="n">
-        <v>6765053</v>
+        <v>6765171</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24698,7 +24718,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24708,7 +24728,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24735,7 +24755,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129565864</v>
+        <v>129565958</v>
       </c>
       <c r="B225" t="n">
         <v>79044</v>
@@ -24770,10 +24790,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>442678</v>
+        <v>443398</v>
       </c>
       <c r="R225" t="n">
-        <v>6764817</v>
+        <v>6765189</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24805,7 +24825,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24815,7 +24835,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24842,50 +24862,45 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129565843</v>
+        <v>129565869</v>
       </c>
       <c r="B226" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>443077</v>
+        <v>442712</v>
       </c>
       <c r="R226" t="n">
-        <v>6765075</v>
+        <v>6764831</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24917,7 +24932,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24927,7 +24942,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24954,50 +24969,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129565841</v>
+        <v>129565877</v>
       </c>
       <c r="B227" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>443266</v>
+        <v>442708</v>
       </c>
       <c r="R227" t="n">
-        <v>6765164</v>
+        <v>6764885</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25029,7 +25039,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25039,7 +25049,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25066,50 +25076,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129565748</v>
+        <v>129565864</v>
       </c>
       <c r="B228" t="n">
-        <v>5197</v>
+        <v>79044</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>443420</v>
+        <v>442678</v>
       </c>
       <c r="R228" t="n">
-        <v>6765200</v>
+        <v>6764817</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25141,7 +25146,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25151,7 +25156,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25178,50 +25183,45 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129565831</v>
+        <v>129565897</v>
       </c>
       <c r="B229" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>443008</v>
+        <v>443095</v>
       </c>
       <c r="R229" t="n">
-        <v>6765171</v>
+        <v>6765053</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25253,7 +25253,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25263,7 +25263,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD229" t="b">

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -1970,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129565754</v>
+        <v>129566006</v>
       </c>
       <c r="B14" t="n">
-        <v>79689</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,21 +1981,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443335</v>
+        <v>443030</v>
       </c>
       <c r="R14" t="n">
-        <v>6765160</v>
+        <v>6765092</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129565854</v>
+        <v>129565921</v>
       </c>
       <c r="B15" t="n">
-        <v>78827</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,21 +2088,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443342</v>
+        <v>442732</v>
       </c>
       <c r="R15" t="n">
-        <v>6765500</v>
+        <v>6765254</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129565851</v>
+        <v>129565900</v>
       </c>
       <c r="B16" t="n">
-        <v>78827</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443355</v>
+        <v>443088</v>
       </c>
       <c r="R16" t="n">
-        <v>6765158</v>
+        <v>6765128</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129566006</v>
+        <v>129565909</v>
       </c>
       <c r="B17" t="n">
         <v>79070</v>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443030</v>
+        <v>442834</v>
       </c>
       <c r="R17" t="n">
-        <v>6765092</v>
+        <v>6765265</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,7 +2398,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129565921</v>
+        <v>129565965</v>
       </c>
       <c r="B18" t="n">
         <v>79070</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442732</v>
+        <v>443429</v>
       </c>
       <c r="R18" t="n">
-        <v>6765254</v>
+        <v>6765332</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,45 +2505,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129565900</v>
+        <v>129565834</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443088</v>
+        <v>442810</v>
       </c>
       <c r="R19" t="n">
-        <v>6765128</v>
+        <v>6765170</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,7 +2580,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2585,7 +2590,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129565909</v>
+        <v>129565773</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,21 +2628,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2647,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442834</v>
+        <v>443322</v>
       </c>
       <c r="R20" t="n">
-        <v>6765265</v>
+        <v>6765427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,7 +2687,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2692,7 +2697,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2719,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129565965</v>
+        <v>129565754</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,21 +2735,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443429</v>
+        <v>443335</v>
       </c>
       <c r="R21" t="n">
-        <v>6765332</v>
+        <v>6765160</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2794,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2799,7 +2804,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2826,50 +2831,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129565834</v>
+        <v>129565854</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>78827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442810</v>
+        <v>443342</v>
       </c>
       <c r="R22" t="n">
-        <v>6765170</v>
+        <v>6765500</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,10 +2938,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129565773</v>
+        <v>129565851</v>
       </c>
       <c r="B23" t="n">
-        <v>79660</v>
+        <v>78827</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2949,21 +2949,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443322</v>
+        <v>443355</v>
       </c>
       <c r="R23" t="n">
-        <v>6765427</v>
+        <v>6765158</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,10 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129565860</v>
+        <v>129565757</v>
       </c>
       <c r="B24" t="n">
-        <v>82905</v>
+        <v>79689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>442861</v>
+        <v>443135</v>
       </c>
       <c r="R24" t="n">
-        <v>6764907</v>
+        <v>6765214</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3125,12 +3125,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt, 100-tal fruktkroppar på minst 300 år gammal gran.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3157,10 +3152,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129565942</v>
+        <v>129565853</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>78827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,21 +3163,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442719</v>
+        <v>443296</v>
       </c>
       <c r="R25" t="n">
-        <v>6764829</v>
+        <v>6765502</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,7 +3222,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3237,7 +3232,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3264,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129565898</v>
+        <v>129565759</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>83039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,21 +3270,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3299,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443095</v>
+        <v>442678</v>
       </c>
       <c r="R26" t="n">
-        <v>6765057</v>
+        <v>6764817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,7 +3329,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3344,7 +3339,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3371,45 +3366,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129565998</v>
+        <v>129565783</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>56920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443044</v>
+        <v>442977</v>
       </c>
       <c r="R27" t="n">
-        <v>6765344</v>
+        <v>6765352</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,7 +3448,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3451,7 +3458,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3478,45 +3485,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129566015</v>
+        <v>129565782</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>56920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442816</v>
+        <v>442771</v>
       </c>
       <c r="R28" t="n">
-        <v>6764845</v>
+        <v>6764923</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3560,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3558,7 +3570,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3585,32 +3597,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129565818</v>
+        <v>129566021</v>
       </c>
       <c r="B29" t="n">
-        <v>92901</v>
+        <v>92863</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3620,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443118</v>
+        <v>443030</v>
       </c>
       <c r="R29" t="n">
-        <v>6765378</v>
+        <v>6765092</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3655,7 +3667,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3665,7 +3677,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3692,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129565923</v>
+        <v>129565860</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>82905</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,21 +3715,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3727,10 +3739,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442732</v>
+        <v>442861</v>
       </c>
       <c r="R30" t="n">
-        <v>6765250</v>
+        <v>6764907</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3762,7 +3774,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3772,7 +3784,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt, 100-tal fruktkroppar på minst 300 år gammal gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3799,32 +3816,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129566021</v>
+        <v>129565942</v>
       </c>
       <c r="B31" t="n">
-        <v>92863</v>
+        <v>79070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3834,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443030</v>
+        <v>442719</v>
       </c>
       <c r="R31" t="n">
-        <v>6765092</v>
+        <v>6764829</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,7 +3886,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3879,7 +3896,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3906,10 +3923,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129565757</v>
+        <v>129565898</v>
       </c>
       <c r="B32" t="n">
-        <v>79689</v>
+        <v>79070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3917,21 +3934,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3941,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443135</v>
+        <v>443095</v>
       </c>
       <c r="R32" t="n">
-        <v>6765214</v>
+        <v>6765057</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3976,7 +3993,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3986,7 +4003,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4013,10 +4030,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129565853</v>
+        <v>129565998</v>
       </c>
       <c r="B33" t="n">
-        <v>78827</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4024,21 +4041,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4048,10 +4065,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443296</v>
+        <v>443044</v>
       </c>
       <c r="R33" t="n">
-        <v>6765502</v>
+        <v>6765344</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4083,7 +4100,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4093,7 +4110,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4120,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129565759</v>
+        <v>129566015</v>
       </c>
       <c r="B34" t="n">
-        <v>83039</v>
+        <v>79070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4131,21 +4148,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4155,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>442678</v>
+        <v>442816</v>
       </c>
       <c r="R34" t="n">
-        <v>6764817</v>
+        <v>6764845</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,7 +4207,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4200,7 +4217,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4227,57 +4244,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129565783</v>
+        <v>129565818</v>
       </c>
       <c r="B35" t="n">
-        <v>56920</v>
+        <v>92901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>442977</v>
+        <v>443118</v>
       </c>
       <c r="R35" t="n">
-        <v>6765352</v>
+        <v>6765378</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4309,7 +4314,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4319,7 +4324,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4346,50 +4351,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129565782</v>
+        <v>129565923</v>
       </c>
       <c r="B36" t="n">
-        <v>56920</v>
+        <v>79070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>442771</v>
+        <v>442732</v>
       </c>
       <c r="R36" t="n">
-        <v>6764923</v>
+        <v>6765250</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5854,32 +5854,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129565957</v>
+        <v>129565812</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>97627</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443383</v>
+        <v>443420</v>
       </c>
       <c r="R50" t="n">
-        <v>6765197</v>
+        <v>6765417</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129565917</v>
+        <v>129565767</v>
       </c>
       <c r="B51" t="n">
-        <v>79070</v>
+        <v>79102</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442736</v>
+        <v>443318</v>
       </c>
       <c r="R51" t="n">
-        <v>6765272</v>
+        <v>6765387</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6068,7 +6068,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129566007</v>
+        <v>129565957</v>
       </c>
       <c r="B52" t="n">
         <v>79070</v>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442988</v>
+        <v>443383</v>
       </c>
       <c r="R52" t="n">
-        <v>6765104</v>
+        <v>6765197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,7 +6175,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129565863</v>
+        <v>129565917</v>
       </c>
       <c r="B53" t="n">
         <v>79070</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442660</v>
+        <v>442736</v>
       </c>
       <c r="R53" t="n">
-        <v>6764812</v>
+        <v>6765272</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6282,7 +6282,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129565880</v>
+        <v>129566007</v>
       </c>
       <c r="B54" t="n">
         <v>79070</v>
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442751</v>
+        <v>442988</v>
       </c>
       <c r="R54" t="n">
-        <v>6764908</v>
+        <v>6765104</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6389,7 +6389,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129565969</v>
+        <v>129565863</v>
       </c>
       <c r="B55" t="n">
         <v>79070</v>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443402</v>
+        <v>442660</v>
       </c>
       <c r="R55" t="n">
-        <v>6765392</v>
+        <v>6764812</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6496,10 +6496,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129565767</v>
+        <v>129565880</v>
       </c>
       <c r="B56" t="n">
-        <v>79102</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6507,21 +6507,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443318</v>
+        <v>442751</v>
       </c>
       <c r="R56" t="n">
-        <v>6765387</v>
+        <v>6764908</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6603,10 +6603,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129565804</v>
+        <v>129565969</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6614,39 +6614,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442847</v>
+        <v>443402</v>
       </c>
       <c r="R57" t="n">
-        <v>6765272</v>
+        <v>6765392</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6678,7 +6673,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6688,7 +6683,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6715,10 +6710,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129565772</v>
+        <v>129565804</v>
       </c>
       <c r="B58" t="n">
-        <v>79660</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6726,34 +6721,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443016</v>
+        <v>442847</v>
       </c>
       <c r="R58" t="n">
-        <v>6765122</v>
+        <v>6765272</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6822,10 +6822,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129565845</v>
+        <v>129565772</v>
       </c>
       <c r="B59" t="n">
-        <v>78828</v>
+        <v>79660</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443296</v>
+        <v>443016</v>
       </c>
       <c r="R59" t="n">
-        <v>6765499</v>
+        <v>6765122</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6929,32 +6929,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129565812</v>
+        <v>129565845</v>
       </c>
       <c r="B60" t="n">
-        <v>97627</v>
+        <v>78828</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443420</v>
+        <v>443296</v>
       </c>
       <c r="R60" t="n">
-        <v>6765417</v>
+        <v>6765499</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8770,45 +8770,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129565953</v>
+        <v>129565820</v>
       </c>
       <c r="B77" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443326</v>
+        <v>443109</v>
       </c>
       <c r="R77" t="n">
-        <v>6765167</v>
+        <v>6765024</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8840,7 +8845,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8850,7 +8855,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8877,7 +8882,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129565883</v>
+        <v>129565953</v>
       </c>
       <c r="B78" t="n">
         <v>79070</v>
@@ -8912,10 +8917,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>442773</v>
+        <v>443326</v>
       </c>
       <c r="R78" t="n">
-        <v>6764941</v>
+        <v>6765167</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8947,7 +8952,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8957,7 +8962,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8984,7 +8989,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129565941</v>
+        <v>129565883</v>
       </c>
       <c r="B79" t="n">
         <v>79070</v>
@@ -9019,10 +9024,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442718</v>
+        <v>442773</v>
       </c>
       <c r="R79" t="n">
-        <v>6764837</v>
+        <v>6764941</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9054,7 +9059,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9064,7 +9069,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9091,7 +9096,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129565873</v>
+        <v>129565941</v>
       </c>
       <c r="B80" t="n">
         <v>79070</v>
@@ -9126,10 +9131,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>442684</v>
+        <v>442718</v>
       </c>
       <c r="R80" t="n">
-        <v>6764865</v>
+        <v>6764837</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9161,7 +9166,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9171,7 +9176,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9198,7 +9203,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129565979</v>
+        <v>129565873</v>
       </c>
       <c r="B81" t="n">
         <v>79070</v>
@@ -9233,10 +9238,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443306</v>
+        <v>442684</v>
       </c>
       <c r="R81" t="n">
-        <v>6765458</v>
+        <v>6764865</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9268,7 +9273,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9278,7 +9283,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9305,7 +9310,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129565930</v>
+        <v>129565979</v>
       </c>
       <c r="B82" t="n">
         <v>79070</v>
@@ -9340,10 +9345,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>442768</v>
+        <v>443306</v>
       </c>
       <c r="R82" t="n">
-        <v>6765164</v>
+        <v>6765458</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9375,7 +9380,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9385,7 +9390,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9412,7 +9417,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129565988</v>
+        <v>129565930</v>
       </c>
       <c r="B83" t="n">
         <v>79070</v>
@@ -9447,10 +9452,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443284</v>
+        <v>442768</v>
       </c>
       <c r="R83" t="n">
-        <v>6765343</v>
+        <v>6765164</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9482,7 +9487,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9492,7 +9497,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9519,7 +9524,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129565914</v>
+        <v>129565988</v>
       </c>
       <c r="B84" t="n">
         <v>79070</v>
@@ -9554,10 +9559,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>442770</v>
+        <v>443284</v>
       </c>
       <c r="R84" t="n">
-        <v>6765256</v>
+        <v>6765343</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9589,7 +9594,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9599,7 +9604,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9626,7 +9631,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129565987</v>
+        <v>129565914</v>
       </c>
       <c r="B85" t="n">
         <v>79070</v>
@@ -9661,10 +9666,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443310</v>
+        <v>442770</v>
       </c>
       <c r="R85" t="n">
-        <v>6765374</v>
+        <v>6765256</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9696,7 +9701,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9706,7 +9711,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9733,50 +9738,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129565820</v>
+        <v>129565987</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443109</v>
+        <v>443310</v>
       </c>
       <c r="R86" t="n">
-        <v>6765024</v>
+        <v>6765374</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9845,10 +9845,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129566027</v>
+        <v>129565844</v>
       </c>
       <c r="B87" t="n">
-        <v>78736</v>
+        <v>78828</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443043</v>
+        <v>443017</v>
       </c>
       <c r="R87" t="n">
-        <v>6765047</v>
+        <v>6765118</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9952,10 +9952,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129565844</v>
+        <v>129565849</v>
       </c>
       <c r="B88" t="n">
-        <v>78828</v>
+        <v>78827</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9963,21 +9963,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443017</v>
+        <v>443033</v>
       </c>
       <c r="R88" t="n">
-        <v>6765118</v>
+        <v>6765241</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10059,45 +10059,52 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129565932</v>
+        <v>129565784</v>
       </c>
       <c r="B89" t="n">
-        <v>79070</v>
+        <v>56920</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>442724</v>
+        <v>443093</v>
       </c>
       <c r="R89" t="n">
-        <v>6765212</v>
+        <v>6765290</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10129,7 +10136,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10139,7 +10146,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10166,10 +10173,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129565966</v>
+        <v>129566027</v>
       </c>
       <c r="B90" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10177,21 +10184,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10201,10 +10208,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443432</v>
+        <v>443043</v>
       </c>
       <c r="R90" t="n">
-        <v>6765347</v>
+        <v>6765047</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10236,7 +10243,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10246,7 +10253,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10273,7 +10280,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129565902</v>
+        <v>129565932</v>
       </c>
       <c r="B91" t="n">
         <v>79070</v>
@@ -10308,10 +10315,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443010</v>
+        <v>442724</v>
       </c>
       <c r="R91" t="n">
-        <v>6765160</v>
+        <v>6765212</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10343,7 +10350,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10353,7 +10360,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10380,7 +10387,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129565976</v>
+        <v>129565966</v>
       </c>
       <c r="B92" t="n">
         <v>79070</v>
@@ -10415,10 +10422,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443332</v>
+        <v>443432</v>
       </c>
       <c r="R92" t="n">
-        <v>6765403</v>
+        <v>6765347</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10450,7 +10457,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10467,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10487,7 +10494,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129565956</v>
+        <v>129565902</v>
       </c>
       <c r="B93" t="n">
         <v>79070</v>
@@ -10522,10 +10529,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443366</v>
+        <v>443010</v>
       </c>
       <c r="R93" t="n">
-        <v>6765190</v>
+        <v>6765160</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10564,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10574,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10594,7 +10601,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129565961</v>
+        <v>129565976</v>
       </c>
       <c r="B94" t="n">
         <v>79070</v>
@@ -10629,10 +10636,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443405</v>
+        <v>443332</v>
       </c>
       <c r="R94" t="n">
-        <v>6765244</v>
+        <v>6765403</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10671,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10681,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,7 +10708,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129566005</v>
+        <v>129565956</v>
       </c>
       <c r="B95" t="n">
         <v>79070</v>
@@ -10736,10 +10743,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443160</v>
+        <v>443366</v>
       </c>
       <c r="R95" t="n">
-        <v>6765086</v>
+        <v>6765190</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10771,7 +10778,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10781,7 +10788,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10808,7 +10815,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129565899</v>
+        <v>129565961</v>
       </c>
       <c r="B96" t="n">
         <v>79070</v>
@@ -10843,10 +10850,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443088</v>
+        <v>443405</v>
       </c>
       <c r="R96" t="n">
-        <v>6765090</v>
+        <v>6765244</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10878,7 +10885,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10888,7 +10895,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10915,10 +10922,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129565849</v>
+        <v>129566005</v>
       </c>
       <c r="B97" t="n">
-        <v>78827</v>
+        <v>79070</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10926,21 +10933,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10950,10 +10957,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443033</v>
+        <v>443160</v>
       </c>
       <c r="R97" t="n">
-        <v>6765241</v>
+        <v>6765086</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10985,7 +10992,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10995,7 +11002,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11022,52 +11029,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129565784</v>
+        <v>129565899</v>
       </c>
       <c r="B98" t="n">
-        <v>56920</v>
+        <v>79070</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443093</v>
+        <v>443088</v>
       </c>
       <c r="R98" t="n">
-        <v>6765290</v>
+        <v>6765090</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13943,10 +13943,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129566030</v>
+        <v>129565775</v>
       </c>
       <c r="B125" t="n">
-        <v>78736</v>
+        <v>79660</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443283</v>
+        <v>443250</v>
       </c>
       <c r="R125" t="n">
-        <v>6765488</v>
+        <v>6765209</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14050,10 +14050,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129565775</v>
+        <v>129566030</v>
       </c>
       <c r="B126" t="n">
-        <v>79660</v>
+        <v>78736</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14061,21 +14061,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14085,10 +14085,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443250</v>
+        <v>443283</v>
       </c>
       <c r="R126" t="n">
-        <v>6765209</v>
+        <v>6765488</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14157,45 +14157,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129565766</v>
+        <v>129565840</v>
       </c>
       <c r="B127" t="n">
-        <v>79102</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443305</v>
+        <v>443118</v>
       </c>
       <c r="R127" t="n">
-        <v>6765463</v>
+        <v>6765278</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14227,7 +14232,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14237,7 +14242,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14264,45 +14269,52 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129566025</v>
+        <v>129565785</v>
       </c>
       <c r="B128" t="n">
-        <v>78736</v>
+        <v>56920</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>442693</v>
+        <v>443076</v>
       </c>
       <c r="R128" t="n">
-        <v>6764827</v>
+        <v>6765380</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14334,7 +14346,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14344,7 +14356,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14371,10 +14383,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129566032</v>
+        <v>129565766</v>
       </c>
       <c r="B129" t="n">
-        <v>78736</v>
+        <v>79102</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14382,21 +14394,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14406,10 +14418,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443236</v>
+        <v>443305</v>
       </c>
       <c r="R129" t="n">
-        <v>6765316</v>
+        <v>6765463</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14441,7 +14453,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14451,7 +14463,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14478,10 +14490,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129565985</v>
+        <v>129566025</v>
       </c>
       <c r="B130" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14489,21 +14501,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14513,10 +14525,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443324</v>
+        <v>442693</v>
       </c>
       <c r="R130" t="n">
-        <v>6765398</v>
+        <v>6764827</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14548,7 +14560,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14558,7 +14570,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14585,10 +14597,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129565925</v>
+        <v>129566032</v>
       </c>
       <c r="B131" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14596,21 +14608,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14620,10 +14632,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>442732</v>
+        <v>443236</v>
       </c>
       <c r="R131" t="n">
-        <v>6765239</v>
+        <v>6765316</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14655,7 +14667,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14665,7 +14677,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14692,7 +14704,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129566004</v>
+        <v>129565985</v>
       </c>
       <c r="B132" t="n">
         <v>79070</v>
@@ -14727,10 +14739,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443246</v>
+        <v>443324</v>
       </c>
       <c r="R132" t="n">
-        <v>6765145</v>
+        <v>6765398</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14762,7 +14774,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14772,7 +14784,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14799,7 +14811,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129565951</v>
+        <v>129565925</v>
       </c>
       <c r="B133" t="n">
         <v>79070</v>
@@ -14834,10 +14846,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443224</v>
+        <v>442732</v>
       </c>
       <c r="R133" t="n">
-        <v>6765097</v>
+        <v>6765239</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14869,7 +14881,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14879,7 +14891,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14906,7 +14918,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129565959</v>
+        <v>129566004</v>
       </c>
       <c r="B134" t="n">
         <v>79070</v>
@@ -14941,10 +14953,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443414</v>
+        <v>443246</v>
       </c>
       <c r="R134" t="n">
-        <v>6765221</v>
+        <v>6765145</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14976,7 +14988,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14986,7 +14998,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15013,7 +15025,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129565920</v>
+        <v>129565951</v>
       </c>
       <c r="B135" t="n">
         <v>79070</v>
@@ -15048,10 +15060,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>442734</v>
+        <v>443224</v>
       </c>
       <c r="R135" t="n">
-        <v>6765264</v>
+        <v>6765097</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15083,7 +15095,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15093,7 +15105,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15120,52 +15132,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129565785</v>
+        <v>129565959</v>
       </c>
       <c r="B136" t="n">
-        <v>56920</v>
+        <v>79070</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>443076</v>
+        <v>443414</v>
       </c>
       <c r="R136" t="n">
-        <v>6765380</v>
+        <v>6765221</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15197,7 +15202,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15207,7 +15212,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15234,50 +15239,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129565840</v>
+        <v>129565920</v>
       </c>
       <c r="B137" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>443118</v>
+        <v>442734</v>
       </c>
       <c r="R137" t="n">
-        <v>6765278</v>
+        <v>6765264</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15346,32 +15346,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129565764</v>
+        <v>129565769</v>
       </c>
       <c r="B138" t="n">
-        <v>79102</v>
+        <v>91545</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15381,10 +15381,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>443048</v>
+        <v>443362</v>
       </c>
       <c r="R138" t="n">
-        <v>6765235</v>
+        <v>6765377</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15453,10 +15453,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129566026</v>
+        <v>129565862</v>
       </c>
       <c r="B139" t="n">
-        <v>78736</v>
+        <v>79070</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15464,34 +15464,39 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>442684</v>
+        <v>442822</v>
       </c>
       <c r="R139" t="n">
-        <v>6764861</v>
+        <v>6764864</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15523,7 +15528,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15533,7 +15538,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15560,32 +15565,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129565769</v>
+        <v>129565962</v>
       </c>
       <c r="B140" t="n">
-        <v>91545</v>
+        <v>79070</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15595,10 +15600,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443362</v>
+        <v>443405</v>
       </c>
       <c r="R140" t="n">
-        <v>6765377</v>
+        <v>6765256</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15630,7 +15635,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15640,7 +15645,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15667,10 +15672,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129566031</v>
+        <v>129565991</v>
       </c>
       <c r="B141" t="n">
-        <v>78736</v>
+        <v>79070</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15678,21 +15683,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15702,10 +15707,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443296</v>
+        <v>443155</v>
       </c>
       <c r="R141" t="n">
-        <v>6765499</v>
+        <v>6765323</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15737,7 +15742,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15747,7 +15752,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15774,10 +15779,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129565780</v>
+        <v>129565901</v>
       </c>
       <c r="B142" t="n">
-        <v>91581</v>
+        <v>79070</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15785,21 +15790,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15809,10 +15814,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>443405</v>
+        <v>443054</v>
       </c>
       <c r="R142" t="n">
-        <v>6765308</v>
+        <v>6765138</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15844,7 +15849,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15854,7 +15859,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15881,7 +15886,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129565862</v>
+        <v>129565893</v>
       </c>
       <c r="B143" t="n">
         <v>79070</v>
@@ -15910,21 +15915,16 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>442822</v>
+        <v>442835</v>
       </c>
       <c r="R143" t="n">
-        <v>6764864</v>
+        <v>6764863</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15956,7 +15956,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15993,7 +15993,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129565962</v>
+        <v>129565990</v>
       </c>
       <c r="B144" t="n">
         <v>79070</v>
@@ -16028,10 +16028,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>443405</v>
+        <v>443229</v>
       </c>
       <c r="R144" t="n">
-        <v>6765256</v>
+        <v>6765319</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16100,7 +16100,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129565991</v>
+        <v>129566014</v>
       </c>
       <c r="B145" t="n">
         <v>79070</v>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>443155</v>
+        <v>442813</v>
       </c>
       <c r="R145" t="n">
-        <v>6765323</v>
+        <v>6764860</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16207,7 +16207,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129565901</v>
+        <v>129565913</v>
       </c>
       <c r="B146" t="n">
         <v>79070</v>
@@ -16242,10 +16242,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>443054</v>
+        <v>442773</v>
       </c>
       <c r="R146" t="n">
-        <v>6765138</v>
+        <v>6765264</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16314,7 +16314,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129565893</v>
+        <v>129565871</v>
       </c>
       <c r="B147" t="n">
         <v>79070</v>
@@ -16349,10 +16349,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>442835</v>
+        <v>442690</v>
       </c>
       <c r="R147" t="n">
-        <v>6764863</v>
+        <v>6764850</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16384,7 +16384,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16421,7 +16421,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129565990</v>
+        <v>129565895</v>
       </c>
       <c r="B148" t="n">
         <v>79070</v>
@@ -16456,10 +16456,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>443229</v>
+        <v>443005</v>
       </c>
       <c r="R148" t="n">
-        <v>6765319</v>
+        <v>6765037</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16528,7 +16528,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129566014</v>
+        <v>129565977</v>
       </c>
       <c r="B149" t="n">
         <v>79070</v>
@@ -16563,10 +16563,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>442813</v>
+        <v>443313</v>
       </c>
       <c r="R149" t="n">
-        <v>6764860</v>
+        <v>6765439</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16635,10 +16635,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129565913</v>
+        <v>129565752</v>
       </c>
       <c r="B150" t="n">
-        <v>79070</v>
+        <v>79689</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16646,21 +16646,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16670,10 +16670,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>442773</v>
+        <v>443004</v>
       </c>
       <c r="R150" t="n">
-        <v>6765264</v>
+        <v>6765163</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16705,7 +16705,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16742,10 +16742,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129565871</v>
+        <v>129565764</v>
       </c>
       <c r="B151" t="n">
-        <v>79070</v>
+        <v>79102</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16753,21 +16753,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16777,10 +16777,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>442690</v>
+        <v>443048</v>
       </c>
       <c r="R151" t="n">
-        <v>6764850</v>
+        <v>6765235</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16822,7 +16822,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16849,10 +16849,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129565895</v>
+        <v>129566026</v>
       </c>
       <c r="B152" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16860,21 +16860,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16884,10 +16884,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>443005</v>
+        <v>442684</v>
       </c>
       <c r="R152" t="n">
-        <v>6765037</v>
+        <v>6764861</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16956,10 +16956,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129565977</v>
+        <v>129566031</v>
       </c>
       <c r="B153" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16967,21 +16967,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16991,10 +16991,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>443313</v>
+        <v>443296</v>
       </c>
       <c r="R153" t="n">
-        <v>6765439</v>
+        <v>6765499</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17063,10 +17063,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129565752</v>
+        <v>129565780</v>
       </c>
       <c r="B154" t="n">
-        <v>79689</v>
+        <v>91581</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17074,21 +17074,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17098,10 +17098,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443004</v>
+        <v>443405</v>
       </c>
       <c r="R154" t="n">
-        <v>6765163</v>
+        <v>6765308</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17501,50 +17501,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129565799</v>
+        <v>129565809</v>
       </c>
       <c r="B158" t="n">
-        <v>57727</v>
+        <v>79137</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>637</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>443086</v>
+        <v>442863</v>
       </c>
       <c r="R158" t="n">
-        <v>6765106</v>
+        <v>6764893</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17576,7 +17571,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17586,7 +17581,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>20-tal bålar inom 10 m på fem olika granar.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18469,45 +18469,50 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129565809</v>
+        <v>129565799</v>
       </c>
       <c r="B167" t="n">
-        <v>79137</v>
+        <v>57727</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>637</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>442863</v>
+        <v>443086</v>
       </c>
       <c r="R167" t="n">
-        <v>6764893</v>
+        <v>6765106</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18539,7 +18544,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18549,12 +18554,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>20-tal bålar inom 10 m på fem olika granar.</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19569,32 +19569,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129566033</v>
+        <v>129565808</v>
       </c>
       <c r="B177" t="n">
-        <v>78736</v>
+        <v>97627</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19604,10 +19604,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>443144</v>
+        <v>443432</v>
       </c>
       <c r="R177" t="n">
-        <v>6765199</v>
+        <v>6765348</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19676,10 +19676,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129565927</v>
+        <v>129566033</v>
       </c>
       <c r="B178" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19687,21 +19687,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19711,10 +19711,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>442770</v>
+        <v>443144</v>
       </c>
       <c r="R178" t="n">
-        <v>6765225</v>
+        <v>6765199</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19783,7 +19783,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129565912</v>
+        <v>129565927</v>
       </c>
       <c r="B179" t="n">
         <v>79070</v>
@@ -19818,10 +19818,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>442776</v>
+        <v>442770</v>
       </c>
       <c r="R179" t="n">
-        <v>6765280</v>
+        <v>6765225</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19890,7 +19890,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129565972</v>
+        <v>129565912</v>
       </c>
       <c r="B180" t="n">
         <v>79070</v>
@@ -19925,10 +19925,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>443398</v>
+        <v>442776</v>
       </c>
       <c r="R180" t="n">
-        <v>6765434</v>
+        <v>6765280</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19960,7 +19960,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19997,7 +19997,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129565971</v>
+        <v>129565972</v>
       </c>
       <c r="B181" t="n">
         <v>79070</v>
@@ -20032,10 +20032,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>443406</v>
+        <v>443398</v>
       </c>
       <c r="R181" t="n">
-        <v>6765450</v>
+        <v>6765434</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20104,7 +20104,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129565984</v>
+        <v>129565971</v>
       </c>
       <c r="B182" t="n">
         <v>79070</v>
@@ -20139,10 +20139,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443338</v>
+        <v>443406</v>
       </c>
       <c r="R182" t="n">
-        <v>6765441</v>
+        <v>6765450</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20211,7 +20211,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129565879</v>
+        <v>129565984</v>
       </c>
       <c r="B183" t="n">
         <v>79070</v>
@@ -20246,10 +20246,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>442749</v>
+        <v>443338</v>
       </c>
       <c r="R183" t="n">
-        <v>6764886</v>
+        <v>6765441</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20318,7 +20318,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129565973</v>
+        <v>129565879</v>
       </c>
       <c r="B184" t="n">
         <v>79070</v>
@@ -20353,10 +20353,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443383</v>
+        <v>442749</v>
       </c>
       <c r="R184" t="n">
-        <v>6765415</v>
+        <v>6764886</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20388,7 +20388,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20398,7 +20398,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20425,7 +20425,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129566002</v>
+        <v>129565973</v>
       </c>
       <c r="B185" t="n">
         <v>79070</v>
@@ -20460,10 +20460,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>443134</v>
+        <v>443383</v>
       </c>
       <c r="R185" t="n">
-        <v>6765184</v>
+        <v>6765415</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20505,7 +20505,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20532,10 +20532,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129565806</v>
+        <v>129566002</v>
       </c>
       <c r="B186" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20543,39 +20543,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>443430</v>
+        <v>443134</v>
       </c>
       <c r="R186" t="n">
-        <v>6765200</v>
+        <v>6765184</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20607,7 +20602,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20617,7 +20612,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20644,10 +20639,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129565787</v>
+        <v>129565806</v>
       </c>
       <c r="B187" t="n">
-        <v>57890</v>
+        <v>57727</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20655,27 +20650,27 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="M187" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -20684,10 +20679,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>443283</v>
+        <v>443430</v>
       </c>
       <c r="R187" t="n">
-        <v>6765488</v>
+        <v>6765200</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20719,7 +20714,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20729,7 +20724,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20756,38 +20751,38 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129565833</v>
+        <v>129565787</v>
       </c>
       <c r="B188" t="n">
-        <v>8450</v>
+        <v>57890</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="M188" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -20796,10 +20791,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>442775</v>
+        <v>443283</v>
       </c>
       <c r="R188" t="n">
-        <v>6765271</v>
+        <v>6765488</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20831,7 +20826,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20841,7 +20836,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20868,10 +20863,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129565808</v>
+        <v>129565833</v>
       </c>
       <c r="B189" t="n">
-        <v>97627</v>
+        <v>8450</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20879,34 +20874,39 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>443432</v>
+        <v>442775</v>
       </c>
       <c r="R189" t="n">
-        <v>6765348</v>
+        <v>6765271</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20975,45 +20975,50 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129566024</v>
+        <v>129565826</v>
       </c>
       <c r="B190" t="n">
-        <v>78736</v>
+        <v>8450</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>443088</v>
+        <v>443073</v>
       </c>
       <c r="R190" t="n">
-        <v>6765114</v>
+        <v>6765287</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21045,7 +21050,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21055,12 +21060,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsyn</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129565963</v>
+        <v>129565771</v>
       </c>
       <c r="B191" t="n">
-        <v>79070</v>
+        <v>79660</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>443410</v>
+        <v>443081</v>
       </c>
       <c r="R191" t="n">
-        <v>6765453</v>
+        <v>6765117</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21194,10 +21194,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129566009</v>
+        <v>129566024</v>
       </c>
       <c r="B192" t="n">
-        <v>79070</v>
+        <v>78736</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21205,21 +21205,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21229,10 +21229,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>442846</v>
+        <v>443088</v>
       </c>
       <c r="R192" t="n">
-        <v>6764891</v>
+        <v>6765114</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21274,7 +21274,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsyn</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21301,7 +21306,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129566001</v>
+        <v>129565963</v>
       </c>
       <c r="B193" t="n">
         <v>79070</v>
@@ -21336,10 +21341,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443140</v>
+        <v>443410</v>
       </c>
       <c r="R193" t="n">
-        <v>6765218</v>
+        <v>6765453</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21371,7 +21376,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21381,7 +21386,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21408,7 +21413,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129565878</v>
+        <v>129566009</v>
       </c>
       <c r="B194" t="n">
         <v>79070</v>
@@ -21443,10 +21448,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>442745</v>
+        <v>442846</v>
       </c>
       <c r="R194" t="n">
-        <v>6764895</v>
+        <v>6764891</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21478,7 +21483,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21488,7 +21493,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21515,50 +21520,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129565826</v>
+        <v>129566001</v>
       </c>
       <c r="B195" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443073</v>
+        <v>443140</v>
       </c>
       <c r="R195" t="n">
-        <v>6765287</v>
+        <v>6765218</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21600,7 +21600,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21627,10 +21627,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129565771</v>
+        <v>129565878</v>
       </c>
       <c r="B196" t="n">
-        <v>79660</v>
+        <v>79070</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21638,21 +21638,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21662,10 +21662,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443081</v>
+        <v>442745</v>
       </c>
       <c r="R196" t="n">
-        <v>6765117</v>
+        <v>6764895</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21697,7 +21697,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21707,7 +21707,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22799,7 +22799,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129565807</v>
+        <v>129565803</v>
       </c>
       <c r="B207" t="n">
         <v>57727</v>
@@ -22830,7 +22830,7 @@
       <c r="I207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -22839,10 +22839,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>442850</v>
+        <v>443250</v>
       </c>
       <c r="R207" t="n">
-        <v>6764898</v>
+        <v>6765211</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22874,7 +22874,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22911,7 +22911,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129565803</v>
+        <v>129565807</v>
       </c>
       <c r="B208" t="n">
         <v>57727</v>
@@ -22942,7 +22942,7 @@
       <c r="I208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -22951,10 +22951,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>443250</v>
+        <v>442850</v>
       </c>
       <c r="R208" t="n">
-        <v>6765211</v>
+        <v>6764898</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22986,7 +22986,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD208" t="b">

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -7802,10 +7802,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129565847</v>
+        <v>129565978</v>
       </c>
       <c r="B68" t="n">
-        <v>81061</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7813,21 +7813,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443068</v>
+        <v>443303</v>
       </c>
       <c r="R68" t="n">
-        <v>6765019</v>
+        <v>6765447</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7909,10 +7909,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129565801</v>
+        <v>129565903</v>
       </c>
       <c r="B69" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7920,39 +7920,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443258</v>
+        <v>443051</v>
       </c>
       <c r="R69" t="n">
-        <v>6765343</v>
+        <v>6765229</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7984,7 +7979,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7994,7 +7989,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8021,7 +8016,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129565978</v>
+        <v>129565993</v>
       </c>
       <c r="B70" t="n">
         <v>79076</v>
@@ -8056,10 +8051,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443303</v>
+        <v>443126</v>
       </c>
       <c r="R70" t="n">
-        <v>6765447</v>
+        <v>6765359</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8091,7 +8086,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8101,7 +8096,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8128,7 +8123,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129565903</v>
+        <v>129566017</v>
       </c>
       <c r="B71" t="n">
         <v>79076</v>
@@ -8163,10 +8158,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443051</v>
+        <v>442707</v>
       </c>
       <c r="R71" t="n">
-        <v>6765229</v>
+        <v>6764791</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8198,7 +8193,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8208,7 +8203,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8235,7 +8230,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129565993</v>
+        <v>129565911</v>
       </c>
       <c r="B72" t="n">
         <v>79076</v>
@@ -8270,10 +8265,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443126</v>
+        <v>442817</v>
       </c>
       <c r="R72" t="n">
-        <v>6765359</v>
+        <v>6765276</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8305,7 +8300,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8315,7 +8310,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8342,7 +8337,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129566017</v>
+        <v>129565866</v>
       </c>
       <c r="B73" t="n">
         <v>79076</v>
@@ -8377,10 +8372,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>442707</v>
+        <v>442685</v>
       </c>
       <c r="R73" t="n">
-        <v>6764791</v>
+        <v>6764827</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8412,7 +8407,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8422,7 +8417,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8449,7 +8444,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129565911</v>
+        <v>129565994</v>
       </c>
       <c r="B74" t="n">
         <v>79076</v>
@@ -8484,10 +8479,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>442817</v>
+        <v>443076</v>
       </c>
       <c r="R74" t="n">
-        <v>6765276</v>
+        <v>6765364</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8519,7 +8514,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8529,7 +8524,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8556,10 +8551,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129565866</v>
+        <v>129565801</v>
       </c>
       <c r="B75" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8567,34 +8562,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>442685</v>
+        <v>443258</v>
       </c>
       <c r="R75" t="n">
-        <v>6764827</v>
+        <v>6765343</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8663,10 +8663,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129565994</v>
+        <v>129565847</v>
       </c>
       <c r="B76" t="n">
-        <v>79076</v>
+        <v>81061</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8674,21 +8674,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443076</v>
+        <v>443068</v>
       </c>
       <c r="R76" t="n">
-        <v>6765364</v>
+        <v>6765019</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9845,10 +9845,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129566027</v>
+        <v>129565849</v>
       </c>
       <c r="B87" t="n">
-        <v>78742</v>
+        <v>78833</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443043</v>
+        <v>443033</v>
       </c>
       <c r="R87" t="n">
-        <v>6765047</v>
+        <v>6765241</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9952,7 +9952,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129565902</v>
+        <v>129565932</v>
       </c>
       <c r="B88" t="n">
         <v>79076</v>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443010</v>
+        <v>442724</v>
       </c>
       <c r="R88" t="n">
-        <v>6765160</v>
+        <v>6765212</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10059,7 +10059,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129565976</v>
+        <v>129565966</v>
       </c>
       <c r="B89" t="n">
         <v>79076</v>
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443332</v>
+        <v>443432</v>
       </c>
       <c r="R89" t="n">
-        <v>6765403</v>
+        <v>6765347</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129565899</v>
+        <v>129566005</v>
       </c>
       <c r="B90" t="n">
         <v>79076</v>
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443088</v>
+        <v>443160</v>
       </c>
       <c r="R90" t="n">
-        <v>6765090</v>
+        <v>6765086</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10273,10 +10273,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129565849</v>
+        <v>129565956</v>
       </c>
       <c r="B91" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10284,21 +10284,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443033</v>
+        <v>443366</v>
       </c>
       <c r="R91" t="n">
-        <v>6765241</v>
+        <v>6765190</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10380,7 +10380,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129565932</v>
+        <v>129565961</v>
       </c>
       <c r="B92" t="n">
         <v>79076</v>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>442724</v>
+        <v>443405</v>
       </c>
       <c r="R92" t="n">
-        <v>6765212</v>
+        <v>6765244</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10487,45 +10487,52 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129565966</v>
+        <v>129565784</v>
       </c>
       <c r="B93" t="n">
-        <v>79076</v>
+        <v>56926</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443432</v>
+        <v>443093</v>
       </c>
       <c r="R93" t="n">
-        <v>6765347</v>
+        <v>6765290</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10564,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10574,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10594,10 +10601,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129566005</v>
+        <v>129565844</v>
       </c>
       <c r="B94" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10605,21 +10612,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10629,10 +10636,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443160</v>
+        <v>443017</v>
       </c>
       <c r="R94" t="n">
-        <v>6765086</v>
+        <v>6765118</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10671,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10681,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,10 +10708,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129565956</v>
+        <v>129566027</v>
       </c>
       <c r="B95" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10712,21 +10719,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10736,10 +10743,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443366</v>
+        <v>443043</v>
       </c>
       <c r="R95" t="n">
-        <v>6765190</v>
+        <v>6765047</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10771,7 +10778,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10781,7 +10788,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10808,7 +10815,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129565961</v>
+        <v>129565902</v>
       </c>
       <c r="B96" t="n">
         <v>79076</v>
@@ -10843,10 +10850,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443405</v>
+        <v>443010</v>
       </c>
       <c r="R96" t="n">
-        <v>6765244</v>
+        <v>6765160</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10878,7 +10885,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10888,7 +10895,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10915,52 +10922,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129565784</v>
+        <v>129565976</v>
       </c>
       <c r="B97" t="n">
-        <v>56926</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443093</v>
+        <v>443332</v>
       </c>
       <c r="R97" t="n">
-        <v>6765290</v>
+        <v>6765403</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11029,10 +11029,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129565844</v>
+        <v>129565899</v>
       </c>
       <c r="B98" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11040,21 +11040,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11064,10 +11064,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443017</v>
+        <v>443088</v>
       </c>
       <c r="R98" t="n">
-        <v>6765118</v>
+        <v>6765090</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11136,10 +11136,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129565868</v>
+        <v>129565768</v>
       </c>
       <c r="B99" t="n">
-        <v>79076</v>
+        <v>79108</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11147,21 +11147,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>442689</v>
+        <v>442990</v>
       </c>
       <c r="R99" t="n">
-        <v>6764832</v>
+        <v>6765105</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11243,7 +11243,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129565749</v>
+        <v>129565753</v>
       </c>
       <c r="B100" t="n">
         <v>79695</v>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>442782</v>
+        <v>443271</v>
       </c>
       <c r="R100" t="n">
-        <v>6765271</v>
+        <v>6765126</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11323,12 +11323,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsyn</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11355,10 +11350,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129565768</v>
+        <v>129565760</v>
       </c>
       <c r="B101" t="n">
-        <v>79108</v>
+        <v>83045</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11366,21 +11361,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11390,10 +11385,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>442990</v>
+        <v>442682</v>
       </c>
       <c r="R101" t="n">
-        <v>6765105</v>
+        <v>6764828</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,7 +11420,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11435,7 +11430,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11462,10 +11457,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129565753</v>
+        <v>129565906</v>
       </c>
       <c r="B102" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11473,21 +11468,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11497,10 +11492,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443271</v>
+        <v>442852</v>
       </c>
       <c r="R102" t="n">
-        <v>6765126</v>
+        <v>6765301</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11532,7 +11527,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11542,7 +11537,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11569,10 +11564,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129565760</v>
+        <v>129565870</v>
       </c>
       <c r="B103" t="n">
-        <v>83045</v>
+        <v>79076</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11580,21 +11575,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11604,10 +11599,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>442682</v>
+        <v>442695</v>
       </c>
       <c r="R103" t="n">
-        <v>6764828</v>
+        <v>6764852</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11639,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11649,7 +11644,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11676,7 +11671,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129565906</v>
+        <v>129565874</v>
       </c>
       <c r="B104" t="n">
         <v>79076</v>
@@ -11711,10 +11706,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>442852</v>
+        <v>442679</v>
       </c>
       <c r="R104" t="n">
-        <v>6765301</v>
+        <v>6764871</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11746,7 +11741,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11756,7 +11751,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11783,7 +11778,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129565870</v>
+        <v>129565868</v>
       </c>
       <c r="B105" t="n">
         <v>79076</v>
@@ -11818,10 +11813,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>442695</v>
+        <v>442689</v>
       </c>
       <c r="R105" t="n">
-        <v>6764852</v>
+        <v>6764832</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11853,7 +11848,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11863,7 +11858,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11890,10 +11885,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129565874</v>
+        <v>129565749</v>
       </c>
       <c r="B106" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11901,21 +11896,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11925,10 +11920,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>442679</v>
+        <v>442782</v>
       </c>
       <c r="R106" t="n">
-        <v>6764871</v>
+        <v>6765271</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11960,7 +11955,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11970,7 +11965,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsyn</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11997,10 +11997,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129566023</v>
+        <v>129565876</v>
       </c>
       <c r="B107" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12008,21 +12008,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12032,10 +12032,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443207</v>
+        <v>442690</v>
       </c>
       <c r="R107" t="n">
-        <v>6765081</v>
+        <v>6764884</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12077,12 +12077,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12109,7 +12104,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129565876</v>
+        <v>129565960</v>
       </c>
       <c r="B108" t="n">
         <v>79076</v>
@@ -12144,10 +12139,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>442690</v>
+        <v>443403</v>
       </c>
       <c r="R108" t="n">
-        <v>6764884</v>
+        <v>6765238</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12179,7 +12174,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12189,7 +12184,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12216,45 +12211,50 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129565960</v>
+        <v>129565821</v>
       </c>
       <c r="B109" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443403</v>
+        <v>443034</v>
       </c>
       <c r="R109" t="n">
-        <v>6765238</v>
+        <v>6765053</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12323,10 +12323,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129565751</v>
+        <v>129566023</v>
       </c>
       <c r="B110" t="n">
-        <v>79695</v>
+        <v>78742</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12334,21 +12334,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12358,10 +12358,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>442690</v>
+        <v>443207</v>
       </c>
       <c r="R110" t="n">
-        <v>6764886</v>
+        <v>6765081</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12403,7 +12403,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12430,7 +12435,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129565750</v>
+        <v>129565751</v>
       </c>
       <c r="B111" t="n">
         <v>79695</v>
@@ -12465,10 +12470,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443145</v>
+        <v>442690</v>
       </c>
       <c r="R111" t="n">
-        <v>6765323</v>
+        <v>6764886</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12500,7 +12505,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12510,12 +12515,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På enda silverlågan med hänsyn i hela anmälan</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12542,10 +12542,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129565891</v>
+        <v>129565750</v>
       </c>
       <c r="B112" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12553,21 +12553,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12577,10 +12577,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>442829</v>
+        <v>443145</v>
       </c>
       <c r="R112" t="n">
-        <v>6764901</v>
+        <v>6765323</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12612,7 +12612,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12622,7 +12622,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På enda silverlågan med hänsyn i hela anmälan</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12649,50 +12654,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129565821</v>
+        <v>129565891</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443034</v>
+        <v>442829</v>
       </c>
       <c r="R113" t="n">
-        <v>6765053</v>
+        <v>6764901</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12761,10 +12761,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129566030</v>
+        <v>129565852</v>
       </c>
       <c r="B114" t="n">
-        <v>78742</v>
+        <v>78833</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12772,21 +12772,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443283</v>
+        <v>443321</v>
       </c>
       <c r="R114" t="n">
-        <v>6765488</v>
+        <v>6765425</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12868,10 +12868,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129565756</v>
+        <v>129565762</v>
       </c>
       <c r="B115" t="n">
-        <v>79695</v>
+        <v>83045</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12879,21 +12879,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12903,10 +12903,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443179</v>
+        <v>442861</v>
       </c>
       <c r="R115" t="n">
-        <v>6765294</v>
+        <v>6764908</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12975,10 +12975,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129565800</v>
+        <v>129565850</v>
       </c>
       <c r="B116" t="n">
-        <v>57733</v>
+        <v>78833</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12986,39 +12986,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443020</v>
+        <v>443017</v>
       </c>
       <c r="R116" t="n">
-        <v>6764999</v>
+        <v>6765114</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13050,7 +13045,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13060,7 +13055,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13087,10 +13082,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129565775</v>
+        <v>129565755</v>
       </c>
       <c r="B117" t="n">
-        <v>79666</v>
+        <v>79695</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13098,21 +13093,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13122,10 +13117,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443250</v>
+        <v>443282</v>
       </c>
       <c r="R117" t="n">
-        <v>6765209</v>
+        <v>6765487</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13157,7 +13152,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13167,7 +13162,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13194,10 +13189,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129565852</v>
+        <v>129565892</v>
       </c>
       <c r="B118" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13205,21 +13200,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13229,10 +13224,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443321</v>
+        <v>442831</v>
       </c>
       <c r="R118" t="n">
-        <v>6765425</v>
+        <v>6764873</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13264,7 +13259,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13274,7 +13269,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13301,10 +13296,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129565762</v>
+        <v>129565926</v>
       </c>
       <c r="B119" t="n">
-        <v>83045</v>
+        <v>79076</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13312,21 +13307,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13336,10 +13331,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>442861</v>
+        <v>442748</v>
       </c>
       <c r="R119" t="n">
-        <v>6764908</v>
+        <v>6765234</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13371,7 +13366,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13381,7 +13376,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13408,10 +13403,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129565850</v>
+        <v>129566008</v>
       </c>
       <c r="B120" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13419,21 +13414,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13443,10 +13438,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443017</v>
+        <v>442968</v>
       </c>
       <c r="R120" t="n">
-        <v>6765114</v>
+        <v>6765088</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13478,7 +13473,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13488,7 +13483,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13515,10 +13510,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129565755</v>
+        <v>129565949</v>
       </c>
       <c r="B121" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13526,21 +13521,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13550,10 +13545,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443282</v>
+        <v>443110</v>
       </c>
       <c r="R121" t="n">
-        <v>6765487</v>
+        <v>6765023</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13585,7 +13580,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13595,7 +13590,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13622,10 +13617,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129565992</v>
+        <v>129565800</v>
       </c>
       <c r="B122" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13633,34 +13628,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443143</v>
+        <v>443020</v>
       </c>
       <c r="R122" t="n">
-        <v>6765322</v>
+        <v>6764999</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13729,10 +13729,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129565892</v>
+        <v>129566030</v>
       </c>
       <c r="B123" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13740,21 +13740,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13764,10 +13764,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>442831</v>
+        <v>443283</v>
       </c>
       <c r="R123" t="n">
-        <v>6764873</v>
+        <v>6765488</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13836,7 +13836,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129565926</v>
+        <v>129565992</v>
       </c>
       <c r="B124" t="n">
         <v>79076</v>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>442748</v>
+        <v>443143</v>
       </c>
       <c r="R124" t="n">
-        <v>6765234</v>
+        <v>6765322</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13943,10 +13943,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129566008</v>
+        <v>129565756</v>
       </c>
       <c r="B125" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>442968</v>
+        <v>443179</v>
       </c>
       <c r="R125" t="n">
-        <v>6765088</v>
+        <v>6765294</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14050,10 +14050,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129565949</v>
+        <v>129565775</v>
       </c>
       <c r="B126" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14061,21 +14061,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14085,10 +14085,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443110</v>
+        <v>443250</v>
       </c>
       <c r="R126" t="n">
-        <v>6765023</v>
+        <v>6765209</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14157,10 +14157,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129566032</v>
+        <v>129566004</v>
       </c>
       <c r="B127" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14168,21 +14168,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14192,10 +14192,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443236</v>
+        <v>443246</v>
       </c>
       <c r="R127" t="n">
-        <v>6765316</v>
+        <v>6765145</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14227,7 +14227,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14264,10 +14264,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129565766</v>
+        <v>129565959</v>
       </c>
       <c r="B128" t="n">
-        <v>79108</v>
+        <v>79076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14275,21 +14275,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14299,10 +14299,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443305</v>
+        <v>443414</v>
       </c>
       <c r="R128" t="n">
-        <v>6765463</v>
+        <v>6765221</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14371,10 +14371,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129566025</v>
+        <v>129565985</v>
       </c>
       <c r="B129" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14382,21 +14382,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14406,10 +14406,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>442693</v>
+        <v>443324</v>
       </c>
       <c r="R129" t="n">
-        <v>6764827</v>
+        <v>6765398</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14478,50 +14478,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129565840</v>
+        <v>129565925</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443118</v>
+        <v>442732</v>
       </c>
       <c r="R130" t="n">
-        <v>6765278</v>
+        <v>6765239</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14553,7 +14548,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14563,7 +14558,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14590,7 +14585,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129566004</v>
+        <v>129565951</v>
       </c>
       <c r="B131" t="n">
         <v>79076</v>
@@ -14625,10 +14620,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443246</v>
+        <v>443224</v>
       </c>
       <c r="R131" t="n">
-        <v>6765145</v>
+        <v>6765097</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14660,7 +14655,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14670,7 +14665,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14697,7 +14692,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129565959</v>
+        <v>129565920</v>
       </c>
       <c r="B132" t="n">
         <v>79076</v>
@@ -14732,10 +14727,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443414</v>
+        <v>442734</v>
       </c>
       <c r="R132" t="n">
-        <v>6765221</v>
+        <v>6765264</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14767,7 +14762,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14777,7 +14772,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14804,45 +14799,50 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129565985</v>
+        <v>129565840</v>
       </c>
       <c r="B133" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443324</v>
+        <v>443118</v>
       </c>
       <c r="R133" t="n">
-        <v>6765398</v>
+        <v>6765278</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14911,10 +14911,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129565925</v>
+        <v>129566032</v>
       </c>
       <c r="B134" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14922,21 +14922,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14946,10 +14946,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>442732</v>
+        <v>443236</v>
       </c>
       <c r="R134" t="n">
-        <v>6765239</v>
+        <v>6765316</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14981,7 +14981,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15018,10 +15018,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129565951</v>
+        <v>129565766</v>
       </c>
       <c r="B135" t="n">
-        <v>79076</v>
+        <v>79108</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15029,21 +15029,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15053,10 +15053,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>443224</v>
+        <v>443305</v>
       </c>
       <c r="R135" t="n">
-        <v>6765097</v>
+        <v>6765463</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15125,10 +15125,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129565920</v>
+        <v>129566025</v>
       </c>
       <c r="B136" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15136,21 +15136,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15160,10 +15160,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>442734</v>
+        <v>442693</v>
       </c>
       <c r="R136" t="n">
-        <v>6765264</v>
+        <v>6764827</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15346,32 +15346,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129565752</v>
+        <v>129565769</v>
       </c>
       <c r="B138" t="n">
-        <v>79695</v>
+        <v>91552</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15381,10 +15381,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>443004</v>
+        <v>443362</v>
       </c>
       <c r="R138" t="n">
-        <v>6765163</v>
+        <v>6765377</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15453,10 +15453,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129565901</v>
+        <v>129565764</v>
       </c>
       <c r="B139" t="n">
-        <v>79076</v>
+        <v>79108</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15464,21 +15464,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15488,10 +15488,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>443054</v>
+        <v>443048</v>
       </c>
       <c r="R139" t="n">
-        <v>6765138</v>
+        <v>6765235</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15523,7 +15523,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15533,7 +15533,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15560,10 +15560,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129565871</v>
+        <v>129566026</v>
       </c>
       <c r="B140" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15571,21 +15571,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15595,10 +15595,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>442690</v>
+        <v>442684</v>
       </c>
       <c r="R140" t="n">
-        <v>6764850</v>
+        <v>6764861</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15630,7 +15630,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15667,10 +15667,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129565780</v>
+        <v>129566031</v>
       </c>
       <c r="B141" t="n">
-        <v>91588</v>
+        <v>78742</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15678,21 +15678,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15702,10 +15702,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443405</v>
+        <v>443296</v>
       </c>
       <c r="R141" t="n">
-        <v>6765308</v>
+        <v>6765499</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15774,10 +15774,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129565764</v>
+        <v>129565901</v>
       </c>
       <c r="B142" t="n">
-        <v>79108</v>
+        <v>79076</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15785,21 +15785,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15809,10 +15809,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>443048</v>
+        <v>443054</v>
       </c>
       <c r="R142" t="n">
-        <v>6765235</v>
+        <v>6765138</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15881,10 +15881,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129566026</v>
+        <v>129565871</v>
       </c>
       <c r="B143" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15892,21 +15892,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15916,10 +15916,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>442684</v>
+        <v>442690</v>
       </c>
       <c r="R143" t="n">
-        <v>6764861</v>
+        <v>6764850</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15988,10 +15988,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129566031</v>
+        <v>129565862</v>
       </c>
       <c r="B144" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15999,34 +15999,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>443296</v>
+        <v>442822</v>
       </c>
       <c r="R144" t="n">
-        <v>6765499</v>
+        <v>6764864</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16058,7 +16063,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16068,7 +16073,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16095,7 +16100,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129565862</v>
+        <v>129565962</v>
       </c>
       <c r="B145" t="n">
         <v>79076</v>
@@ -16124,21 +16129,16 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>442822</v>
+        <v>443405</v>
       </c>
       <c r="R145" t="n">
-        <v>6764864</v>
+        <v>6765256</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16207,7 +16207,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129565962</v>
+        <v>129565991</v>
       </c>
       <c r="B146" t="n">
         <v>79076</v>
@@ -16242,10 +16242,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>443405</v>
+        <v>443155</v>
       </c>
       <c r="R146" t="n">
-        <v>6765256</v>
+        <v>6765323</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16314,7 +16314,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129565991</v>
+        <v>129565893</v>
       </c>
       <c r="B147" t="n">
         <v>79076</v>
@@ -16349,10 +16349,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>443155</v>
+        <v>442835</v>
       </c>
       <c r="R147" t="n">
-        <v>6765323</v>
+        <v>6764863</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16384,7 +16384,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16421,7 +16421,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129565893</v>
+        <v>129565990</v>
       </c>
       <c r="B148" t="n">
         <v>79076</v>
@@ -16456,10 +16456,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>442835</v>
+        <v>443229</v>
       </c>
       <c r="R148" t="n">
-        <v>6764863</v>
+        <v>6765319</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16528,7 +16528,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129565990</v>
+        <v>129566014</v>
       </c>
       <c r="B149" t="n">
         <v>79076</v>
@@ -16563,10 +16563,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>443229</v>
+        <v>442813</v>
       </c>
       <c r="R149" t="n">
-        <v>6765319</v>
+        <v>6764860</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16635,7 +16635,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129566014</v>
+        <v>129565913</v>
       </c>
       <c r="B150" t="n">
         <v>79076</v>
@@ -16670,10 +16670,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>442813</v>
+        <v>442773</v>
       </c>
       <c r="R150" t="n">
-        <v>6764860</v>
+        <v>6765264</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16705,7 +16705,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16742,7 +16742,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129565913</v>
+        <v>129565895</v>
       </c>
       <c r="B151" t="n">
         <v>79076</v>
@@ -16777,10 +16777,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>442773</v>
+        <v>443005</v>
       </c>
       <c r="R151" t="n">
-        <v>6765264</v>
+        <v>6765037</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16822,7 +16822,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16849,7 +16849,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129565895</v>
+        <v>129565977</v>
       </c>
       <c r="B152" t="n">
         <v>79076</v>
@@ -16884,10 +16884,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>443005</v>
+        <v>443313</v>
       </c>
       <c r="R152" t="n">
-        <v>6765037</v>
+        <v>6765439</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16956,10 +16956,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129565977</v>
+        <v>129565770</v>
       </c>
       <c r="B153" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16967,21 +16967,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16991,10 +16991,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>443313</v>
+        <v>443068</v>
       </c>
       <c r="R153" t="n">
-        <v>6765439</v>
+        <v>6765020</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17063,32 +17063,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129565769</v>
+        <v>129565780</v>
       </c>
       <c r="B154" t="n">
-        <v>91552</v>
+        <v>91588</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17098,10 +17098,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443362</v>
+        <v>443405</v>
       </c>
       <c r="R154" t="n">
-        <v>6765377</v>
+        <v>6765308</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17170,10 +17170,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129565770</v>
+        <v>129565752</v>
       </c>
       <c r="B155" t="n">
-        <v>79666</v>
+        <v>79695</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17181,21 +17181,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17205,10 +17205,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443068</v>
+        <v>443004</v>
       </c>
       <c r="R155" t="n">
-        <v>6765020</v>
+        <v>6765163</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18693,45 +18693,50 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129565968</v>
+        <v>129565829</v>
       </c>
       <c r="B169" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>443400</v>
+        <v>443008</v>
       </c>
       <c r="R169" t="n">
-        <v>6765375</v>
+        <v>6765122</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18763,7 +18768,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18773,7 +18778,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18800,45 +18805,50 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129565929</v>
+        <v>129565822</v>
       </c>
       <c r="B170" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>442823</v>
+        <v>443092</v>
       </c>
       <c r="R170" t="n">
-        <v>6765181</v>
+        <v>6765061</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18870,7 +18880,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18880,7 +18890,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18907,45 +18917,50 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129566012</v>
+        <v>129565830</v>
       </c>
       <c r="B171" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>442827</v>
+        <v>443009</v>
       </c>
       <c r="R171" t="n">
-        <v>6764880</v>
+        <v>6765160</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18977,7 +18992,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18987,7 +19002,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19014,45 +19029,50 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129565910</v>
+        <v>129565828</v>
       </c>
       <c r="B172" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>442825</v>
+        <v>443021</v>
       </c>
       <c r="R172" t="n">
-        <v>6765266</v>
+        <v>6765053</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19084,7 +19104,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19094,7 +19114,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19121,50 +19141,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129565829</v>
+        <v>129565968</v>
       </c>
       <c r="B173" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443008</v>
+        <v>443400</v>
       </c>
       <c r="R173" t="n">
-        <v>6765122</v>
+        <v>6765375</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19196,7 +19211,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19206,7 +19221,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19233,50 +19248,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129565822</v>
+        <v>129565929</v>
       </c>
       <c r="B174" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443092</v>
+        <v>442823</v>
       </c>
       <c r="R174" t="n">
-        <v>6765061</v>
+        <v>6765181</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19308,7 +19318,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19318,7 +19328,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19345,50 +19355,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129565830</v>
+        <v>129566012</v>
       </c>
       <c r="B175" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>443009</v>
+        <v>442827</v>
       </c>
       <c r="R175" t="n">
-        <v>6765160</v>
+        <v>6764880</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19420,7 +19425,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19430,7 +19435,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19457,50 +19462,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129565828</v>
+        <v>129565910</v>
       </c>
       <c r="B176" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>443021</v>
+        <v>442825</v>
       </c>
       <c r="R176" t="n">
-        <v>6765053</v>
+        <v>6765266</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19569,7 +19569,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129565927</v>
+        <v>129565972</v>
       </c>
       <c r="B177" t="n">
         <v>79076</v>
@@ -19604,10 +19604,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>442770</v>
+        <v>443398</v>
       </c>
       <c r="R177" t="n">
-        <v>6765225</v>
+        <v>6765434</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19676,10 +19676,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129565912</v>
+        <v>129565787</v>
       </c>
       <c r="B178" t="n">
-        <v>79076</v>
+        <v>57896</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19687,34 +19687,39 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>442776</v>
+        <v>443283</v>
       </c>
       <c r="R178" t="n">
-        <v>6765280</v>
+        <v>6765488</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19746,7 +19751,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19756,7 +19761,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19783,45 +19788,50 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129565971</v>
+        <v>129565833</v>
       </c>
       <c r="B179" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>443406</v>
+        <v>442775</v>
       </c>
       <c r="R179" t="n">
-        <v>6765450</v>
+        <v>6765271</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19853,7 +19863,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19863,7 +19873,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19890,32 +19900,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129565984</v>
+        <v>129565808</v>
       </c>
       <c r="B180" t="n">
-        <v>79076</v>
+        <v>97640</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19925,10 +19935,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>443338</v>
+        <v>443432</v>
       </c>
       <c r="R180" t="n">
-        <v>6765441</v>
+        <v>6765348</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19960,7 +19970,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19970,7 +19980,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19997,10 +20007,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129565879</v>
+        <v>129566033</v>
       </c>
       <c r="B181" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20008,21 +20018,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20032,10 +20042,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>442749</v>
+        <v>443144</v>
       </c>
       <c r="R181" t="n">
-        <v>6764886</v>
+        <v>6765199</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20067,7 +20077,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20077,7 +20087,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20104,7 +20114,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129565973</v>
+        <v>129565927</v>
       </c>
       <c r="B182" t="n">
         <v>79076</v>
@@ -20139,10 +20149,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443383</v>
+        <v>442770</v>
       </c>
       <c r="R182" t="n">
-        <v>6765415</v>
+        <v>6765225</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20174,7 +20184,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20184,7 +20194,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20211,7 +20221,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129566002</v>
+        <v>129565912</v>
       </c>
       <c r="B183" t="n">
         <v>79076</v>
@@ -20246,10 +20256,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>443134</v>
+        <v>442776</v>
       </c>
       <c r="R183" t="n">
-        <v>6765184</v>
+        <v>6765280</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20281,7 +20291,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20291,7 +20301,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20318,10 +20328,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129565787</v>
+        <v>129565971</v>
       </c>
       <c r="B184" t="n">
-        <v>57896</v>
+        <v>79076</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20329,39 +20339,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443283</v>
+        <v>443406</v>
       </c>
       <c r="R184" t="n">
-        <v>6765488</v>
+        <v>6765450</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20393,7 +20398,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20403,7 +20408,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20430,50 +20435,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129565833</v>
+        <v>129565984</v>
       </c>
       <c r="B185" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>442775</v>
+        <v>443338</v>
       </c>
       <c r="R185" t="n">
-        <v>6765271</v>
+        <v>6765441</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20515,7 +20515,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20542,32 +20542,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129565808</v>
+        <v>129565879</v>
       </c>
       <c r="B186" t="n">
-        <v>97640</v>
+        <v>79076</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20577,10 +20577,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>443432</v>
+        <v>442749</v>
       </c>
       <c r="R186" t="n">
-        <v>6765348</v>
+        <v>6764886</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20612,7 +20612,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20649,10 +20649,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129566033</v>
+        <v>129565973</v>
       </c>
       <c r="B187" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20660,21 +20660,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>443144</v>
+        <v>443383</v>
       </c>
       <c r="R187" t="n">
-        <v>6765199</v>
+        <v>6765415</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20719,7 +20719,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20729,7 +20729,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20756,7 +20756,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129565972</v>
+        <v>129566002</v>
       </c>
       <c r="B188" t="n">
         <v>79076</v>
@@ -20791,10 +20791,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>443398</v>
+        <v>443134</v>
       </c>
       <c r="R188" t="n">
-        <v>6765434</v>
+        <v>6765184</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20826,7 +20826,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20975,10 +20975,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129565771</v>
+        <v>129566024</v>
       </c>
       <c r="B190" t="n">
-        <v>79666</v>
+        <v>78742</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20986,21 +20986,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21010,10 +21010,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>443081</v>
+        <v>443088</v>
       </c>
       <c r="R190" t="n">
-        <v>6765117</v>
+        <v>6765114</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21055,7 +21055,12 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsyn</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21082,50 +21087,45 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129565826</v>
+        <v>129565963</v>
       </c>
       <c r="B191" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>443073</v>
+        <v>443410</v>
       </c>
       <c r="R191" t="n">
-        <v>6765287</v>
+        <v>6765453</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21194,10 +21194,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129565846</v>
+        <v>129565878</v>
       </c>
       <c r="B192" t="n">
-        <v>92007</v>
+        <v>79076</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21205,16 +21205,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21224,10 +21229,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>443405</v>
+        <v>442745</v>
       </c>
       <c r="R192" t="n">
-        <v>6765306</v>
+        <v>6764895</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21259,7 +21264,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21269,7 +21274,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21296,45 +21301,50 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129566024</v>
+        <v>129565826</v>
       </c>
       <c r="B193" t="n">
-        <v>78742</v>
+        <v>8450</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443088</v>
+        <v>443073</v>
       </c>
       <c r="R193" t="n">
-        <v>6765114</v>
+        <v>6765287</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21366,7 +21376,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21376,12 +21386,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsyn</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21408,7 +21413,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129565963</v>
+        <v>129566009</v>
       </c>
       <c r="B194" t="n">
         <v>79076</v>
@@ -21443,10 +21448,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>443410</v>
+        <v>442846</v>
       </c>
       <c r="R194" t="n">
-        <v>6765453</v>
+        <v>6764891</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21478,7 +21483,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21488,7 +21493,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21515,7 +21520,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129565878</v>
+        <v>129566001</v>
       </c>
       <c r="B195" t="n">
         <v>79076</v>
@@ -21550,10 +21555,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>442745</v>
+        <v>443140</v>
       </c>
       <c r="R195" t="n">
-        <v>6764895</v>
+        <v>6765218</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21585,7 +21590,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21595,7 +21600,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21622,10 +21627,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129566009</v>
+        <v>129565771</v>
       </c>
       <c r="B196" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21633,21 +21638,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21657,10 +21662,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>442846</v>
+        <v>443081</v>
       </c>
       <c r="R196" t="n">
-        <v>6764891</v>
+        <v>6765117</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21692,7 +21697,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21702,7 +21707,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21729,10 +21734,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129566001</v>
+        <v>129565846</v>
       </c>
       <c r="B197" t="n">
-        <v>79076</v>
+        <v>92007</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21740,21 +21745,16 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21764,10 +21764,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>443140</v>
+        <v>443405</v>
       </c>
       <c r="R197" t="n">
-        <v>6765218</v>
+        <v>6765306</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21809,7 +21809,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21836,7 +21836,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129565919</v>
+        <v>129565981</v>
       </c>
       <c r="B198" t="n">
         <v>79076</v>
@@ -21871,10 +21871,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>442733</v>
+        <v>443294</v>
       </c>
       <c r="R198" t="n">
-        <v>6765274</v>
+        <v>6765505</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21916,7 +21916,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21943,7 +21943,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129565907</v>
+        <v>129565894</v>
       </c>
       <c r="B199" t="n">
         <v>79076</v>
@@ -21978,10 +21978,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>442863</v>
+        <v>442973</v>
       </c>
       <c r="R199" t="n">
-        <v>6765287</v>
+        <v>6764957</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22013,7 +22013,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22023,7 +22023,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22050,10 +22050,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129565803</v>
+        <v>129565817</v>
       </c>
       <c r="B200" t="n">
-        <v>57733</v>
+        <v>92908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22061,39 +22061,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>443250</v>
+        <v>442767</v>
       </c>
       <c r="R200" t="n">
-        <v>6765211</v>
+        <v>6765229</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22125,7 +22120,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22135,7 +22130,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22162,10 +22157,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129565807</v>
+        <v>129565763</v>
       </c>
       <c r="B201" t="n">
-        <v>57733</v>
+        <v>79108</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22173,39 +22168,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>442850</v>
+        <v>443051</v>
       </c>
       <c r="R201" t="n">
-        <v>6764898</v>
+        <v>6765229</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22237,7 +22227,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22247,7 +22237,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22274,10 +22264,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129565763</v>
+        <v>129565955</v>
       </c>
       <c r="B202" t="n">
-        <v>79108</v>
+        <v>79076</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22285,21 +22275,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22309,10 +22299,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>443051</v>
+        <v>443351</v>
       </c>
       <c r="R202" t="n">
-        <v>6765229</v>
+        <v>6765163</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22344,7 +22334,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22354,7 +22344,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22381,7 +22371,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129565981</v>
+        <v>129565950</v>
       </c>
       <c r="B203" t="n">
         <v>79076</v>
@@ -22416,10 +22406,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>443294</v>
+        <v>443156</v>
       </c>
       <c r="R203" t="n">
-        <v>6765505</v>
+        <v>6765060</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22451,7 +22441,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22461,7 +22451,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22488,7 +22478,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129565894</v>
+        <v>129565919</v>
       </c>
       <c r="B204" t="n">
         <v>79076</v>
@@ -22523,10 +22513,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>442973</v>
+        <v>442733</v>
       </c>
       <c r="R204" t="n">
-        <v>6764957</v>
+        <v>6765274</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22558,7 +22548,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22568,7 +22558,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22595,10 +22585,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129565817</v>
+        <v>129565908</v>
       </c>
       <c r="B205" t="n">
-        <v>92908</v>
+        <v>79076</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22606,21 +22596,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22630,10 +22620,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>442767</v>
+        <v>442859</v>
       </c>
       <c r="R205" t="n">
-        <v>6765229</v>
+        <v>6765277</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22665,7 +22655,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22675,7 +22665,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22702,7 +22692,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129565955</v>
+        <v>129565907</v>
       </c>
       <c r="B206" t="n">
         <v>79076</v>
@@ -22737,10 +22727,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>443351</v>
+        <v>442863</v>
       </c>
       <c r="R206" t="n">
-        <v>6765163</v>
+        <v>6765287</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22772,7 +22762,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22782,7 +22772,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22809,10 +22799,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129565950</v>
+        <v>129565803</v>
       </c>
       <c r="B207" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22820,34 +22810,39 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>443156</v>
+        <v>443250</v>
       </c>
       <c r="R207" t="n">
-        <v>6765060</v>
+        <v>6765211</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22879,7 +22874,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22889,7 +22884,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22916,10 +22911,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129565908</v>
+        <v>129565807</v>
       </c>
       <c r="B208" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22927,34 +22922,39 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>442859</v>
+        <v>442850</v>
       </c>
       <c r="R208" t="n">
-        <v>6765277</v>
+        <v>6764898</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22986,7 +22986,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23130,10 +23130,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129565916</v>
+        <v>129565798</v>
       </c>
       <c r="B210" t="n">
-        <v>79076</v>
+        <v>91539</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23141,21 +23141,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23165,10 +23165,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>442750</v>
+        <v>442855</v>
       </c>
       <c r="R210" t="n">
-        <v>6765268</v>
+        <v>6764903</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23200,7 +23200,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23237,10 +23237,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129565924</v>
+        <v>129565774</v>
       </c>
       <c r="B211" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23248,21 +23248,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23272,10 +23272,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>442729</v>
+        <v>443296</v>
       </c>
       <c r="R211" t="n">
-        <v>6765242</v>
+        <v>6765472</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23307,7 +23307,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23344,7 +23344,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129565970</v>
+        <v>129565916</v>
       </c>
       <c r="B212" t="n">
         <v>79076</v>
@@ -23379,10 +23379,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>443416</v>
+        <v>442750</v>
       </c>
       <c r="R212" t="n">
-        <v>6765453</v>
+        <v>6765268</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23451,10 +23451,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129565774</v>
+        <v>129565924</v>
       </c>
       <c r="B213" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23462,21 +23462,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23486,10 +23486,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>443296</v>
+        <v>442729</v>
       </c>
       <c r="R213" t="n">
-        <v>6765472</v>
+        <v>6765242</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23558,10 +23558,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129565798</v>
+        <v>129565970</v>
       </c>
       <c r="B214" t="n">
-        <v>91539</v>
+        <v>79076</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23569,21 +23569,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23593,10 +23593,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>442855</v>
+        <v>443416</v>
       </c>
       <c r="R214" t="n">
-        <v>6764903</v>
+        <v>6765453</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23628,7 +23628,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD214" t="b">

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -1970,45 +1970,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129565754</v>
+        <v>129565834</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443335</v>
+        <v>442810</v>
       </c>
       <c r="R14" t="n">
-        <v>6765160</v>
+        <v>6765170</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,7 +2045,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2050,7 +2055,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2826,50 +2831,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129565834</v>
+        <v>129565773</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442810</v>
+        <v>443322</v>
       </c>
       <c r="R22" t="n">
-        <v>6765170</v>
+        <v>6765427</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,10 +2938,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129565773</v>
+        <v>129565754</v>
       </c>
       <c r="B23" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2949,21 +2949,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443322</v>
+        <v>443335</v>
       </c>
       <c r="R23" t="n">
-        <v>6765427</v>
+        <v>6765160</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3045,32 +3045,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129565818</v>
+        <v>129566021</v>
       </c>
       <c r="B24" t="n">
-        <v>92913</v>
+        <v>92875</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443118</v>
+        <v>443030</v>
       </c>
       <c r="R24" t="n">
-        <v>6765378</v>
+        <v>6765092</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,10 +3366,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129565757</v>
+        <v>129565923</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,21 +3377,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443135</v>
+        <v>442732</v>
       </c>
       <c r="R27" t="n">
-        <v>6765214</v>
+        <v>6765250</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3473,7 +3473,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129565923</v>
+        <v>129565898</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442732</v>
+        <v>443095</v>
       </c>
       <c r="R28" t="n">
-        <v>6765250</v>
+        <v>6765057</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3580,10 +3580,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129565898</v>
+        <v>129565853</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3591,21 +3591,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443095</v>
+        <v>443296</v>
       </c>
       <c r="R29" t="n">
-        <v>6765057</v>
+        <v>6765502</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3687,10 +3687,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129565853</v>
+        <v>129565759</v>
       </c>
       <c r="B30" t="n">
-        <v>78838</v>
+        <v>83050</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3698,21 +3698,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443296</v>
+        <v>442678</v>
       </c>
       <c r="R30" t="n">
-        <v>6765502</v>
+        <v>6764817</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129565759</v>
+        <v>129565998</v>
       </c>
       <c r="B31" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442678</v>
+        <v>443044</v>
       </c>
       <c r="R31" t="n">
-        <v>6764817</v>
+        <v>6765344</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3901,10 +3901,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129565998</v>
+        <v>129565757</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443044</v>
+        <v>443135</v>
       </c>
       <c r="R32" t="n">
-        <v>6765344</v>
+        <v>6765214</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4120,32 +4120,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129566021</v>
+        <v>129565818</v>
       </c>
       <c r="B34" t="n">
-        <v>92875</v>
+        <v>92913</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443030</v>
+        <v>443118</v>
       </c>
       <c r="R34" t="n">
-        <v>6765092</v>
+        <v>6765378</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4458,45 +4458,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129566029</v>
+        <v>129565839</v>
       </c>
       <c r="B37" t="n">
-        <v>78747</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442780</v>
+        <v>443000</v>
       </c>
       <c r="R37" t="n">
-        <v>6765272</v>
+        <v>6764985</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4538,7 +4543,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4779,10 +4784,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129565996</v>
+        <v>129565758</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4790,21 +4795,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4814,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443073</v>
+        <v>443250</v>
       </c>
       <c r="R40" t="n">
-        <v>6765365</v>
+        <v>6765208</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4849,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4859,7 +4864,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4886,7 +4891,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129565964</v>
+        <v>129565996</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -4921,10 +4926,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443407</v>
+        <v>443073</v>
       </c>
       <c r="R41" t="n">
-        <v>6765308</v>
+        <v>6765365</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4956,7 +4961,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4966,7 +4971,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4993,7 +4998,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129565974</v>
+        <v>129565964</v>
       </c>
       <c r="B42" t="n">
         <v>79081</v>
@@ -5028,10 +5033,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443350</v>
+        <v>443407</v>
       </c>
       <c r="R42" t="n">
-        <v>6765366</v>
+        <v>6765308</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5063,7 +5068,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5073,7 +5078,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5100,7 +5105,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129566018</v>
+        <v>129565974</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -5135,10 +5140,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442699</v>
+        <v>443350</v>
       </c>
       <c r="R43" t="n">
-        <v>6764782</v>
+        <v>6765366</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,7 +5175,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5180,7 +5185,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5207,7 +5212,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129565983</v>
+        <v>129566018</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5242,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443363</v>
+        <v>442699</v>
       </c>
       <c r="R44" t="n">
-        <v>6765473</v>
+        <v>6764782</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5277,7 +5282,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5287,7 +5292,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5314,7 +5319,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129565997</v>
+        <v>129565983</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5349,10 +5354,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443058</v>
+        <v>443363</v>
       </c>
       <c r="R45" t="n">
-        <v>6765367</v>
+        <v>6765473</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5384,7 +5389,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5394,7 +5399,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,7 +5426,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129566013</v>
+        <v>129565997</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5456,10 +5461,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442823</v>
+        <v>443058</v>
       </c>
       <c r="R46" t="n">
-        <v>6764875</v>
+        <v>6765367</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,7 +5496,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5501,7 +5506,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,7 +5533,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129565954</v>
+        <v>129566013</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5563,10 +5568,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443345</v>
+        <v>442823</v>
       </c>
       <c r="R47" t="n">
-        <v>6765155</v>
+        <v>6764875</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,7 +5603,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5608,7 +5613,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5635,10 +5640,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129565758</v>
+        <v>129565954</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5646,21 +5651,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5670,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443250</v>
+        <v>443345</v>
       </c>
       <c r="R48" t="n">
-        <v>6765208</v>
+        <v>6765155</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5705,7 +5710,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5715,7 +5720,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5742,50 +5747,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129565839</v>
+        <v>129566029</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>78747</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443000</v>
+        <v>442780</v>
       </c>
       <c r="R49" t="n">
-        <v>6764985</v>
+        <v>6765272</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5854,10 +5854,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129565772</v>
+        <v>129565863</v>
       </c>
       <c r="B50" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443016</v>
+        <v>442660</v>
       </c>
       <c r="R50" t="n">
-        <v>6765122</v>
+        <v>6764812</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129565845</v>
+        <v>129565880</v>
       </c>
       <c r="B51" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443296</v>
+        <v>442751</v>
       </c>
       <c r="R51" t="n">
-        <v>6765499</v>
+        <v>6764908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6068,32 +6068,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129565812</v>
+        <v>129565969</v>
       </c>
       <c r="B52" t="n">
-        <v>97645</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443420</v>
+        <v>443402</v>
       </c>
       <c r="R52" t="n">
-        <v>6765417</v>
+        <v>6765392</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,10 +6175,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129565804</v>
+        <v>129565957</v>
       </c>
       <c r="B53" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6186,39 +6186,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442847</v>
+        <v>443383</v>
       </c>
       <c r="R53" t="n">
-        <v>6765272</v>
+        <v>6765197</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6250,7 +6245,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6260,7 +6255,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6287,10 +6282,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129565767</v>
+        <v>129566007</v>
       </c>
       <c r="B54" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6298,21 +6293,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6322,10 +6317,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443318</v>
+        <v>442988</v>
       </c>
       <c r="R54" t="n">
-        <v>6765387</v>
+        <v>6765104</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6357,7 +6352,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6367,7 +6362,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6394,7 +6389,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129565863</v>
+        <v>129565917</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -6429,10 +6424,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442660</v>
+        <v>442736</v>
       </c>
       <c r="R55" t="n">
-        <v>6764812</v>
+        <v>6765272</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6464,7 +6459,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6474,7 +6469,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6501,10 +6496,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129565880</v>
+        <v>129565767</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6512,21 +6507,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6536,10 +6531,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442751</v>
+        <v>443318</v>
       </c>
       <c r="R56" t="n">
-        <v>6764908</v>
+        <v>6765387</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6571,7 +6566,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6581,7 +6576,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6608,10 +6603,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129565969</v>
+        <v>129565804</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6619,34 +6614,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443402</v>
+        <v>442847</v>
       </c>
       <c r="R57" t="n">
-        <v>6765392</v>
+        <v>6765272</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6715,32 +6715,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129565957</v>
+        <v>129565812</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>97645</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6750,10 +6750,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443383</v>
+        <v>443420</v>
       </c>
       <c r="R58" t="n">
-        <v>6765197</v>
+        <v>6765417</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6822,10 +6822,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129566007</v>
+        <v>129565845</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442988</v>
+        <v>443296</v>
       </c>
       <c r="R59" t="n">
-        <v>6765104</v>
+        <v>6765499</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6929,10 +6929,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129565917</v>
+        <v>129565772</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442736</v>
+        <v>443016</v>
       </c>
       <c r="R60" t="n">
-        <v>6765272</v>
+        <v>6765122</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7036,57 +7036,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129565786</v>
+        <v>129565788</v>
       </c>
       <c r="B61" t="n">
-        <v>56926</v>
+        <v>91614</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443115</v>
+        <v>442726</v>
       </c>
       <c r="R61" t="n">
-        <v>6765337</v>
+        <v>6764799</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7118,7 +7106,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7128,7 +7116,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7155,10 +7143,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129565788</v>
+        <v>129565761</v>
       </c>
       <c r="B62" t="n">
-        <v>91614</v>
+        <v>83050</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7166,21 +7154,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7190,10 +7178,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442726</v>
+        <v>442685</v>
       </c>
       <c r="R62" t="n">
-        <v>6764799</v>
+        <v>6764849</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7225,7 +7213,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7235,7 +7223,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7262,10 +7250,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129565761</v>
+        <v>129565865</v>
       </c>
       <c r="B63" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7273,21 +7261,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7297,10 +7285,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442685</v>
+        <v>442669</v>
       </c>
       <c r="R63" t="n">
-        <v>6764849</v>
+        <v>6764828</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7332,7 +7320,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7342,7 +7330,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7369,7 +7357,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129565865</v>
+        <v>129565882</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -7404,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442669</v>
+        <v>442762</v>
       </c>
       <c r="R64" t="n">
-        <v>6764828</v>
+        <v>6764920</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7439,7 +7427,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7449,7 +7437,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7476,7 +7464,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129565882</v>
+        <v>129566003</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7511,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442762</v>
+        <v>443142</v>
       </c>
       <c r="R65" t="n">
-        <v>6764920</v>
+        <v>6765165</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7546,7 +7534,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7556,7 +7544,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7583,45 +7571,57 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129566003</v>
+        <v>129565786</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443142</v>
+        <v>443115</v>
       </c>
       <c r="R66" t="n">
-        <v>6765165</v>
+        <v>6765337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7802,10 +7802,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129565801</v>
+        <v>129565866</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7813,39 +7813,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443258</v>
+        <v>442685</v>
       </c>
       <c r="R68" t="n">
-        <v>6765343</v>
+        <v>6764827</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7877,7 +7872,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7887,7 +7882,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7914,10 +7909,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129565847</v>
+        <v>129565978</v>
       </c>
       <c r="B69" t="n">
-        <v>81066</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7925,21 +7920,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7949,10 +7944,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443068</v>
+        <v>443303</v>
       </c>
       <c r="R69" t="n">
-        <v>6765019</v>
+        <v>6765447</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7984,7 +7979,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7994,7 +7989,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8021,7 +8016,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129565866</v>
+        <v>129565911</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -8056,10 +8051,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>442685</v>
+        <v>442817</v>
       </c>
       <c r="R70" t="n">
-        <v>6764827</v>
+        <v>6765276</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8091,7 +8086,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8101,7 +8096,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8128,7 +8123,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129565978</v>
+        <v>129565993</v>
       </c>
       <c r="B71" t="n">
         <v>79081</v>
@@ -8163,10 +8158,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443303</v>
+        <v>443126</v>
       </c>
       <c r="R71" t="n">
-        <v>6765447</v>
+        <v>6765359</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8198,7 +8193,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8208,7 +8203,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8235,7 +8230,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129565911</v>
+        <v>129566017</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -8270,10 +8265,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>442817</v>
+        <v>442707</v>
       </c>
       <c r="R72" t="n">
-        <v>6765276</v>
+        <v>6764791</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8305,7 +8300,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8315,7 +8310,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8342,7 +8337,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129565993</v>
+        <v>129565903</v>
       </c>
       <c r="B73" t="n">
         <v>79081</v>
@@ -8377,10 +8372,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443126</v>
+        <v>443051</v>
       </c>
       <c r="R73" t="n">
-        <v>6765359</v>
+        <v>6765229</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8412,7 +8407,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8422,7 +8417,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8449,7 +8444,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129566017</v>
+        <v>129565994</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -8484,10 +8479,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>442707</v>
+        <v>443076</v>
       </c>
       <c r="R74" t="n">
-        <v>6764791</v>
+        <v>6765364</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8519,7 +8514,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8529,7 +8524,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8556,10 +8551,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129565903</v>
+        <v>129565801</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8567,34 +8562,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443051</v>
+        <v>443258</v>
       </c>
       <c r="R75" t="n">
-        <v>6765229</v>
+        <v>6765343</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8663,10 +8663,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129565994</v>
+        <v>129565847</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>81066</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8674,21 +8674,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443076</v>
+        <v>443068</v>
       </c>
       <c r="R76" t="n">
-        <v>6765364</v>
+        <v>6765019</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9845,7 +9845,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129565976</v>
+        <v>129565966</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443332</v>
+        <v>443432</v>
       </c>
       <c r="R87" t="n">
-        <v>6765403</v>
+        <v>6765347</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9952,10 +9952,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129565849</v>
+        <v>129565976</v>
       </c>
       <c r="B88" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9963,21 +9963,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443033</v>
+        <v>443332</v>
       </c>
       <c r="R88" t="n">
-        <v>6765241</v>
+        <v>6765403</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10059,10 +10059,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129566005</v>
+        <v>129565849</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10070,21 +10070,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443160</v>
+        <v>443033</v>
       </c>
       <c r="R89" t="n">
-        <v>6765086</v>
+        <v>6765241</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129565899</v>
+        <v>129566005</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443088</v>
+        <v>443160</v>
       </c>
       <c r="R90" t="n">
-        <v>6765090</v>
+        <v>6765086</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10273,7 +10273,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129565956</v>
+        <v>129565899</v>
       </c>
       <c r="B91" t="n">
         <v>79081</v>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443366</v>
+        <v>443088</v>
       </c>
       <c r="R91" t="n">
-        <v>6765190</v>
+        <v>6765090</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10380,7 +10380,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129565932</v>
+        <v>129565956</v>
       </c>
       <c r="B92" t="n">
         <v>79081</v>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>442724</v>
+        <v>443366</v>
       </c>
       <c r="R92" t="n">
-        <v>6765212</v>
+        <v>6765190</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10487,7 +10487,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129565902</v>
+        <v>129565932</v>
       </c>
       <c r="B93" t="n">
         <v>79081</v>
@@ -10522,10 +10522,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443010</v>
+        <v>442724</v>
       </c>
       <c r="R93" t="n">
-        <v>6765160</v>
+        <v>6765212</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10594,7 +10594,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129565961</v>
+        <v>129565902</v>
       </c>
       <c r="B94" t="n">
         <v>79081</v>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443405</v>
+        <v>443010</v>
       </c>
       <c r="R94" t="n">
-        <v>6765244</v>
+        <v>6765160</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,7 +10701,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129565966</v>
+        <v>129565961</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443432</v>
+        <v>443405</v>
       </c>
       <c r="R95" t="n">
-        <v>6765347</v>
+        <v>6765244</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10808,52 +10808,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129565784</v>
+        <v>129566027</v>
       </c>
       <c r="B96" t="n">
-        <v>56926</v>
+        <v>78747</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443093</v>
+        <v>443043</v>
       </c>
       <c r="R96" t="n">
-        <v>6765290</v>
+        <v>6765047</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10885,7 +10878,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10895,7 +10888,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10922,45 +10915,52 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129565844</v>
+        <v>129565784</v>
       </c>
       <c r="B97" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443017</v>
+        <v>443093</v>
       </c>
       <c r="R97" t="n">
-        <v>6765118</v>
+        <v>6765290</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11029,10 +11029,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129566027</v>
+        <v>129565844</v>
       </c>
       <c r="B98" t="n">
-        <v>78747</v>
+        <v>78839</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11040,21 +11040,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11064,10 +11064,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443043</v>
+        <v>443017</v>
       </c>
       <c r="R98" t="n">
-        <v>6765047</v>
+        <v>6765118</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11136,10 +11136,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129565753</v>
+        <v>129565874</v>
       </c>
       <c r="B99" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11147,21 +11147,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443271</v>
+        <v>442679</v>
       </c>
       <c r="R99" t="n">
-        <v>6765126</v>
+        <v>6764871</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11243,10 +11243,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129565749</v>
+        <v>129565760</v>
       </c>
       <c r="B100" t="n">
-        <v>79700</v>
+        <v>83050</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11254,21 +11254,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>442782</v>
+        <v>442682</v>
       </c>
       <c r="R100" t="n">
-        <v>6765271</v>
+        <v>6764828</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11323,12 +11323,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsyn</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11355,10 +11350,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129565768</v>
+        <v>129565870</v>
       </c>
       <c r="B101" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11366,21 +11361,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11390,10 +11385,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>442990</v>
+        <v>442695</v>
       </c>
       <c r="R101" t="n">
-        <v>6765105</v>
+        <v>6764852</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,7 +11420,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11435,7 +11430,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11462,7 +11457,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129565874</v>
+        <v>129565906</v>
       </c>
       <c r="B102" t="n">
         <v>79081</v>
@@ -11497,10 +11492,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>442679</v>
+        <v>442852</v>
       </c>
       <c r="R102" t="n">
-        <v>6764871</v>
+        <v>6765301</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11532,7 +11527,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11542,7 +11537,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11569,10 +11564,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129565760</v>
+        <v>129565868</v>
       </c>
       <c r="B103" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11580,21 +11575,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11604,10 +11599,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>442682</v>
+        <v>442689</v>
       </c>
       <c r="R103" t="n">
-        <v>6764828</v>
+        <v>6764832</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11639,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11649,7 +11644,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11676,10 +11671,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129565870</v>
+        <v>129565768</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11687,21 +11682,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11711,10 +11706,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>442695</v>
+        <v>442990</v>
       </c>
       <c r="R104" t="n">
-        <v>6764852</v>
+        <v>6765105</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11746,7 +11741,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11756,7 +11751,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11783,10 +11778,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129565906</v>
+        <v>129565753</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11794,21 +11789,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11818,10 +11813,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>442852</v>
+        <v>443271</v>
       </c>
       <c r="R105" t="n">
-        <v>6765301</v>
+        <v>6765126</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11853,7 +11848,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11863,7 +11858,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11890,10 +11885,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129565868</v>
+        <v>129565749</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11901,21 +11896,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11925,10 +11920,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>442689</v>
+        <v>442782</v>
       </c>
       <c r="R106" t="n">
-        <v>6764832</v>
+        <v>6765271</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11960,7 +11955,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11970,7 +11965,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsyn</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11997,10 +11997,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129566023</v>
+        <v>129565960</v>
       </c>
       <c r="B107" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12008,21 +12008,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12032,10 +12032,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443207</v>
+        <v>443403</v>
       </c>
       <c r="R107" t="n">
-        <v>6765081</v>
+        <v>6765238</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12077,12 +12077,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12109,7 +12104,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129565960</v>
+        <v>129565891</v>
       </c>
       <c r="B108" t="n">
         <v>79081</v>
@@ -12144,10 +12139,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443403</v>
+        <v>442829</v>
       </c>
       <c r="R108" t="n">
-        <v>6765238</v>
+        <v>6764901</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12179,7 +12174,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12189,7 +12184,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12216,7 +12211,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129565891</v>
+        <v>129565876</v>
       </c>
       <c r="B109" t="n">
         <v>79081</v>
@@ -12251,10 +12246,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>442829</v>
+        <v>442690</v>
       </c>
       <c r="R109" t="n">
-        <v>6764901</v>
+        <v>6764884</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12286,7 +12281,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12296,7 +12291,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12323,10 +12318,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129565876</v>
+        <v>129565751</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12334,21 +12329,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12361,7 +12356,7 @@
         <v>442690</v>
       </c>
       <c r="R110" t="n">
-        <v>6764884</v>
+        <v>6764886</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12393,7 +12388,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12403,7 +12398,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12430,50 +12425,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129565821</v>
+        <v>129566023</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>78747</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443034</v>
+        <v>443207</v>
       </c>
       <c r="R111" t="n">
-        <v>6765053</v>
+        <v>6765081</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12505,7 +12495,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12515,7 +12505,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12542,7 +12537,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129565751</v>
+        <v>129565750</v>
       </c>
       <c r="B112" t="n">
         <v>79700</v>
@@ -12577,10 +12572,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>442690</v>
+        <v>443145</v>
       </c>
       <c r="R112" t="n">
-        <v>6764886</v>
+        <v>6765323</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12612,7 +12607,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12622,7 +12617,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På enda silverlågan med hänsyn i hela anmälan</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12649,45 +12649,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129565750</v>
+        <v>129565821</v>
       </c>
       <c r="B113" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443145</v>
+        <v>443034</v>
       </c>
       <c r="R113" t="n">
-        <v>6765323</v>
+        <v>6765053</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12719,7 +12724,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12729,12 +12734,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>På enda silverlågan med hänsyn i hela anmälan</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14157,52 +14157,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129565785</v>
+        <v>129565985</v>
       </c>
       <c r="B127" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443076</v>
+        <v>443324</v>
       </c>
       <c r="R127" t="n">
-        <v>6765380</v>
+        <v>6765398</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14234,7 +14227,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14244,7 +14237,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14271,10 +14264,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129565766</v>
+        <v>129565925</v>
       </c>
       <c r="B128" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14282,21 +14275,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14306,10 +14299,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443305</v>
+        <v>442732</v>
       </c>
       <c r="R128" t="n">
-        <v>6765463</v>
+        <v>6765239</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14341,7 +14334,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14351,7 +14344,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14378,7 +14371,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129565985</v>
+        <v>129566004</v>
       </c>
       <c r="B129" t="n">
         <v>79081</v>
@@ -14413,10 +14406,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443324</v>
+        <v>443246</v>
       </c>
       <c r="R129" t="n">
-        <v>6765398</v>
+        <v>6765145</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14448,7 +14441,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14458,7 +14451,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14485,7 +14478,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129565925</v>
+        <v>129565920</v>
       </c>
       <c r="B130" t="n">
         <v>79081</v>
@@ -14520,10 +14513,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>442732</v>
+        <v>442734</v>
       </c>
       <c r="R130" t="n">
-        <v>6765239</v>
+        <v>6765264</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14555,7 +14548,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14565,7 +14558,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14592,10 +14585,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129566004</v>
+        <v>129565766</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14603,21 +14596,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14627,10 +14620,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443246</v>
+        <v>443305</v>
       </c>
       <c r="R131" t="n">
-        <v>6765145</v>
+        <v>6765463</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14662,7 +14655,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14672,7 +14665,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14699,10 +14692,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129565920</v>
+        <v>129566025</v>
       </c>
       <c r="B132" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14710,21 +14703,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14734,10 +14727,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>442734</v>
+        <v>442693</v>
       </c>
       <c r="R132" t="n">
-        <v>6765264</v>
+        <v>6764827</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14769,7 +14762,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14779,7 +14772,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14806,10 +14799,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129565959</v>
+        <v>129566032</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14817,21 +14810,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14841,10 +14834,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443414</v>
+        <v>443236</v>
       </c>
       <c r="R133" t="n">
-        <v>6765221</v>
+        <v>6765316</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14876,7 +14869,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14886,7 +14879,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15020,10 +15013,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129566025</v>
+        <v>129565959</v>
       </c>
       <c r="B135" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15031,21 +15024,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15055,10 +15048,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>442693</v>
+        <v>443414</v>
       </c>
       <c r="R135" t="n">
-        <v>6764827</v>
+        <v>6765221</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15090,7 +15083,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15100,7 +15093,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15127,45 +15120,52 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129566032</v>
+        <v>129565785</v>
       </c>
       <c r="B136" t="n">
-        <v>78747</v>
+        <v>56926</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>443236</v>
+        <v>443076</v>
       </c>
       <c r="R136" t="n">
-        <v>6765316</v>
+        <v>6765380</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15453,45 +15453,50 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129566031</v>
+        <v>129565842</v>
       </c>
       <c r="B139" t="n">
-        <v>78747</v>
+        <v>8450</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>443296</v>
+        <v>443232</v>
       </c>
       <c r="R139" t="n">
-        <v>6765499</v>
+        <v>6765136</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15523,7 +15528,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15533,7 +15538,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15560,45 +15565,50 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129565764</v>
+        <v>129565827</v>
       </c>
       <c r="B140" t="n">
-        <v>79113</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443048</v>
+        <v>442998</v>
       </c>
       <c r="R140" t="n">
-        <v>6765235</v>
+        <v>6765028</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15630,7 +15640,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15640,7 +15650,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15667,10 +15677,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129566026</v>
+        <v>129565871</v>
       </c>
       <c r="B141" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15678,21 +15688,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15702,10 +15712,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>442684</v>
+        <v>442690</v>
       </c>
       <c r="R141" t="n">
-        <v>6764861</v>
+        <v>6764850</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15737,7 +15747,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15747,7 +15757,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15774,7 +15784,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129565871</v>
+        <v>129565913</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -15809,10 +15819,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>442690</v>
+        <v>442773</v>
       </c>
       <c r="R142" t="n">
-        <v>6764850</v>
+        <v>6765264</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15844,7 +15854,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15854,7 +15864,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15881,10 +15891,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129565913</v>
+        <v>129565752</v>
       </c>
       <c r="B143" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15892,21 +15902,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15916,10 +15926,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>442773</v>
+        <v>443004</v>
       </c>
       <c r="R143" t="n">
-        <v>6765264</v>
+        <v>6765163</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15951,7 +15961,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15961,7 +15971,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16956,10 +16966,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129565770</v>
+        <v>129566031</v>
       </c>
       <c r="B153" t="n">
-        <v>79671</v>
+        <v>78747</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16967,21 +16977,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16991,10 +17001,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>443068</v>
+        <v>443296</v>
       </c>
       <c r="R153" t="n">
-        <v>6765020</v>
+        <v>6765499</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17026,7 +17036,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17036,7 +17046,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17063,32 +17073,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129565769</v>
+        <v>129565764</v>
       </c>
       <c r="B154" t="n">
-        <v>91557</v>
+        <v>79113</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17098,10 +17108,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443362</v>
+        <v>443048</v>
       </c>
       <c r="R154" t="n">
-        <v>6765377</v>
+        <v>6765235</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17133,7 +17143,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17143,7 +17153,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17170,10 +17180,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129565752</v>
+        <v>129566026</v>
       </c>
       <c r="B155" t="n">
-        <v>79700</v>
+        <v>78747</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17181,21 +17191,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17205,10 +17215,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443004</v>
+        <v>442684</v>
       </c>
       <c r="R155" t="n">
-        <v>6765163</v>
+        <v>6764861</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17240,7 +17250,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17250,7 +17260,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17277,10 +17287,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129565842</v>
+        <v>129565769</v>
       </c>
       <c r="B156" t="n">
-        <v>8450</v>
+        <v>91557</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17288,39 +17298,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>443232</v>
+        <v>443362</v>
       </c>
       <c r="R156" t="n">
-        <v>6765136</v>
+        <v>6765377</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17352,7 +17357,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17362,7 +17367,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17389,50 +17394,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129565827</v>
+        <v>129565770</v>
       </c>
       <c r="B157" t="n">
-        <v>8450</v>
+        <v>79671</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>442998</v>
+        <v>443068</v>
       </c>
       <c r="R157" t="n">
-        <v>6765028</v>
+        <v>6765020</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19569,10 +19569,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129566033</v>
+        <v>129565806</v>
       </c>
       <c r="B177" t="n">
-        <v>78747</v>
+        <v>57733</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19580,34 +19580,39 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>443144</v>
+        <v>443430</v>
       </c>
       <c r="R177" t="n">
-        <v>6765199</v>
+        <v>6765200</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19639,7 +19644,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19649,7 +19654,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19788,10 +19793,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129565833</v>
+        <v>129565808</v>
       </c>
       <c r="B179" t="n">
-        <v>8450</v>
+        <v>97645</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19799,39 +19804,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>442775</v>
+        <v>443432</v>
       </c>
       <c r="R179" t="n">
-        <v>6765271</v>
+        <v>6765348</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19863,7 +19863,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19900,32 +19900,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129565808</v>
+        <v>129566033</v>
       </c>
       <c r="B180" t="n">
-        <v>97645</v>
+        <v>78747</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19935,10 +19935,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>443432</v>
+        <v>443144</v>
       </c>
       <c r="R180" t="n">
-        <v>6765348</v>
+        <v>6765199</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19980,7 +19980,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20007,45 +20007,50 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129565879</v>
+        <v>129565833</v>
       </c>
       <c r="B181" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>442749</v>
+        <v>442775</v>
       </c>
       <c r="R181" t="n">
-        <v>6764886</v>
+        <v>6765271</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20077,7 +20082,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20087,7 +20092,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20114,7 +20119,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129565972</v>
+        <v>129565879</v>
       </c>
       <c r="B182" t="n">
         <v>79081</v>
@@ -20149,10 +20154,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>443398</v>
+        <v>442749</v>
       </c>
       <c r="R182" t="n">
-        <v>6765434</v>
+        <v>6764886</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20184,7 +20189,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20194,7 +20199,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20221,7 +20226,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129566002</v>
+        <v>129565972</v>
       </c>
       <c r="B183" t="n">
         <v>79081</v>
@@ -20256,10 +20261,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>443134</v>
+        <v>443398</v>
       </c>
       <c r="R183" t="n">
-        <v>6765184</v>
+        <v>6765434</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20291,7 +20296,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20301,7 +20306,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20328,7 +20333,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129565973</v>
+        <v>129566002</v>
       </c>
       <c r="B184" t="n">
         <v>79081</v>
@@ -20363,10 +20368,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443383</v>
+        <v>443134</v>
       </c>
       <c r="R184" t="n">
-        <v>6765415</v>
+        <v>6765184</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20398,7 +20403,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20408,7 +20413,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20435,7 +20440,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129565927</v>
+        <v>129565973</v>
       </c>
       <c r="B185" t="n">
         <v>79081</v>
@@ -20470,10 +20475,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>442770</v>
+        <v>443383</v>
       </c>
       <c r="R185" t="n">
-        <v>6765225</v>
+        <v>6765415</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20505,7 +20510,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20515,7 +20520,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20542,7 +20547,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129565984</v>
+        <v>129565927</v>
       </c>
       <c r="B186" t="n">
         <v>79081</v>
@@ -20577,10 +20582,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>443338</v>
+        <v>442770</v>
       </c>
       <c r="R186" t="n">
-        <v>6765441</v>
+        <v>6765225</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20612,7 +20617,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20622,7 +20627,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20649,7 +20654,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129565912</v>
+        <v>129565984</v>
       </c>
       <c r="B187" t="n">
         <v>79081</v>
@@ -20684,10 +20689,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>442776</v>
+        <v>443338</v>
       </c>
       <c r="R187" t="n">
-        <v>6765280</v>
+        <v>6765441</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20719,7 +20724,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20729,7 +20734,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20756,7 +20761,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129565971</v>
+        <v>129565912</v>
       </c>
       <c r="B188" t="n">
         <v>79081</v>
@@ -20791,10 +20796,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>443406</v>
+        <v>442776</v>
       </c>
       <c r="R188" t="n">
-        <v>6765450</v>
+        <v>6765280</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20826,7 +20831,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20836,7 +20841,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20863,10 +20868,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129565806</v>
+        <v>129565971</v>
       </c>
       <c r="B189" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20874,39 +20879,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>443430</v>
+        <v>443406</v>
       </c>
       <c r="R189" t="n">
-        <v>6765200</v>
+        <v>6765450</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20975,10 +20975,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129565771</v>
+        <v>129565963</v>
       </c>
       <c r="B190" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20986,21 +20986,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21010,10 +21010,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>443081</v>
+        <v>443410</v>
       </c>
       <c r="R190" t="n">
-        <v>6765117</v>
+        <v>6765453</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21055,7 +21055,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21082,10 +21082,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129565846</v>
+        <v>129565878</v>
       </c>
       <c r="B191" t="n">
-        <v>92012</v>
+        <v>79081</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21093,16 +21093,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21112,10 +21117,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>443405</v>
+        <v>442745</v>
       </c>
       <c r="R191" t="n">
-        <v>6765306</v>
+        <v>6764895</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21147,7 +21152,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21157,7 +21162,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21184,10 +21189,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129566024</v>
+        <v>129566001</v>
       </c>
       <c r="B192" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21195,21 +21200,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21219,10 +21224,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>443088</v>
+        <v>443140</v>
       </c>
       <c r="R192" t="n">
-        <v>6765114</v>
+        <v>6765218</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21254,7 +21259,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21264,12 +21269,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsyn</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21296,7 +21296,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129565963</v>
+        <v>129566009</v>
       </c>
       <c r="B193" t="n">
         <v>79081</v>
@@ -21331,10 +21331,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443410</v>
+        <v>442846</v>
       </c>
       <c r="R193" t="n">
-        <v>6765453</v>
+        <v>6764891</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21403,10 +21403,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129565878</v>
+        <v>129566024</v>
       </c>
       <c r="B194" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21414,21 +21414,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21438,10 +21438,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>442745</v>
+        <v>443088</v>
       </c>
       <c r="R194" t="n">
-        <v>6764895</v>
+        <v>6765114</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21483,7 +21483,12 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsyn</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21510,45 +21515,50 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129566001</v>
+        <v>129565826</v>
       </c>
       <c r="B195" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443140</v>
+        <v>443073</v>
       </c>
       <c r="R195" t="n">
-        <v>6765218</v>
+        <v>6765287</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21580,7 +21590,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21590,7 +21600,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21617,10 +21627,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129566009</v>
+        <v>129565771</v>
       </c>
       <c r="B196" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21628,21 +21638,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21652,10 +21662,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>442846</v>
+        <v>443081</v>
       </c>
       <c r="R196" t="n">
-        <v>6764891</v>
+        <v>6765117</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21687,7 +21697,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21697,7 +21707,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21724,50 +21734,40 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129565826</v>
+        <v>129565846</v>
       </c>
       <c r="B197" t="n">
-        <v>8450</v>
+        <v>92012</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>443073</v>
+        <v>443405</v>
       </c>
       <c r="R197" t="n">
-        <v>6765287</v>
+        <v>6765306</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21809,7 +21809,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21836,10 +21836,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129565817</v>
+        <v>129565763</v>
       </c>
       <c r="B198" t="n">
-        <v>92913</v>
+        <v>79113</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21847,21 +21847,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5966</v>
+        <v>185</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21871,7 +21871,7 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>442767</v>
+        <v>443051</v>
       </c>
       <c r="R198" t="n">
         <v>6765229</v>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21916,7 +21916,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21943,10 +21943,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129565763</v>
+        <v>129565803</v>
       </c>
       <c r="B199" t="n">
-        <v>79113</v>
+        <v>57733</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21954,34 +21954,39 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>443051</v>
+        <v>443250</v>
       </c>
       <c r="R199" t="n">
-        <v>6765229</v>
+        <v>6765211</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22013,7 +22018,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22023,7 +22028,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22050,10 +22055,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129565950</v>
+        <v>129565807</v>
       </c>
       <c r="B200" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22061,34 +22066,39 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>443156</v>
+        <v>442850</v>
       </c>
       <c r="R200" t="n">
-        <v>6765060</v>
+        <v>6764898</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22120,7 +22130,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22130,7 +22140,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22157,7 +22167,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129565908</v>
+        <v>129565950</v>
       </c>
       <c r="B201" t="n">
         <v>79081</v>
@@ -22192,10 +22202,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>442859</v>
+        <v>443156</v>
       </c>
       <c r="R201" t="n">
-        <v>6765277</v>
+        <v>6765060</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22227,7 +22237,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22237,7 +22247,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22264,7 +22274,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129565981</v>
+        <v>129565908</v>
       </c>
       <c r="B202" t="n">
         <v>79081</v>
@@ -22299,10 +22309,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>443294</v>
+        <v>442859</v>
       </c>
       <c r="R202" t="n">
-        <v>6765505</v>
+        <v>6765277</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22334,7 +22344,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22344,7 +22354,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22371,7 +22381,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129565955</v>
+        <v>129565981</v>
       </c>
       <c r="B203" t="n">
         <v>79081</v>
@@ -22406,10 +22416,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>443351</v>
+        <v>443294</v>
       </c>
       <c r="R203" t="n">
-        <v>6765163</v>
+        <v>6765505</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22441,7 +22451,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22451,7 +22461,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22478,7 +22488,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129565919</v>
+        <v>129565955</v>
       </c>
       <c r="B204" t="n">
         <v>79081</v>
@@ -22513,10 +22523,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>442733</v>
+        <v>443351</v>
       </c>
       <c r="R204" t="n">
-        <v>6765274</v>
+        <v>6765163</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22548,7 +22558,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22558,7 +22568,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22585,7 +22595,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129565894</v>
+        <v>129565919</v>
       </c>
       <c r="B205" t="n">
         <v>79081</v>
@@ -22620,10 +22630,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>442973</v>
+        <v>442733</v>
       </c>
       <c r="R205" t="n">
-        <v>6764957</v>
+        <v>6765274</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22655,7 +22665,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22665,7 +22675,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22692,7 +22702,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129565907</v>
+        <v>129565894</v>
       </c>
       <c r="B206" t="n">
         <v>79081</v>
@@ -22727,10 +22737,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>442863</v>
+        <v>442973</v>
       </c>
       <c r="R206" t="n">
-        <v>6765287</v>
+        <v>6764957</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22762,7 +22772,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22772,7 +22782,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22799,10 +22809,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129565803</v>
+        <v>129565907</v>
       </c>
       <c r="B207" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22810,39 +22820,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>443250</v>
+        <v>442863</v>
       </c>
       <c r="R207" t="n">
-        <v>6765211</v>
+        <v>6765287</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22874,7 +22879,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22884,7 +22889,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22911,10 +22916,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129565807</v>
+        <v>129565817</v>
       </c>
       <c r="B208" t="n">
-        <v>57733</v>
+        <v>92913</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22922,39 +22927,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>442850</v>
+        <v>442767</v>
       </c>
       <c r="R208" t="n">
-        <v>6764898</v>
+        <v>6765229</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22986,7 +22986,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23023,10 +23023,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129565774</v>
+        <v>129565982</v>
       </c>
       <c r="B209" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23034,21 +23034,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23058,10 +23058,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>443296</v>
+        <v>443328</v>
       </c>
       <c r="R209" t="n">
-        <v>6765472</v>
+        <v>6765500</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23093,7 +23093,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23130,7 +23130,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129565982</v>
+        <v>129565881</v>
       </c>
       <c r="B210" t="n">
         <v>79081</v>
@@ -23165,10 +23165,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>443328</v>
+        <v>442754</v>
       </c>
       <c r="R210" t="n">
-        <v>6765500</v>
+        <v>6764914</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23200,7 +23200,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23237,7 +23237,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129565881</v>
+        <v>129565970</v>
       </c>
       <c r="B211" t="n">
         <v>79081</v>
@@ -23272,10 +23272,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>442754</v>
+        <v>443416</v>
       </c>
       <c r="R211" t="n">
-        <v>6764914</v>
+        <v>6765453</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23307,7 +23307,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23344,7 +23344,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129565970</v>
+        <v>129566000</v>
       </c>
       <c r="B212" t="n">
         <v>79081</v>
@@ -23379,10 +23379,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>443416</v>
+        <v>443144</v>
       </c>
       <c r="R212" t="n">
-        <v>6765453</v>
+        <v>6765233</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23451,7 +23451,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129566000</v>
+        <v>129565872</v>
       </c>
       <c r="B213" t="n">
         <v>79081</v>
@@ -23486,10 +23486,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>443144</v>
+        <v>442685</v>
       </c>
       <c r="R213" t="n">
-        <v>6765233</v>
+        <v>6764849</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23558,7 +23558,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129565872</v>
+        <v>129565916</v>
       </c>
       <c r="B214" t="n">
         <v>79081</v>
@@ -23593,10 +23593,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>442685</v>
+        <v>442750</v>
       </c>
       <c r="R214" t="n">
-        <v>6764849</v>
+        <v>6765268</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23628,7 +23628,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23665,7 +23665,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129565916</v>
+        <v>129565924</v>
       </c>
       <c r="B215" t="n">
         <v>79081</v>
@@ -23700,10 +23700,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>442750</v>
+        <v>442729</v>
       </c>
       <c r="R215" t="n">
-        <v>6765268</v>
+        <v>6765242</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23745,7 +23745,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23772,10 +23772,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129565924</v>
+        <v>129565798</v>
       </c>
       <c r="B216" t="n">
-        <v>79081</v>
+        <v>91544</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23783,21 +23783,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -23807,10 +23807,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>442729</v>
+        <v>442855</v>
       </c>
       <c r="R216" t="n">
-        <v>6765242</v>
+        <v>6764903</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23852,7 +23852,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23986,10 +23986,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129565798</v>
+        <v>129565774</v>
       </c>
       <c r="B218" t="n">
-        <v>91544</v>
+        <v>79671</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23997,21 +23997,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>112</v>
+        <v>229821</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24021,10 +24021,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>442855</v>
+        <v>443296</v>
       </c>
       <c r="R218" t="n">
-        <v>6764903</v>
+        <v>6765472</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24056,7 +24056,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD218" t="b">

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -1970,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129565900</v>
+        <v>129565773</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,21 +1981,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443088</v>
+        <v>443322</v>
       </c>
       <c r="R14" t="n">
-        <v>6765128</v>
+        <v>6765427</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,7 +2077,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129565965</v>
+        <v>129565900</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443429</v>
+        <v>443088</v>
       </c>
       <c r="R15" t="n">
-        <v>6765332</v>
+        <v>6765128</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,7 +2184,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129566006</v>
+        <v>129565965</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443030</v>
+        <v>443429</v>
       </c>
       <c r="R16" t="n">
-        <v>6765092</v>
+        <v>6765332</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129565921</v>
+        <v>129566006</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442732</v>
+        <v>443030</v>
       </c>
       <c r="R17" t="n">
-        <v>6765254</v>
+        <v>6765092</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129565851</v>
+        <v>129565921</v>
       </c>
       <c r="B18" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443355</v>
+        <v>442732</v>
       </c>
       <c r="R18" t="n">
-        <v>6765158</v>
+        <v>6765254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129565909</v>
+        <v>129565851</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,21 +2516,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442834</v>
+        <v>443355</v>
       </c>
       <c r="R19" t="n">
-        <v>6765265</v>
+        <v>6765158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,10 +2612,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129565854</v>
+        <v>129565909</v>
       </c>
       <c r="B20" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,21 +2623,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443342</v>
+        <v>442834</v>
       </c>
       <c r="R20" t="n">
-        <v>6765500</v>
+        <v>6765265</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2719,10 +2719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129565754</v>
+        <v>129565854</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443335</v>
+        <v>443342</v>
       </c>
       <c r="R21" t="n">
-        <v>6765160</v>
+        <v>6765500</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2826,50 +2826,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129565834</v>
+        <v>129565754</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442810</v>
+        <v>443335</v>
       </c>
       <c r="R22" t="n">
-        <v>6765170</v>
+        <v>6765160</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,7 +2896,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2911,7 +2906,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,45 +2933,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129565773</v>
+        <v>129565834</v>
       </c>
       <c r="B23" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443322</v>
+        <v>442810</v>
       </c>
       <c r="R23" t="n">
-        <v>6765427</v>
+        <v>6765170</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129565957</v>
+        <v>129565804</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,34 +5972,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443383</v>
+        <v>442847</v>
       </c>
       <c r="R51" t="n">
-        <v>6765197</v>
+        <v>6765272</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6031,7 +6036,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6041,7 +6046,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6068,7 +6073,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129566007</v>
+        <v>129565957</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -6103,10 +6108,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442988</v>
+        <v>443383</v>
       </c>
       <c r="R52" t="n">
-        <v>6765104</v>
+        <v>6765197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6138,7 +6143,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6148,7 +6153,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,7 +6180,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129565863</v>
+        <v>129566007</v>
       </c>
       <c r="B53" t="n">
         <v>79081</v>
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442660</v>
+        <v>442988</v>
       </c>
       <c r="R53" t="n">
-        <v>6764812</v>
+        <v>6765104</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6245,7 +6250,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6255,7 +6260,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6282,7 +6287,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129565880</v>
+        <v>129565863</v>
       </c>
       <c r="B54" t="n">
         <v>79081</v>
@@ -6317,10 +6322,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442751</v>
+        <v>442660</v>
       </c>
       <c r="R54" t="n">
-        <v>6764908</v>
+        <v>6764812</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6352,7 +6357,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6362,7 +6367,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6389,32 +6394,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129565812</v>
+        <v>129565880</v>
       </c>
       <c r="B55" t="n">
-        <v>97651</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6424,10 +6429,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443420</v>
+        <v>442751</v>
       </c>
       <c r="R55" t="n">
-        <v>6765417</v>
+        <v>6764908</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6459,7 +6464,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6469,7 +6474,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6496,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129565772</v>
+        <v>129565969</v>
       </c>
       <c r="B56" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6507,21 +6512,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6531,10 +6536,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443016</v>
+        <v>443402</v>
       </c>
       <c r="R56" t="n">
-        <v>6765122</v>
+        <v>6765392</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6566,7 +6571,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6576,7 +6581,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6603,10 +6608,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129565845</v>
+        <v>129565917</v>
       </c>
       <c r="B57" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6614,21 +6619,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6638,10 +6643,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443296</v>
+        <v>442736</v>
       </c>
       <c r="R57" t="n">
-        <v>6765499</v>
+        <v>6765272</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6673,7 +6678,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6683,7 +6688,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6710,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129565804</v>
+        <v>129565772</v>
       </c>
       <c r="B58" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6721,39 +6726,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442847</v>
+        <v>443016</v>
       </c>
       <c r="R58" t="n">
-        <v>6765272</v>
+        <v>6765122</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6822,10 +6822,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129565969</v>
+        <v>129565845</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443402</v>
+        <v>443296</v>
       </c>
       <c r="R59" t="n">
-        <v>6765392</v>
+        <v>6765499</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6929,32 +6929,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129565917</v>
+        <v>129565812</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>97651</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442736</v>
+        <v>443420</v>
       </c>
       <c r="R60" t="n">
-        <v>6765272</v>
+        <v>6765417</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7036,50 +7036,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129565824</v>
+        <v>129565788</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>91620</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443207</v>
+        <v>442726</v>
       </c>
       <c r="R61" t="n">
-        <v>6765086</v>
+        <v>6764799</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7111,7 +7106,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7121,7 +7116,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7148,10 +7143,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129565788</v>
+        <v>129565761</v>
       </c>
       <c r="B62" t="n">
-        <v>91620</v>
+        <v>83052</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7159,21 +7154,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7183,10 +7178,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442726</v>
+        <v>442685</v>
       </c>
       <c r="R62" t="n">
-        <v>6764799</v>
+        <v>6764849</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7218,7 +7213,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7228,7 +7223,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7255,10 +7250,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129565761</v>
+        <v>129565865</v>
       </c>
       <c r="B63" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7266,21 +7261,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7290,10 +7285,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442685</v>
+        <v>442669</v>
       </c>
       <c r="R63" t="n">
-        <v>6764849</v>
+        <v>6764828</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7325,7 +7320,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7335,7 +7330,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7362,7 +7357,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129565865</v>
+        <v>129565882</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -7397,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442669</v>
+        <v>442762</v>
       </c>
       <c r="R64" t="n">
-        <v>6764828</v>
+        <v>6764920</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7432,7 +7427,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7442,7 +7437,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7469,7 +7464,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129565882</v>
+        <v>129566003</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7504,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442762</v>
+        <v>443142</v>
       </c>
       <c r="R65" t="n">
-        <v>6764920</v>
+        <v>6765165</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7539,7 +7534,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7549,7 +7544,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7576,45 +7571,57 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129566003</v>
+        <v>129565786</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443142</v>
+        <v>443115</v>
       </c>
       <c r="R66" t="n">
-        <v>6765165</v>
+        <v>6765337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7646,7 +7653,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7656,7 +7663,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7683,10 +7690,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129565786</v>
+        <v>129565824</v>
       </c>
       <c r="B67" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7694,46 +7701,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443115</v>
+        <v>443207</v>
       </c>
       <c r="R67" t="n">
-        <v>6765337</v>
+        <v>6765086</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9845,10 +9845,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129566027</v>
+        <v>129565844</v>
       </c>
       <c r="B87" t="n">
-        <v>78747</v>
+        <v>78839</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443043</v>
+        <v>443017</v>
       </c>
       <c r="R87" t="n">
-        <v>6765047</v>
+        <v>6765118</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9952,10 +9952,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129565932</v>
+        <v>129566027</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9963,21 +9963,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>442724</v>
+        <v>443043</v>
       </c>
       <c r="R88" t="n">
-        <v>6765212</v>
+        <v>6765047</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10059,7 +10059,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129565902</v>
+        <v>129565932</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443010</v>
+        <v>442724</v>
       </c>
       <c r="R89" t="n">
-        <v>6765160</v>
+        <v>6765212</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129565976</v>
+        <v>129565902</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443332</v>
+        <v>443010</v>
       </c>
       <c r="R90" t="n">
-        <v>6765403</v>
+        <v>6765160</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10273,10 +10273,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129565849</v>
+        <v>129565976</v>
       </c>
       <c r="B91" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10284,21 +10284,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443033</v>
+        <v>443332</v>
       </c>
       <c r="R91" t="n">
-        <v>6765241</v>
+        <v>6765403</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10380,10 +10380,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129566005</v>
+        <v>129565849</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10391,21 +10391,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443160</v>
+        <v>443033</v>
       </c>
       <c r="R92" t="n">
-        <v>6765086</v>
+        <v>6765241</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10487,7 +10487,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129565899</v>
+        <v>129566005</v>
       </c>
       <c r="B93" t="n">
         <v>79081</v>
@@ -10522,10 +10522,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443088</v>
+        <v>443160</v>
       </c>
       <c r="R93" t="n">
-        <v>6765090</v>
+        <v>6765086</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10594,7 +10594,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129565956</v>
+        <v>129565899</v>
       </c>
       <c r="B94" t="n">
         <v>79081</v>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443366</v>
+        <v>443088</v>
       </c>
       <c r="R94" t="n">
-        <v>6765190</v>
+        <v>6765090</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,7 +10701,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129565961</v>
+        <v>129565956</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443405</v>
+        <v>443366</v>
       </c>
       <c r="R95" t="n">
-        <v>6765244</v>
+        <v>6765190</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10808,7 +10808,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129565966</v>
+        <v>129565961</v>
       </c>
       <c r="B96" t="n">
         <v>79081</v>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443432</v>
+        <v>443405</v>
       </c>
       <c r="R96" t="n">
-        <v>6765347</v>
+        <v>6765244</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10915,52 +10915,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129565784</v>
+        <v>129565966</v>
       </c>
       <c r="B97" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443093</v>
+        <v>443432</v>
       </c>
       <c r="R97" t="n">
-        <v>6765290</v>
+        <v>6765347</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10992,7 +10985,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11002,7 +10995,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11029,45 +11022,52 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129565844</v>
+        <v>129565784</v>
       </c>
       <c r="B98" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443017</v>
+        <v>443093</v>
       </c>
       <c r="R98" t="n">
-        <v>6765118</v>
+        <v>6765290</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12761,10 +12761,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129565800</v>
+        <v>129566030</v>
       </c>
       <c r="B114" t="n">
-        <v>57733</v>
+        <v>78747</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12772,39 +12772,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443020</v>
+        <v>443283</v>
       </c>
       <c r="R114" t="n">
-        <v>6764999</v>
+        <v>6765488</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12836,7 +12831,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12846,7 +12841,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12873,10 +12868,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129565892</v>
+        <v>129565800</v>
       </c>
       <c r="B115" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12884,34 +12879,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>442831</v>
+        <v>443020</v>
       </c>
       <c r="R115" t="n">
-        <v>6764873</v>
+        <v>6764999</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12980,10 +12980,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129565852</v>
+        <v>129565775</v>
       </c>
       <c r="B116" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12991,21 +12991,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13015,10 +13015,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443321</v>
+        <v>443250</v>
       </c>
       <c r="R116" t="n">
-        <v>6765425</v>
+        <v>6765209</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13087,10 +13087,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129565756</v>
+        <v>129565949</v>
       </c>
       <c r="B117" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13098,21 +13098,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13122,10 +13122,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443179</v>
+        <v>443110</v>
       </c>
       <c r="R117" t="n">
-        <v>6765294</v>
+        <v>6765023</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13194,7 +13194,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129565926</v>
+        <v>129565892</v>
       </c>
       <c r="B118" t="n">
         <v>79081</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>442748</v>
+        <v>442831</v>
       </c>
       <c r="R118" t="n">
-        <v>6765234</v>
+        <v>6764873</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13301,10 +13301,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129565992</v>
+        <v>129565852</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13312,21 +13312,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13336,10 +13336,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443143</v>
+        <v>443321</v>
       </c>
       <c r="R119" t="n">
-        <v>6765322</v>
+        <v>6765425</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13408,10 +13408,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129566008</v>
+        <v>129565756</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13419,21 +13419,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13443,10 +13443,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>442968</v>
+        <v>443179</v>
       </c>
       <c r="R120" t="n">
-        <v>6765088</v>
+        <v>6765294</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13515,10 +13515,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129565850</v>
+        <v>129565926</v>
       </c>
       <c r="B121" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13526,21 +13526,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13550,10 +13550,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443017</v>
+        <v>442748</v>
       </c>
       <c r="R121" t="n">
-        <v>6765114</v>
+        <v>6765234</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13622,10 +13622,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129565762</v>
+        <v>129565992</v>
       </c>
       <c r="B122" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13633,21 +13633,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>442861</v>
+        <v>443143</v>
       </c>
       <c r="R122" t="n">
-        <v>6764908</v>
+        <v>6765322</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13729,10 +13729,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129565755</v>
+        <v>129566008</v>
       </c>
       <c r="B123" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13740,21 +13740,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13764,10 +13764,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443282</v>
+        <v>442968</v>
       </c>
       <c r="R123" t="n">
-        <v>6765487</v>
+        <v>6765088</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13836,10 +13836,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129565775</v>
+        <v>129565850</v>
       </c>
       <c r="B124" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13847,21 +13847,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443250</v>
+        <v>443017</v>
       </c>
       <c r="R124" t="n">
-        <v>6765209</v>
+        <v>6765114</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13943,10 +13943,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129566030</v>
+        <v>129565762</v>
       </c>
       <c r="B125" t="n">
-        <v>78747</v>
+        <v>83052</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443283</v>
+        <v>442861</v>
       </c>
       <c r="R125" t="n">
-        <v>6765488</v>
+        <v>6764908</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14050,10 +14050,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129565949</v>
+        <v>129565755</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14061,21 +14061,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14085,10 +14085,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443110</v>
+        <v>443282</v>
       </c>
       <c r="R126" t="n">
-        <v>6765023</v>
+        <v>6765487</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -17501,45 +17501,50 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129565809</v>
+        <v>129565799</v>
       </c>
       <c r="B158" t="n">
-        <v>79148</v>
+        <v>57733</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>637</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>442863</v>
+        <v>443086</v>
       </c>
       <c r="R158" t="n">
-        <v>6764893</v>
+        <v>6765106</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17571,7 +17576,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17581,12 +17586,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>20-tal bålar inom 10 m på fem olika granar.</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17613,10 +17613,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129565799</v>
+        <v>129565967</v>
       </c>
       <c r="B159" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17624,39 +17624,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>443086</v>
+        <v>443420</v>
       </c>
       <c r="R159" t="n">
-        <v>6765106</v>
+        <v>6765366</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17688,7 +17683,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17698,7 +17693,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17725,7 +17720,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129565967</v>
+        <v>129565975</v>
       </c>
       <c r="B160" t="n">
         <v>79081</v>
@@ -17760,10 +17755,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>443420</v>
+        <v>443337</v>
       </c>
       <c r="R160" t="n">
-        <v>6765366</v>
+        <v>6765385</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17795,7 +17790,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17805,7 +17800,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17832,45 +17827,50 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129565975</v>
+        <v>129565823</v>
       </c>
       <c r="B161" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>443337</v>
+        <v>443008</v>
       </c>
       <c r="R161" t="n">
-        <v>6765385</v>
+        <v>6765154</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17902,7 +17902,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17939,32 +17939,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129565989</v>
+        <v>129565809</v>
       </c>
       <c r="B162" t="n">
-        <v>79081</v>
+        <v>79148</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17974,10 +17974,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>443256</v>
+        <v>442863</v>
       </c>
       <c r="R162" t="n">
-        <v>6765342</v>
+        <v>6764893</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18009,7 +18009,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18019,7 +18019,12 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>20-tal bålar inom 10 m på fem olika granar.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18046,7 +18051,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129565986</v>
+        <v>129565989</v>
       </c>
       <c r="B163" t="n">
         <v>79081</v>
@@ -18081,10 +18086,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>443319</v>
+        <v>443256</v>
       </c>
       <c r="R163" t="n">
-        <v>6765391</v>
+        <v>6765342</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18116,7 +18121,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18126,7 +18131,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18153,7 +18158,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129565952</v>
+        <v>129565986</v>
       </c>
       <c r="B164" t="n">
         <v>79081</v>
@@ -18188,10 +18193,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>443251</v>
+        <v>443319</v>
       </c>
       <c r="R164" t="n">
-        <v>6765117</v>
+        <v>6765391</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18223,7 +18228,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18233,7 +18238,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18260,7 +18265,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129565933</v>
+        <v>129565952</v>
       </c>
       <c r="B165" t="n">
         <v>79081</v>
@@ -18295,10 +18300,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>442711</v>
+        <v>443251</v>
       </c>
       <c r="R165" t="n">
-        <v>6765211</v>
+        <v>6765117</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18330,7 +18335,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18340,7 +18345,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18367,7 +18372,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129565928</v>
+        <v>129565933</v>
       </c>
       <c r="B166" t="n">
         <v>79081</v>
@@ -18402,10 +18407,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>442782</v>
+        <v>442711</v>
       </c>
       <c r="R166" t="n">
-        <v>6765222</v>
+        <v>6765211</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18437,7 +18442,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18447,7 +18452,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18474,7 +18479,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129565980</v>
+        <v>129565928</v>
       </c>
       <c r="B167" t="n">
         <v>79081</v>
@@ -18509,10 +18514,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>443299</v>
+        <v>442782</v>
       </c>
       <c r="R167" t="n">
-        <v>6765469</v>
+        <v>6765222</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18544,7 +18549,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18554,7 +18559,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18581,50 +18586,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129565823</v>
+        <v>129565980</v>
       </c>
       <c r="B168" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>443008</v>
+        <v>443299</v>
       </c>
       <c r="R168" t="n">
-        <v>6765154</v>
+        <v>6765469</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18656,7 +18656,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18693,50 +18693,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129565829</v>
+        <v>129566012</v>
       </c>
       <c r="B169" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>443008</v>
+        <v>442827</v>
       </c>
       <c r="R169" t="n">
-        <v>6765122</v>
+        <v>6764880</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18768,7 +18763,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18778,7 +18773,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18805,50 +18800,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129565828</v>
+        <v>129565910</v>
       </c>
       <c r="B170" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>443021</v>
+        <v>442825</v>
       </c>
       <c r="R170" t="n">
-        <v>6765053</v>
+        <v>6765266</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18880,7 +18870,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18890,7 +18880,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18917,50 +18907,45 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129565830</v>
+        <v>129565968</v>
       </c>
       <c r="B171" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>443009</v>
+        <v>443400</v>
       </c>
       <c r="R171" t="n">
-        <v>6765160</v>
+        <v>6765375</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18992,7 +18977,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19002,7 +18987,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19029,50 +19014,45 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129565822</v>
+        <v>129565929</v>
       </c>
       <c r="B172" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>443092</v>
+        <v>442823</v>
       </c>
       <c r="R172" t="n">
-        <v>6765061</v>
+        <v>6765181</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19104,7 +19084,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19114,7 +19094,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19141,45 +19121,50 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129566012</v>
+        <v>129565829</v>
       </c>
       <c r="B173" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>442827</v>
+        <v>443008</v>
       </c>
       <c r="R173" t="n">
-        <v>6764880</v>
+        <v>6765122</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19211,7 +19196,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19221,7 +19206,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19248,45 +19233,50 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129565910</v>
+        <v>129565828</v>
       </c>
       <c r="B174" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>442825</v>
+        <v>443021</v>
       </c>
       <c r="R174" t="n">
-        <v>6765266</v>
+        <v>6765053</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19318,7 +19308,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19328,7 +19318,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19355,45 +19345,50 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129565968</v>
+        <v>129565830</v>
       </c>
       <c r="B175" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>443400</v>
+        <v>443009</v>
       </c>
       <c r="R175" t="n">
-        <v>6765375</v>
+        <v>6765160</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19425,7 +19420,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19435,7 +19430,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19462,45 +19457,50 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129565929</v>
+        <v>129565822</v>
       </c>
       <c r="B176" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>442823</v>
+        <v>443092</v>
       </c>
       <c r="R176" t="n">
-        <v>6765181</v>
+        <v>6765061</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19569,10 +19569,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129565787</v>
+        <v>129566033</v>
       </c>
       <c r="B177" t="n">
-        <v>57896</v>
+        <v>78747</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19580,39 +19580,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>443283</v>
+        <v>443144</v>
       </c>
       <c r="R177" t="n">
-        <v>6765488</v>
+        <v>6765199</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19644,7 +19639,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19654,7 +19649,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19681,50 +19676,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129565833</v>
+        <v>129565879</v>
       </c>
       <c r="B178" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>442775</v>
+        <v>442749</v>
       </c>
       <c r="R178" t="n">
-        <v>6765271</v>
+        <v>6764886</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19756,7 +19746,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19766,7 +19756,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19793,10 +19783,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129565806</v>
+        <v>129565972</v>
       </c>
       <c r="B179" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19804,39 +19794,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>443430</v>
+        <v>443398</v>
       </c>
       <c r="R179" t="n">
-        <v>6765200</v>
+        <v>6765434</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19868,7 +19853,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19878,7 +19863,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19905,7 +19890,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129565971</v>
+        <v>129566002</v>
       </c>
       <c r="B180" t="n">
         <v>79081</v>
@@ -19940,10 +19925,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>443406</v>
+        <v>443134</v>
       </c>
       <c r="R180" t="n">
-        <v>6765450</v>
+        <v>6765184</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19975,7 +19960,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19985,7 +19970,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20012,10 +19997,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129566033</v>
+        <v>129565973</v>
       </c>
       <c r="B181" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20023,21 +20008,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20047,10 +20032,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>443144</v>
+        <v>443383</v>
       </c>
       <c r="R181" t="n">
-        <v>6765199</v>
+        <v>6765415</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20082,7 +20067,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20092,7 +20077,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20119,7 +20104,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129565879</v>
+        <v>129565927</v>
       </c>
       <c r="B182" t="n">
         <v>79081</v>
@@ -20154,10 +20139,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>442749</v>
+        <v>442770</v>
       </c>
       <c r="R182" t="n">
-        <v>6764886</v>
+        <v>6765225</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20189,7 +20174,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20199,7 +20184,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20226,7 +20211,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129565972</v>
+        <v>129565984</v>
       </c>
       <c r="B183" t="n">
         <v>79081</v>
@@ -20261,10 +20246,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>443398</v>
+        <v>443338</v>
       </c>
       <c r="R183" t="n">
-        <v>6765434</v>
+        <v>6765441</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20296,7 +20281,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20306,7 +20291,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20333,7 +20318,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129566002</v>
+        <v>129565912</v>
       </c>
       <c r="B184" t="n">
         <v>79081</v>
@@ -20368,10 +20353,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>443134</v>
+        <v>442776</v>
       </c>
       <c r="R184" t="n">
-        <v>6765184</v>
+        <v>6765280</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20403,7 +20388,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20413,7 +20398,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20440,10 +20425,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129565973</v>
+        <v>129565806</v>
       </c>
       <c r="B185" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20451,34 +20436,39 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>443383</v>
+        <v>443430</v>
       </c>
       <c r="R185" t="n">
-        <v>6765415</v>
+        <v>6765200</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20510,7 +20500,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20520,7 +20510,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20547,7 +20537,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129565927</v>
+        <v>129565971</v>
       </c>
       <c r="B186" t="n">
         <v>79081</v>
@@ -20582,10 +20572,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>442770</v>
+        <v>443406</v>
       </c>
       <c r="R186" t="n">
-        <v>6765225</v>
+        <v>6765450</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20617,7 +20607,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20627,7 +20617,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20654,10 +20644,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129565984</v>
+        <v>129565787</v>
       </c>
       <c r="B187" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20665,34 +20655,39 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>443338</v>
+        <v>443283</v>
       </c>
       <c r="R187" t="n">
-        <v>6765441</v>
+        <v>6765488</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20724,7 +20719,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20734,7 +20729,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20761,45 +20756,50 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129565912</v>
+        <v>129565833</v>
       </c>
       <c r="B188" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>442776</v>
+        <v>442775</v>
       </c>
       <c r="R188" t="n">
-        <v>6765280</v>
+        <v>6765271</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20831,7 +20831,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24307,50 +24307,45 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129565841</v>
+        <v>129565958</v>
       </c>
       <c r="B221" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>443266</v>
+        <v>443398</v>
       </c>
       <c r="R221" t="n">
-        <v>6765164</v>
+        <v>6765189</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24382,7 +24377,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24392,7 +24387,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24419,50 +24414,45 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129565748</v>
+        <v>129565877</v>
       </c>
       <c r="B222" t="n">
-        <v>5197</v>
+        <v>79081</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>443420</v>
+        <v>442708</v>
       </c>
       <c r="R222" t="n">
-        <v>6765200</v>
+        <v>6764885</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24494,7 +24484,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24504,7 +24494,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24531,50 +24521,45 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129565843</v>
+        <v>129565897</v>
       </c>
       <c r="B223" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>443077</v>
+        <v>443095</v>
       </c>
       <c r="R223" t="n">
-        <v>6765075</v>
+        <v>6765053</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24606,7 +24591,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24616,7 +24601,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24643,7 +24628,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129565958</v>
+        <v>129565864</v>
       </c>
       <c r="B224" t="n">
         <v>79081</v>
@@ -24678,10 +24663,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>443398</v>
+        <v>442678</v>
       </c>
       <c r="R224" t="n">
-        <v>6765189</v>
+        <v>6764817</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24713,7 +24698,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24723,7 +24708,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24750,45 +24735,50 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129565877</v>
+        <v>129565841</v>
       </c>
       <c r="B225" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>442708</v>
+        <v>443266</v>
       </c>
       <c r="R225" t="n">
-        <v>6764885</v>
+        <v>6765164</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24820,7 +24810,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24830,7 +24820,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24857,45 +24847,50 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129565897</v>
+        <v>129565748</v>
       </c>
       <c r="B226" t="n">
-        <v>79081</v>
+        <v>5197</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>443095</v>
+        <v>443420</v>
       </c>
       <c r="R226" t="n">
-        <v>6765053</v>
+        <v>6765200</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24927,7 +24922,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24937,7 +24932,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24964,7 +24959,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129565864</v>
+        <v>129565869</v>
       </c>
       <c r="B227" t="n">
         <v>79081</v>
@@ -24999,10 +24994,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>442678</v>
+        <v>442712</v>
       </c>
       <c r="R227" t="n">
-        <v>6764817</v>
+        <v>6764831</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25034,7 +25029,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25044,7 +25039,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25071,45 +25066,50 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129565869</v>
+        <v>129565831</v>
       </c>
       <c r="B228" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>442712</v>
+        <v>443008</v>
       </c>
       <c r="R228" t="n">
-        <v>6764831</v>
+        <v>6765171</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25151,7 +25151,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25178,7 +25178,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129565831</v>
+        <v>129565843</v>
       </c>
       <c r="B229" t="n">
         <v>8450</v>
@@ -25218,10 +25218,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>443008</v>
+        <v>443077</v>
       </c>
       <c r="R229" t="n">
-        <v>6765171</v>
+        <v>6765075</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25253,7 +25253,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25263,7 +25263,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD229" t="b">

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -8770,7 +8770,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129565941</v>
+        <v>129565953</v>
       </c>
       <c r="B77" t="n">
         <v>79081</v>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>442718</v>
+        <v>443326</v>
       </c>
       <c r="R77" t="n">
-        <v>6764837</v>
+        <v>6765167</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8877,7 +8877,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129565987</v>
+        <v>129565873</v>
       </c>
       <c r="B78" t="n">
         <v>79081</v>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443310</v>
+        <v>442684</v>
       </c>
       <c r="R78" t="n">
-        <v>6765374</v>
+        <v>6764865</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8984,7 +8984,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129565883</v>
+        <v>129565988</v>
       </c>
       <c r="B79" t="n">
         <v>79081</v>
@@ -9019,10 +9019,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442773</v>
+        <v>443284</v>
       </c>
       <c r="R79" t="n">
-        <v>6764941</v>
+        <v>6765343</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9091,7 +9091,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129565979</v>
+        <v>129565914</v>
       </c>
       <c r="B80" t="n">
         <v>79081</v>
@@ -9126,10 +9126,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443306</v>
+        <v>442770</v>
       </c>
       <c r="R80" t="n">
-        <v>6765458</v>
+        <v>6765256</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9198,7 +9198,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129565930</v>
+        <v>129565941</v>
       </c>
       <c r="B81" t="n">
         <v>79081</v>
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>442768</v>
+        <v>442718</v>
       </c>
       <c r="R81" t="n">
-        <v>6765164</v>
+        <v>6764837</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9305,50 +9305,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129565820</v>
+        <v>129565987</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443109</v>
+        <v>443310</v>
       </c>
       <c r="R82" t="n">
-        <v>6765024</v>
+        <v>6765374</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9380,7 +9375,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9390,7 +9385,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9417,7 +9412,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129565953</v>
+        <v>129565883</v>
       </c>
       <c r="B83" t="n">
         <v>79081</v>
@@ -9452,10 +9447,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443326</v>
+        <v>442773</v>
       </c>
       <c r="R83" t="n">
-        <v>6765167</v>
+        <v>6764941</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9487,7 +9482,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9497,7 +9492,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9524,7 +9519,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129565873</v>
+        <v>129565979</v>
       </c>
       <c r="B84" t="n">
         <v>79081</v>
@@ -9559,10 +9554,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>442684</v>
+        <v>443306</v>
       </c>
       <c r="R84" t="n">
-        <v>6764865</v>
+        <v>6765458</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9594,7 +9589,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9604,7 +9599,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9631,7 +9626,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129565988</v>
+        <v>129565930</v>
       </c>
       <c r="B85" t="n">
         <v>79081</v>
@@ -9666,10 +9661,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443284</v>
+        <v>442768</v>
       </c>
       <c r="R85" t="n">
-        <v>6765343</v>
+        <v>6765164</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9701,7 +9696,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9711,7 +9706,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9738,45 +9733,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129565914</v>
+        <v>129565820</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>442770</v>
+        <v>443109</v>
       </c>
       <c r="R86" t="n">
-        <v>6765256</v>
+        <v>6765024</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12761,10 +12761,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129566030</v>
+        <v>129565800</v>
       </c>
       <c r="B114" t="n">
-        <v>78747</v>
+        <v>57733</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12772,34 +12772,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443283</v>
+        <v>443020</v>
       </c>
       <c r="R114" t="n">
-        <v>6765488</v>
+        <v>6764999</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12831,7 +12836,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12841,7 +12846,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12868,10 +12873,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129565800</v>
+        <v>129565892</v>
       </c>
       <c r="B115" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12879,39 +12884,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443020</v>
+        <v>442831</v>
       </c>
       <c r="R115" t="n">
-        <v>6764999</v>
+        <v>6764873</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12980,10 +12980,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129565775</v>
+        <v>129565852</v>
       </c>
       <c r="B116" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12991,21 +12991,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13015,10 +13015,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443250</v>
+        <v>443321</v>
       </c>
       <c r="R116" t="n">
-        <v>6765209</v>
+        <v>6765425</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13087,10 +13087,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129565949</v>
+        <v>129565756</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13098,21 +13098,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13122,10 +13122,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443110</v>
+        <v>443179</v>
       </c>
       <c r="R117" t="n">
-        <v>6765023</v>
+        <v>6765294</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13194,7 +13194,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129565892</v>
+        <v>129565926</v>
       </c>
       <c r="B118" t="n">
         <v>79081</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>442831</v>
+        <v>442748</v>
       </c>
       <c r="R118" t="n">
-        <v>6764873</v>
+        <v>6765234</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13301,10 +13301,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129565852</v>
+        <v>129565992</v>
       </c>
       <c r="B119" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13312,21 +13312,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13336,10 +13336,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443321</v>
+        <v>443143</v>
       </c>
       <c r="R119" t="n">
-        <v>6765425</v>
+        <v>6765322</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13408,10 +13408,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129565756</v>
+        <v>129566008</v>
       </c>
       <c r="B120" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13419,21 +13419,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13443,10 +13443,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443179</v>
+        <v>442968</v>
       </c>
       <c r="R120" t="n">
-        <v>6765294</v>
+        <v>6765088</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13515,10 +13515,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129565926</v>
+        <v>129565850</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13526,21 +13526,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13550,10 +13550,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>442748</v>
+        <v>443017</v>
       </c>
       <c r="R121" t="n">
-        <v>6765234</v>
+        <v>6765114</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13622,10 +13622,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129565992</v>
+        <v>129565762</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13633,21 +13633,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443143</v>
+        <v>442861</v>
       </c>
       <c r="R122" t="n">
-        <v>6765322</v>
+        <v>6764908</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13729,10 +13729,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129566008</v>
+        <v>129565755</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13740,21 +13740,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13764,10 +13764,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>442968</v>
+        <v>443282</v>
       </c>
       <c r="R123" t="n">
-        <v>6765088</v>
+        <v>6765487</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13836,10 +13836,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129565850</v>
+        <v>129565775</v>
       </c>
       <c r="B124" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13847,21 +13847,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443017</v>
+        <v>443250</v>
       </c>
       <c r="R124" t="n">
-        <v>6765114</v>
+        <v>6765209</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13943,10 +13943,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129565762</v>
+        <v>129566030</v>
       </c>
       <c r="B125" t="n">
-        <v>83052</v>
+        <v>78747</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>442861</v>
+        <v>443283</v>
       </c>
       <c r="R125" t="n">
-        <v>6764908</v>
+        <v>6765488</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14050,10 +14050,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129565755</v>
+        <v>129565949</v>
       </c>
       <c r="B126" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14061,21 +14061,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14085,10 +14085,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443282</v>
+        <v>443110</v>
       </c>
       <c r="R126" t="n">
-        <v>6765487</v>
+        <v>6765023</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -21836,10 +21836,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129565803</v>
+        <v>129565763</v>
       </c>
       <c r="B198" t="n">
-        <v>57733</v>
+        <v>79113</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21847,39 +21847,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>443250</v>
+        <v>443051</v>
       </c>
       <c r="R198" t="n">
-        <v>6765211</v>
+        <v>6765229</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21911,7 +21906,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21921,7 +21916,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21948,10 +21943,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129565807</v>
+        <v>129565817</v>
       </c>
       <c r="B199" t="n">
-        <v>57733</v>
+        <v>92919</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21959,39 +21954,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>442850</v>
+        <v>442767</v>
       </c>
       <c r="R199" t="n">
-        <v>6764898</v>
+        <v>6765229</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22023,7 +22013,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22033,7 +22023,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22060,10 +22050,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129565763</v>
+        <v>129565919</v>
       </c>
       <c r="B200" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22071,21 +22061,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22095,10 +22085,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>443051</v>
+        <v>442733</v>
       </c>
       <c r="R200" t="n">
-        <v>6765229</v>
+        <v>6765274</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22130,7 +22120,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22140,7 +22130,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22167,10 +22157,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129565817</v>
+        <v>129565950</v>
       </c>
       <c r="B201" t="n">
-        <v>92919</v>
+        <v>79081</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22178,21 +22168,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22202,10 +22192,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>442767</v>
+        <v>443156</v>
       </c>
       <c r="R201" t="n">
-        <v>6765229</v>
+        <v>6765060</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22237,7 +22227,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22247,7 +22237,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22274,7 +22264,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129565919</v>
+        <v>129565908</v>
       </c>
       <c r="B202" t="n">
         <v>79081</v>
@@ -22309,10 +22299,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>442733</v>
+        <v>442859</v>
       </c>
       <c r="R202" t="n">
-        <v>6765274</v>
+        <v>6765277</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22344,7 +22334,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22354,7 +22344,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22381,7 +22371,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129565950</v>
+        <v>129565981</v>
       </c>
       <c r="B203" t="n">
         <v>79081</v>
@@ -22416,10 +22406,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>443156</v>
+        <v>443294</v>
       </c>
       <c r="R203" t="n">
-        <v>6765060</v>
+        <v>6765505</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22451,7 +22441,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22461,7 +22451,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22488,7 +22478,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129565908</v>
+        <v>129565955</v>
       </c>
       <c r="B204" t="n">
         <v>79081</v>
@@ -22523,10 +22513,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>442859</v>
+        <v>443351</v>
       </c>
       <c r="R204" t="n">
-        <v>6765277</v>
+        <v>6765163</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22558,7 +22548,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22568,7 +22558,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22595,7 +22585,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129565981</v>
+        <v>129565894</v>
       </c>
       <c r="B205" t="n">
         <v>79081</v>
@@ -22630,10 +22620,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>443294</v>
+        <v>442973</v>
       </c>
       <c r="R205" t="n">
-        <v>6765505</v>
+        <v>6764957</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22665,7 +22655,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22675,7 +22665,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22702,7 +22692,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129565955</v>
+        <v>129565907</v>
       </c>
       <c r="B206" t="n">
         <v>79081</v>
@@ -22737,10 +22727,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>443351</v>
+        <v>442863</v>
       </c>
       <c r="R206" t="n">
-        <v>6765163</v>
+        <v>6765287</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22772,7 +22762,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22782,7 +22772,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22809,10 +22799,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129565894</v>
+        <v>129565803</v>
       </c>
       <c r="B207" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22820,34 +22810,39 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>442973</v>
+        <v>443250</v>
       </c>
       <c r="R207" t="n">
-        <v>6764957</v>
+        <v>6765211</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22879,7 +22874,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22889,7 +22884,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22916,10 +22911,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129565907</v>
+        <v>129565807</v>
       </c>
       <c r="B208" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22927,34 +22922,39 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>442863</v>
+        <v>442850</v>
       </c>
       <c r="R208" t="n">
-        <v>6765287</v>
+        <v>6764898</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22986,7 +22986,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24307,45 +24307,50 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129565958</v>
+        <v>129565841</v>
       </c>
       <c r="B221" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>443398</v>
+        <v>443266</v>
       </c>
       <c r="R221" t="n">
-        <v>6765189</v>
+        <v>6765164</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24377,7 +24382,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24387,7 +24392,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24414,45 +24419,50 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129565877</v>
+        <v>129565748</v>
       </c>
       <c r="B222" t="n">
-        <v>79081</v>
+        <v>5197</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>442708</v>
+        <v>443420</v>
       </c>
       <c r="R222" t="n">
-        <v>6764885</v>
+        <v>6765200</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24484,7 +24494,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24494,7 +24504,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24521,45 +24531,50 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129565897</v>
+        <v>129565843</v>
       </c>
       <c r="B223" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>443095</v>
+        <v>443077</v>
       </c>
       <c r="R223" t="n">
-        <v>6765053</v>
+        <v>6765075</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24591,7 +24606,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24601,7 +24616,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24628,7 +24643,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129565864</v>
+        <v>129565958</v>
       </c>
       <c r="B224" t="n">
         <v>79081</v>
@@ -24663,10 +24678,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>442678</v>
+        <v>443398</v>
       </c>
       <c r="R224" t="n">
-        <v>6764817</v>
+        <v>6765189</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24698,7 +24713,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24708,7 +24723,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24735,50 +24750,45 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129565841</v>
+        <v>129565877</v>
       </c>
       <c r="B225" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>443266</v>
+        <v>442708</v>
       </c>
       <c r="R225" t="n">
-        <v>6765164</v>
+        <v>6764885</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24810,7 +24820,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24820,7 +24830,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24847,50 +24857,45 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129565748</v>
+        <v>129565897</v>
       </c>
       <c r="B226" t="n">
-        <v>5197</v>
+        <v>79081</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>443420</v>
+        <v>443095</v>
       </c>
       <c r="R226" t="n">
-        <v>6765200</v>
+        <v>6765053</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24922,7 +24927,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24932,7 +24937,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24959,7 +24964,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129565869</v>
+        <v>129565864</v>
       </c>
       <c r="B227" t="n">
         <v>79081</v>
@@ -24994,10 +24999,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>442712</v>
+        <v>442678</v>
       </c>
       <c r="R227" t="n">
-        <v>6764831</v>
+        <v>6764817</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25029,7 +25034,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25039,7 +25044,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25066,50 +25071,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129565831</v>
+        <v>129565869</v>
       </c>
       <c r="B228" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>443008</v>
+        <v>442712</v>
       </c>
       <c r="R228" t="n">
-        <v>6765171</v>
+        <v>6764831</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25151,7 +25151,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25178,7 +25178,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129565843</v>
+        <v>129565831</v>
       </c>
       <c r="B229" t="n">
         <v>8450</v>
@@ -25218,10 +25218,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>443077</v>
+        <v>443008</v>
       </c>
       <c r="R229" t="n">
-        <v>6765075</v>
+        <v>6765171</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25253,7 +25253,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25263,7 +25263,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD229" t="b">

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -24307,50 +24307,45 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129565841</v>
+        <v>129565958</v>
       </c>
       <c r="B221" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>443266</v>
+        <v>443398</v>
       </c>
       <c r="R221" t="n">
-        <v>6765164</v>
+        <v>6765189</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24382,7 +24377,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24392,7 +24387,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24419,50 +24414,45 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129565748</v>
+        <v>129565877</v>
       </c>
       <c r="B222" t="n">
-        <v>5197</v>
+        <v>79081</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>443420</v>
+        <v>442708</v>
       </c>
       <c r="R222" t="n">
-        <v>6765200</v>
+        <v>6764885</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24494,7 +24484,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24504,7 +24494,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24531,50 +24521,45 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129565843</v>
+        <v>129565897</v>
       </c>
       <c r="B223" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>443077</v>
+        <v>443095</v>
       </c>
       <c r="R223" t="n">
-        <v>6765075</v>
+        <v>6765053</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24606,7 +24591,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24616,7 +24601,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24643,7 +24628,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129565958</v>
+        <v>129565864</v>
       </c>
       <c r="B224" t="n">
         <v>79081</v>
@@ -24678,10 +24663,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>443398</v>
+        <v>442678</v>
       </c>
       <c r="R224" t="n">
-        <v>6765189</v>
+        <v>6764817</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24713,7 +24698,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24723,7 +24708,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24750,45 +24735,50 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129565877</v>
+        <v>129565841</v>
       </c>
       <c r="B225" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>442708</v>
+        <v>443266</v>
       </c>
       <c r="R225" t="n">
-        <v>6764885</v>
+        <v>6765164</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24820,7 +24810,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24830,7 +24820,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24857,45 +24847,50 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129565897</v>
+        <v>129565748</v>
       </c>
       <c r="B226" t="n">
-        <v>79081</v>
+        <v>5197</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>443095</v>
+        <v>443420</v>
       </c>
       <c r="R226" t="n">
-        <v>6765053</v>
+        <v>6765200</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24927,7 +24922,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24937,7 +24932,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24964,7 +24959,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129565864</v>
+        <v>129565869</v>
       </c>
       <c r="B227" t="n">
         <v>79081</v>
@@ -24999,10 +24994,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>442678</v>
+        <v>442712</v>
       </c>
       <c r="R227" t="n">
-        <v>6764817</v>
+        <v>6764831</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25034,7 +25029,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25044,7 +25039,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25071,45 +25066,50 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129565869</v>
+        <v>129565831</v>
       </c>
       <c r="B228" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>442712</v>
+        <v>443008</v>
       </c>
       <c r="R228" t="n">
-        <v>6764831</v>
+        <v>6765171</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25151,7 +25151,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25178,7 +25178,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129565831</v>
+        <v>129565843</v>
       </c>
       <c r="B229" t="n">
         <v>8450</v>
@@ -25218,10 +25218,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>443008</v>
+        <v>443077</v>
       </c>
       <c r="R229" t="n">
-        <v>6765171</v>
+        <v>6765075</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25253,7 +25253,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25263,7 +25263,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD229" t="b">

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -6175,7 +6175,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129566007</v>
+        <v>129565880</v>
       </c>
       <c r="B53" t="n">
         <v>79081</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442988</v>
+        <v>442751</v>
       </c>
       <c r="R53" t="n">
-        <v>6765104</v>
+        <v>6764908</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6282,10 +6282,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129565880</v>
+        <v>129565804</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6293,34 +6293,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442751</v>
+        <v>442847</v>
       </c>
       <c r="R54" t="n">
-        <v>6764908</v>
+        <v>6765272</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6352,7 +6357,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6362,7 +6367,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6389,7 +6394,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129565969</v>
+        <v>129565957</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -6424,10 +6429,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443402</v>
+        <v>443383</v>
       </c>
       <c r="R55" t="n">
-        <v>6765392</v>
+        <v>6765197</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6459,7 +6464,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6469,7 +6474,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6496,7 +6501,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129565957</v>
+        <v>129565917</v>
       </c>
       <c r="B56" t="n">
         <v>79081</v>
@@ -6531,10 +6536,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443383</v>
+        <v>442736</v>
       </c>
       <c r="R56" t="n">
-        <v>6765197</v>
+        <v>6765272</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6566,7 +6571,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6576,7 +6581,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6603,7 +6608,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129565917</v>
+        <v>129566007</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6638,10 +6643,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442736</v>
+        <v>442988</v>
       </c>
       <c r="R57" t="n">
-        <v>6765272</v>
+        <v>6765104</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6673,7 +6678,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6683,7 +6688,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6817,10 +6822,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129565804</v>
+        <v>129565969</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6828,39 +6833,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442847</v>
+        <v>443402</v>
       </c>
       <c r="R59" t="n">
-        <v>6765272</v>
+        <v>6765392</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7036,45 +7036,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129566003</v>
+        <v>129565786</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443142</v>
+        <v>443115</v>
       </c>
       <c r="R61" t="n">
-        <v>6765165</v>
+        <v>6765337</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7106,7 +7118,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7116,7 +7128,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7143,7 +7155,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129565882</v>
+        <v>129566003</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -7178,10 +7190,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442762</v>
+        <v>443142</v>
       </c>
       <c r="R62" t="n">
-        <v>6764920</v>
+        <v>6765165</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7213,7 +7225,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7223,7 +7235,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7250,10 +7262,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129565788</v>
+        <v>129565882</v>
       </c>
       <c r="B63" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7261,21 +7273,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7285,10 +7297,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442726</v>
+        <v>442762</v>
       </c>
       <c r="R63" t="n">
-        <v>6764799</v>
+        <v>6764920</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7320,7 +7332,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7330,7 +7342,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7357,10 +7369,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129565865</v>
+        <v>129565788</v>
       </c>
       <c r="B64" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7368,21 +7380,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7392,10 +7404,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442669</v>
+        <v>442726</v>
       </c>
       <c r="R64" t="n">
-        <v>6764828</v>
+        <v>6764799</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7427,7 +7439,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7437,7 +7449,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7464,10 +7476,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129565761</v>
+        <v>129565865</v>
       </c>
       <c r="B65" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7475,21 +7487,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7499,10 +7511,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442685</v>
+        <v>442669</v>
       </c>
       <c r="R65" t="n">
-        <v>6764849</v>
+        <v>6764828</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7534,7 +7546,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7544,7 +7556,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7571,57 +7583,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129565786</v>
+        <v>129565761</v>
       </c>
       <c r="B66" t="n">
-        <v>56926</v>
+        <v>83052</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443115</v>
+        <v>442685</v>
       </c>
       <c r="R66" t="n">
-        <v>6765337</v>
+        <v>6764849</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7802,10 +7802,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129565847</v>
+        <v>129566017</v>
       </c>
       <c r="B68" t="n">
-        <v>81066</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7813,21 +7813,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443068</v>
+        <v>442707</v>
       </c>
       <c r="R68" t="n">
-        <v>6765019</v>
+        <v>6764791</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7909,10 +7909,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129565801</v>
+        <v>129565911</v>
       </c>
       <c r="B69" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7920,39 +7920,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443258</v>
+        <v>442817</v>
       </c>
       <c r="R69" t="n">
-        <v>6765343</v>
+        <v>6765276</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7984,7 +7979,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7994,7 +7989,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8021,7 +8016,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129566017</v>
+        <v>129565866</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -8056,10 +8051,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>442707</v>
+        <v>442685</v>
       </c>
       <c r="R70" t="n">
-        <v>6764791</v>
+        <v>6764827</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8091,7 +8086,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8101,7 +8096,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8128,7 +8123,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129565911</v>
+        <v>129565994</v>
       </c>
       <c r="B71" t="n">
         <v>79081</v>
@@ -8163,10 +8158,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>442817</v>
+        <v>443076</v>
       </c>
       <c r="R71" t="n">
-        <v>6765276</v>
+        <v>6765364</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8198,7 +8193,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8208,7 +8203,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8235,7 +8230,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129565866</v>
+        <v>129565978</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -8270,10 +8265,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>442685</v>
+        <v>443303</v>
       </c>
       <c r="R72" t="n">
-        <v>6764827</v>
+        <v>6765447</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8305,7 +8300,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8315,7 +8310,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8342,7 +8337,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129565994</v>
+        <v>129565903</v>
       </c>
       <c r="B73" t="n">
         <v>79081</v>
@@ -8377,10 +8372,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443076</v>
+        <v>443051</v>
       </c>
       <c r="R73" t="n">
-        <v>6765364</v>
+        <v>6765229</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8412,7 +8407,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8422,7 +8417,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8449,7 +8444,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129565978</v>
+        <v>129565993</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -8484,10 +8479,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443303</v>
+        <v>443126</v>
       </c>
       <c r="R74" t="n">
-        <v>6765447</v>
+        <v>6765359</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8519,7 +8514,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8529,7 +8524,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8556,10 +8551,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129565903</v>
+        <v>129565847</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>81066</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8567,21 +8562,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8591,10 +8586,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443051</v>
+        <v>443068</v>
       </c>
       <c r="R75" t="n">
-        <v>6765229</v>
+        <v>6765019</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8626,7 +8621,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8636,7 +8631,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8663,10 +8658,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129565993</v>
+        <v>129565801</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8674,34 +8669,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443126</v>
+        <v>443258</v>
       </c>
       <c r="R76" t="n">
-        <v>6765359</v>
+        <v>6765343</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9845,10 +9845,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129566027</v>
+        <v>129565932</v>
       </c>
       <c r="B87" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443043</v>
+        <v>442724</v>
       </c>
       <c r="R87" t="n">
-        <v>6765047</v>
+        <v>6765212</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9952,10 +9952,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129565849</v>
+        <v>129565966</v>
       </c>
       <c r="B88" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9963,21 +9963,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443033</v>
+        <v>443432</v>
       </c>
       <c r="R88" t="n">
-        <v>6765241</v>
+        <v>6765347</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10059,52 +10059,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129565784</v>
+        <v>129565902</v>
       </c>
       <c r="B89" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443093</v>
+        <v>443010</v>
       </c>
       <c r="R89" t="n">
-        <v>6765290</v>
+        <v>6765160</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10136,7 +10129,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10146,7 +10139,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10173,7 +10166,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129565932</v>
+        <v>129565976</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -10208,10 +10201,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>442724</v>
+        <v>443332</v>
       </c>
       <c r="R90" t="n">
-        <v>6765212</v>
+        <v>6765403</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10243,7 +10236,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10253,7 +10246,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10280,7 +10273,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129565966</v>
+        <v>129565956</v>
       </c>
       <c r="B91" t="n">
         <v>79081</v>
@@ -10315,10 +10308,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443432</v>
+        <v>443366</v>
       </c>
       <c r="R91" t="n">
-        <v>6765347</v>
+        <v>6765190</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10350,7 +10343,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10360,7 +10353,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10387,7 +10380,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129565902</v>
+        <v>129565961</v>
       </c>
       <c r="B92" t="n">
         <v>79081</v>
@@ -10422,10 +10415,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443010</v>
+        <v>443405</v>
       </c>
       <c r="R92" t="n">
-        <v>6765160</v>
+        <v>6765244</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10457,7 +10450,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10467,7 +10460,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10494,7 +10487,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129565976</v>
+        <v>129566005</v>
       </c>
       <c r="B93" t="n">
         <v>79081</v>
@@ -10529,10 +10522,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443332</v>
+        <v>443160</v>
       </c>
       <c r="R93" t="n">
-        <v>6765403</v>
+        <v>6765086</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10564,7 +10557,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10574,7 +10567,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10601,7 +10594,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129565956</v>
+        <v>129565899</v>
       </c>
       <c r="B94" t="n">
         <v>79081</v>
@@ -10636,10 +10629,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443366</v>
+        <v>443088</v>
       </c>
       <c r="R94" t="n">
-        <v>6765190</v>
+        <v>6765090</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10671,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10681,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10708,10 +10701,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129565961</v>
+        <v>129566027</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10719,21 +10712,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10743,10 +10736,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443405</v>
+        <v>443043</v>
       </c>
       <c r="R95" t="n">
-        <v>6765244</v>
+        <v>6765047</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10778,7 +10771,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10788,7 +10781,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10815,10 +10808,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129566005</v>
+        <v>129565849</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10826,21 +10819,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10850,10 +10843,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443160</v>
+        <v>443033</v>
       </c>
       <c r="R96" t="n">
-        <v>6765086</v>
+        <v>6765241</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10885,7 +10878,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10895,7 +10888,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10922,10 +10915,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129565899</v>
+        <v>129565844</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10933,21 +10926,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10957,10 +10950,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443088</v>
+        <v>443017</v>
       </c>
       <c r="R97" t="n">
-        <v>6765090</v>
+        <v>6765118</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10992,7 +10985,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11002,7 +10995,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11029,45 +11022,52 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129565844</v>
+        <v>129565784</v>
       </c>
       <c r="B98" t="n">
-        <v>78839</v>
+        <v>56926</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443017</v>
+        <v>443093</v>
       </c>
       <c r="R98" t="n">
-        <v>6765118</v>
+        <v>6765290</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13296,10 +13296,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129565852</v>
+        <v>129566030</v>
       </c>
       <c r="B119" t="n">
-        <v>78838</v>
+        <v>78747</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13307,21 +13307,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13331,10 +13331,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443321</v>
+        <v>443283</v>
       </c>
       <c r="R119" t="n">
-        <v>6765425</v>
+        <v>6765488</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13366,7 +13366,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13403,10 +13403,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129565762</v>
+        <v>129565756</v>
       </c>
       <c r="B120" t="n">
-        <v>83052</v>
+        <v>79700</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13414,21 +13414,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13438,10 +13438,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>442861</v>
+        <v>443179</v>
       </c>
       <c r="R120" t="n">
-        <v>6764908</v>
+        <v>6765294</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13473,7 +13473,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13510,10 +13510,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129565755</v>
+        <v>129565852</v>
       </c>
       <c r="B121" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13521,21 +13521,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13545,10 +13545,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443282</v>
+        <v>443321</v>
       </c>
       <c r="R121" t="n">
-        <v>6765487</v>
+        <v>6765425</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13617,10 +13617,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129565800</v>
+        <v>129565762</v>
       </c>
       <c r="B122" t="n">
-        <v>57733</v>
+        <v>83052</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13628,39 +13628,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443020</v>
+        <v>442861</v>
       </c>
       <c r="R122" t="n">
-        <v>6764999</v>
+        <v>6764908</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13692,7 +13687,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13702,7 +13697,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13729,10 +13724,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129565775</v>
+        <v>129565850</v>
       </c>
       <c r="B123" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13740,21 +13735,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13764,10 +13759,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443250</v>
+        <v>443017</v>
       </c>
       <c r="R123" t="n">
-        <v>6765209</v>
+        <v>6765114</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13799,7 +13794,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13809,7 +13804,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13836,7 +13831,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129565756</v>
+        <v>129565755</v>
       </c>
       <c r="B124" t="n">
         <v>79700</v>
@@ -13871,10 +13866,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443179</v>
+        <v>443282</v>
       </c>
       <c r="R124" t="n">
-        <v>6765294</v>
+        <v>6765487</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13906,7 +13901,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13916,7 +13911,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13943,10 +13938,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129566030</v>
+        <v>129565800</v>
       </c>
       <c r="B125" t="n">
-        <v>78747</v>
+        <v>57733</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13954,34 +13949,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443283</v>
+        <v>443020</v>
       </c>
       <c r="R125" t="n">
-        <v>6765488</v>
+        <v>6764999</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14050,10 +14050,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129565850</v>
+        <v>129565775</v>
       </c>
       <c r="B126" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14061,21 +14061,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14085,10 +14085,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443017</v>
+        <v>443250</v>
       </c>
       <c r="R126" t="n">
-        <v>6765114</v>
+        <v>6765209</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -20975,45 +20975,50 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129566024</v>
+        <v>129565826</v>
       </c>
       <c r="B190" t="n">
-        <v>78747</v>
+        <v>8450</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>443088</v>
+        <v>443073</v>
       </c>
       <c r="R190" t="n">
-        <v>6765114</v>
+        <v>6765287</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21045,7 +21050,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21055,12 +21060,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsyn</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129565963</v>
+        <v>129565846</v>
       </c>
       <c r="B191" t="n">
-        <v>79081</v>
+        <v>92018</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21098,21 +21098,16 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21122,10 +21117,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>443410</v>
+        <v>443405</v>
       </c>
       <c r="R191" t="n">
-        <v>6765453</v>
+        <v>6765306</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21157,7 +21152,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21167,7 +21162,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21194,10 +21189,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129566009</v>
+        <v>129565771</v>
       </c>
       <c r="B192" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21205,21 +21200,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21229,10 +21224,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>442846</v>
+        <v>443081</v>
       </c>
       <c r="R192" t="n">
-        <v>6764891</v>
+        <v>6765117</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21264,7 +21259,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21274,7 +21269,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21301,10 +21296,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129566001</v>
+        <v>129566024</v>
       </c>
       <c r="B193" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21312,21 +21307,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21336,10 +21331,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443140</v>
+        <v>443088</v>
       </c>
       <c r="R193" t="n">
-        <v>6765218</v>
+        <v>6765114</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21371,7 +21366,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21381,7 +21376,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsyn</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21408,7 +21408,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129565878</v>
+        <v>129565963</v>
       </c>
       <c r="B194" t="n">
         <v>79081</v>
@@ -21443,10 +21443,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>442745</v>
+        <v>443410</v>
       </c>
       <c r="R194" t="n">
-        <v>6764895</v>
+        <v>6765453</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21478,7 +21478,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21488,7 +21488,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21515,10 +21515,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129565771</v>
+        <v>129566009</v>
       </c>
       <c r="B195" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21526,21 +21526,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21550,10 +21550,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443081</v>
+        <v>442846</v>
       </c>
       <c r="R195" t="n">
-        <v>6765117</v>
+        <v>6764891</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21595,7 +21595,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21622,50 +21622,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129565826</v>
+        <v>129566001</v>
       </c>
       <c r="B196" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443073</v>
+        <v>443140</v>
       </c>
       <c r="R196" t="n">
-        <v>6765287</v>
+        <v>6765218</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21697,7 +21692,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21707,7 +21702,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21734,10 +21729,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129565846</v>
+        <v>129565878</v>
       </c>
       <c r="B197" t="n">
-        <v>92018</v>
+        <v>79081</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21745,16 +21740,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21764,10 +21764,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>443405</v>
+        <v>442745</v>
       </c>
       <c r="R197" t="n">
-        <v>6765306</v>
+        <v>6764895</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21809,7 +21809,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -23023,10 +23023,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129565798</v>
+        <v>129565982</v>
       </c>
       <c r="B209" t="n">
-        <v>91550</v>
+        <v>79081</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23034,21 +23034,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23058,10 +23058,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>442855</v>
+        <v>443328</v>
       </c>
       <c r="R209" t="n">
-        <v>6764903</v>
+        <v>6765500</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23093,7 +23093,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23130,10 +23130,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129565848</v>
+        <v>129565916</v>
       </c>
       <c r="B210" t="n">
-        <v>81066</v>
+        <v>79081</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23141,21 +23141,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23165,10 +23165,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>443251</v>
+        <v>442750</v>
       </c>
       <c r="R210" t="n">
-        <v>6765208</v>
+        <v>6765268</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23200,7 +23200,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23237,7 +23237,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129565982</v>
+        <v>129565872</v>
       </c>
       <c r="B211" t="n">
         <v>79081</v>
@@ -23272,10 +23272,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>443328</v>
+        <v>442685</v>
       </c>
       <c r="R211" t="n">
-        <v>6765500</v>
+        <v>6764849</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23307,7 +23307,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23344,7 +23344,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129565916</v>
+        <v>129566000</v>
       </c>
       <c r="B212" t="n">
         <v>79081</v>
@@ -23379,10 +23379,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>442750</v>
+        <v>443144</v>
       </c>
       <c r="R212" t="n">
-        <v>6765268</v>
+        <v>6765233</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23451,7 +23451,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129565872</v>
+        <v>129565881</v>
       </c>
       <c r="B213" t="n">
         <v>79081</v>
@@ -23486,10 +23486,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>442685</v>
+        <v>442754</v>
       </c>
       <c r="R213" t="n">
-        <v>6764849</v>
+        <v>6764914</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23558,7 +23558,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129566000</v>
+        <v>129565924</v>
       </c>
       <c r="B214" t="n">
         <v>79081</v>
@@ -23593,10 +23593,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>443144</v>
+        <v>442729</v>
       </c>
       <c r="R214" t="n">
-        <v>6765233</v>
+        <v>6765242</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23628,7 +23628,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23665,7 +23665,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129565881</v>
+        <v>129565970</v>
       </c>
       <c r="B215" t="n">
         <v>79081</v>
@@ -23700,10 +23700,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>442754</v>
+        <v>443416</v>
       </c>
       <c r="R215" t="n">
-        <v>6764914</v>
+        <v>6765453</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23745,7 +23745,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23772,10 +23772,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129565924</v>
+        <v>129565798</v>
       </c>
       <c r="B216" t="n">
-        <v>79081</v>
+        <v>91550</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23783,21 +23783,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -23807,10 +23807,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>442729</v>
+        <v>442855</v>
       </c>
       <c r="R216" t="n">
-        <v>6765242</v>
+        <v>6764903</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23852,7 +23852,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23879,10 +23879,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129565970</v>
+        <v>129565848</v>
       </c>
       <c r="B217" t="n">
-        <v>79081</v>
+        <v>81066</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23890,21 +23890,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23914,10 +23914,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>443416</v>
+        <v>443251</v>
       </c>
       <c r="R217" t="n">
-        <v>6765453</v>
+        <v>6765208</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -23959,7 +23959,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD217" t="b">

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -7036,10 +7036,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129565786</v>
+        <v>129565824</v>
       </c>
       <c r="B61" t="n">
-        <v>56926</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7047,46 +7047,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443115</v>
+        <v>443207</v>
       </c>
       <c r="R61" t="n">
-        <v>6765337</v>
+        <v>6765086</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7118,7 +7111,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7128,7 +7121,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7690,10 +7683,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129565824</v>
+        <v>129565786</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>56926</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7701,39 +7694,46 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443207</v>
+        <v>443115</v>
       </c>
       <c r="R67" t="n">
-        <v>6765086</v>
+        <v>6765337</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -10701,10 +10701,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129566027</v>
+        <v>129565844</v>
       </c>
       <c r="B95" t="n">
-        <v>78747</v>
+        <v>78839</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10712,21 +10712,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443043</v>
+        <v>443017</v>
       </c>
       <c r="R95" t="n">
-        <v>6765047</v>
+        <v>6765118</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10808,10 +10808,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129565849</v>
+        <v>129566027</v>
       </c>
       <c r="B96" t="n">
-        <v>78838</v>
+        <v>78747</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10819,21 +10819,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443033</v>
+        <v>443043</v>
       </c>
       <c r="R96" t="n">
-        <v>6765241</v>
+        <v>6765047</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10915,10 +10915,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129565844</v>
+        <v>129565849</v>
       </c>
       <c r="B97" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10926,21 +10926,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10950,10 +10950,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443017</v>
+        <v>443033</v>
       </c>
       <c r="R97" t="n">
-        <v>6765118</v>
+        <v>6765241</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11564,10 +11564,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129565753</v>
+        <v>129565768</v>
       </c>
       <c r="B103" t="n">
-        <v>79700</v>
+        <v>79113</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11575,21 +11575,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11599,10 +11599,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443271</v>
+        <v>442990</v>
       </c>
       <c r="R103" t="n">
-        <v>6765126</v>
+        <v>6765105</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11671,10 +11671,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129565760</v>
+        <v>129565753</v>
       </c>
       <c r="B104" t="n">
-        <v>83052</v>
+        <v>79700</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11682,21 +11682,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11706,10 +11706,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>442682</v>
+        <v>443271</v>
       </c>
       <c r="R104" t="n">
-        <v>6764828</v>
+        <v>6765126</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11778,10 +11778,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129565749</v>
+        <v>129565760</v>
       </c>
       <c r="B105" t="n">
-        <v>79700</v>
+        <v>83052</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11789,21 +11789,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11813,10 +11813,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>442782</v>
+        <v>442682</v>
       </c>
       <c r="R105" t="n">
-        <v>6765271</v>
+        <v>6764828</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11858,12 +11858,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsyn</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11890,10 +11885,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129565768</v>
+        <v>129565749</v>
       </c>
       <c r="B106" t="n">
-        <v>79113</v>
+        <v>79700</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11901,21 +11896,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11925,10 +11920,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>442990</v>
+        <v>442782</v>
       </c>
       <c r="R106" t="n">
-        <v>6765105</v>
+        <v>6765271</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11960,7 +11955,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11970,7 +11965,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsyn</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11997,50 +11997,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129565821</v>
+        <v>129565876</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443034</v>
+        <v>442690</v>
       </c>
       <c r="R107" t="n">
-        <v>6765053</v>
+        <v>6764884</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12072,7 +12067,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12082,7 +12077,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12109,7 +12104,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129565876</v>
+        <v>129565891</v>
       </c>
       <c r="B108" t="n">
         <v>79081</v>
@@ -12144,10 +12139,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>442690</v>
+        <v>442829</v>
       </c>
       <c r="R108" t="n">
-        <v>6764884</v>
+        <v>6764901</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12179,7 +12174,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12189,7 +12184,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12216,7 +12211,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129565891</v>
+        <v>129565960</v>
       </c>
       <c r="B109" t="n">
         <v>79081</v>
@@ -12251,10 +12246,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>442829</v>
+        <v>443403</v>
       </c>
       <c r="R109" t="n">
-        <v>6764901</v>
+        <v>6765238</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12286,7 +12281,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12296,7 +12291,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12323,10 +12318,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129565960</v>
+        <v>129566023</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12334,21 +12329,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12358,10 +12353,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443403</v>
+        <v>443207</v>
       </c>
       <c r="R110" t="n">
-        <v>6765238</v>
+        <v>6765081</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12393,7 +12388,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12403,7 +12398,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12430,10 +12430,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129566023</v>
+        <v>129565751</v>
       </c>
       <c r="B111" t="n">
-        <v>78747</v>
+        <v>79700</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12441,21 +12441,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12465,10 +12465,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443207</v>
+        <v>442690</v>
       </c>
       <c r="R111" t="n">
-        <v>6765081</v>
+        <v>6764886</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12510,12 +12510,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12542,7 +12537,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129565751</v>
+        <v>129565750</v>
       </c>
       <c r="B112" t="n">
         <v>79700</v>
@@ -12577,10 +12572,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>442690</v>
+        <v>443145</v>
       </c>
       <c r="R112" t="n">
-        <v>6764886</v>
+        <v>6765323</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12612,7 +12607,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12622,7 +12617,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På enda silverlågan med hänsyn i hela anmälan</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12649,45 +12649,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129565750</v>
+        <v>129565821</v>
       </c>
       <c r="B113" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443145</v>
+        <v>443034</v>
       </c>
       <c r="R113" t="n">
-        <v>6765323</v>
+        <v>6765053</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12719,7 +12724,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12729,12 +12734,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>På enda silverlågan med hänsyn i hela anmälan</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -15346,10 +15346,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129565862</v>
+        <v>129565780</v>
       </c>
       <c r="B138" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15357,39 +15357,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>442822</v>
+        <v>443405</v>
       </c>
       <c r="R138" t="n">
-        <v>6764864</v>
+        <v>6765308</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15421,7 +15416,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15431,7 +15426,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15458,7 +15453,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129565962</v>
+        <v>129565862</v>
       </c>
       <c r="B139" t="n">
         <v>79081</v>
@@ -15487,16 +15482,21 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>443405</v>
+        <v>442822</v>
       </c>
       <c r="R139" t="n">
-        <v>6765256</v>
+        <v>6764864</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15565,7 +15565,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129565991</v>
+        <v>129565962</v>
       </c>
       <c r="B140" t="n">
         <v>79081</v>
@@ -15600,10 +15600,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>443155</v>
+        <v>443405</v>
       </c>
       <c r="R140" t="n">
-        <v>6765323</v>
+        <v>6765256</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15635,7 +15635,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15672,7 +15672,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129565901</v>
+        <v>129565991</v>
       </c>
       <c r="B141" t="n">
         <v>79081</v>
@@ -15707,10 +15707,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>443054</v>
+        <v>443155</v>
       </c>
       <c r="R141" t="n">
-        <v>6765138</v>
+        <v>6765323</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15779,7 +15779,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129565893</v>
+        <v>129565901</v>
       </c>
       <c r="B142" t="n">
         <v>79081</v>
@@ -15814,10 +15814,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>442835</v>
+        <v>443054</v>
       </c>
       <c r="R142" t="n">
-        <v>6764863</v>
+        <v>6765138</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15886,7 +15886,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129565990</v>
+        <v>129565893</v>
       </c>
       <c r="B143" t="n">
         <v>79081</v>
@@ -15921,10 +15921,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>443229</v>
+        <v>442835</v>
       </c>
       <c r="R143" t="n">
-        <v>6765319</v>
+        <v>6764863</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15956,7 +15956,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15993,7 +15993,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129566014</v>
+        <v>129565990</v>
       </c>
       <c r="B144" t="n">
         <v>79081</v>
@@ -16028,10 +16028,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>442813</v>
+        <v>443229</v>
       </c>
       <c r="R144" t="n">
-        <v>6764860</v>
+        <v>6765319</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16100,32 +16100,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129565769</v>
+        <v>129566014</v>
       </c>
       <c r="B145" t="n">
-        <v>91563</v>
+        <v>79081</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>443362</v>
+        <v>442813</v>
       </c>
       <c r="R145" t="n">
-        <v>6765377</v>
+        <v>6764860</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16207,32 +16207,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129565913</v>
+        <v>129565769</v>
       </c>
       <c r="B146" t="n">
-        <v>79081</v>
+        <v>91563</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16242,10 +16242,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>442773</v>
+        <v>443362</v>
       </c>
       <c r="R146" t="n">
-        <v>6765264</v>
+        <v>6765377</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16314,7 +16314,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129565871</v>
+        <v>129565913</v>
       </c>
       <c r="B147" t="n">
         <v>79081</v>
@@ -16349,10 +16349,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>442690</v>
+        <v>442773</v>
       </c>
       <c r="R147" t="n">
-        <v>6764850</v>
+        <v>6765264</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16384,7 +16384,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16421,7 +16421,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129565895</v>
+        <v>129565871</v>
       </c>
       <c r="B148" t="n">
         <v>79081</v>
@@ -16456,10 +16456,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>443005</v>
+        <v>442690</v>
       </c>
       <c r="R148" t="n">
-        <v>6765037</v>
+        <v>6764850</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16528,7 +16528,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129565977</v>
+        <v>129565895</v>
       </c>
       <c r="B149" t="n">
         <v>79081</v>
@@ -16563,10 +16563,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>443313</v>
+        <v>443005</v>
       </c>
       <c r="R149" t="n">
-        <v>6765439</v>
+        <v>6765037</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16635,10 +16635,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129566031</v>
+        <v>129565977</v>
       </c>
       <c r="B150" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16646,21 +16646,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16670,10 +16670,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>443296</v>
+        <v>443313</v>
       </c>
       <c r="R150" t="n">
-        <v>6765499</v>
+        <v>6765439</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16705,7 +16705,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16742,10 +16742,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129565764</v>
+        <v>129566031</v>
       </c>
       <c r="B151" t="n">
-        <v>79113</v>
+        <v>78747</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16753,21 +16753,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16777,10 +16777,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>443048</v>
+        <v>443296</v>
       </c>
       <c r="R151" t="n">
-        <v>6765235</v>
+        <v>6765499</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16822,7 +16822,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16849,10 +16849,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129566026</v>
+        <v>129565764</v>
       </c>
       <c r="B152" t="n">
-        <v>78747</v>
+        <v>79113</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16860,21 +16860,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16884,10 +16884,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>442684</v>
+        <v>443048</v>
       </c>
       <c r="R152" t="n">
-        <v>6764861</v>
+        <v>6765235</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16956,10 +16956,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129565752</v>
+        <v>129566026</v>
       </c>
       <c r="B153" t="n">
-        <v>79700</v>
+        <v>78747</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16967,21 +16967,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16991,10 +16991,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>443004</v>
+        <v>442684</v>
       </c>
       <c r="R153" t="n">
-        <v>6765163</v>
+        <v>6764861</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17063,10 +17063,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129565780</v>
+        <v>129565770</v>
       </c>
       <c r="B154" t="n">
-        <v>91599</v>
+        <v>79671</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17074,21 +17074,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17098,10 +17098,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>443405</v>
+        <v>443068</v>
       </c>
       <c r="R154" t="n">
-        <v>6765308</v>
+        <v>6765020</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17170,50 +17170,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129565842</v>
+        <v>129565752</v>
       </c>
       <c r="B155" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>443232</v>
+        <v>443004</v>
       </c>
       <c r="R155" t="n">
-        <v>6765136</v>
+        <v>6765163</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17245,7 +17240,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17255,7 +17250,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17282,7 +17277,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129565827</v>
+        <v>129565842</v>
       </c>
       <c r="B156" t="n">
         <v>8450</v>
@@ -17322,10 +17317,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>442998</v>
+        <v>443232</v>
       </c>
       <c r="R156" t="n">
-        <v>6765028</v>
+        <v>6765136</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17357,7 +17352,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17367,7 +17362,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17394,45 +17389,50 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129565770</v>
+        <v>129565827</v>
       </c>
       <c r="B157" t="n">
-        <v>79671</v>
+        <v>8450</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>443068</v>
+        <v>442998</v>
       </c>
       <c r="R157" t="n">
-        <v>6765020</v>
+        <v>6765028</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -21296,10 +21296,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129566024</v>
+        <v>129565963</v>
       </c>
       <c r="B193" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21307,21 +21307,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21331,10 +21331,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443088</v>
+        <v>443410</v>
       </c>
       <c r="R193" t="n">
-        <v>6765114</v>
+        <v>6765453</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21376,12 +21376,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsyn</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21408,7 +21403,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129565963</v>
+        <v>129566009</v>
       </c>
       <c r="B194" t="n">
         <v>79081</v>
@@ -21443,10 +21438,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>443410</v>
+        <v>442846</v>
       </c>
       <c r="R194" t="n">
-        <v>6765453</v>
+        <v>6764891</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21478,7 +21473,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21488,7 +21483,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21515,7 +21510,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129566009</v>
+        <v>129566001</v>
       </c>
       <c r="B195" t="n">
         <v>79081</v>
@@ -21550,10 +21545,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>442846</v>
+        <v>443140</v>
       </c>
       <c r="R195" t="n">
-        <v>6764891</v>
+        <v>6765218</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21585,7 +21580,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21595,7 +21590,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21622,7 +21617,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129566001</v>
+        <v>129565878</v>
       </c>
       <c r="B196" t="n">
         <v>79081</v>
@@ -21657,10 +21652,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443140</v>
+        <v>442745</v>
       </c>
       <c r="R196" t="n">
-        <v>6765218</v>
+        <v>6764895</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21692,7 +21687,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21702,7 +21697,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21729,10 +21724,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129565878</v>
+        <v>129566024</v>
       </c>
       <c r="B197" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21740,21 +21735,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21764,10 +21759,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>442745</v>
+        <v>443088</v>
       </c>
       <c r="R197" t="n">
-        <v>6764895</v>
+        <v>6765114</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21799,7 +21794,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21809,7 +21804,12 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsyn</t>
         </is>
       </c>
       <c r="AD197" t="b">

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -4458,45 +4458,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129565904</v>
+        <v>129565839</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443044</v>
+        <v>443000</v>
       </c>
       <c r="R37" t="n">
-        <v>6765238</v>
+        <v>6764985</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4538,7 +4543,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4565,50 +4570,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129565839</v>
+        <v>129566018</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443000</v>
+        <v>442699</v>
       </c>
       <c r="R38" t="n">
-        <v>6764985</v>
+        <v>6764782</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,10 +4677,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129566018</v>
+        <v>129566029</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>78750</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,21 +4688,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442699</v>
+        <v>442780</v>
       </c>
       <c r="R39" t="n">
-        <v>6764782</v>
+        <v>6765272</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,10 +4784,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129566029</v>
+        <v>129565904</v>
       </c>
       <c r="B40" t="n">
-        <v>78750</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442780</v>
+        <v>443044</v>
       </c>
       <c r="R40" t="n">
-        <v>6765272</v>
+        <v>6765238</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -8770,7 +8770,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129565883</v>
+        <v>129565941</v>
       </c>
       <c r="B77" t="n">
         <v>79084</v>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>442773</v>
+        <v>442718</v>
       </c>
       <c r="R77" t="n">
-        <v>6764941</v>
+        <v>6764837</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8877,7 +8877,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129565914</v>
+        <v>129565873</v>
       </c>
       <c r="B78" t="n">
         <v>79084</v>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>442770</v>
+        <v>442684</v>
       </c>
       <c r="R78" t="n">
-        <v>6765256</v>
+        <v>6764865</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8984,7 +8984,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129565941</v>
+        <v>129565987</v>
       </c>
       <c r="B79" t="n">
         <v>79084</v>
@@ -9019,10 +9019,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442718</v>
+        <v>443310</v>
       </c>
       <c r="R79" t="n">
-        <v>6764837</v>
+        <v>6765374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9091,7 +9091,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129565873</v>
+        <v>129565953</v>
       </c>
       <c r="B80" t="n">
         <v>79084</v>
@@ -9126,10 +9126,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>442684</v>
+        <v>443326</v>
       </c>
       <c r="R80" t="n">
-        <v>6764865</v>
+        <v>6765167</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9198,7 +9198,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129565987</v>
+        <v>129565988</v>
       </c>
       <c r="B81" t="n">
         <v>79084</v>
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443310</v>
+        <v>443284</v>
       </c>
       <c r="R81" t="n">
-        <v>6765374</v>
+        <v>6765343</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9305,7 +9305,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129565953</v>
+        <v>129565883</v>
       </c>
       <c r="B82" t="n">
         <v>79084</v>
@@ -9340,10 +9340,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443326</v>
+        <v>442773</v>
       </c>
       <c r="R82" t="n">
-        <v>6765167</v>
+        <v>6764941</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9412,7 +9412,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129565988</v>
+        <v>129565979</v>
       </c>
       <c r="B83" t="n">
         <v>79084</v>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443284</v>
+        <v>443306</v>
       </c>
       <c r="R83" t="n">
-        <v>6765343</v>
+        <v>6765458</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9626,50 +9626,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129565820</v>
+        <v>129565914</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443109</v>
+        <v>442770</v>
       </c>
       <c r="R85" t="n">
-        <v>6765024</v>
+        <v>6765256</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9701,7 +9696,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9711,7 +9706,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9738,45 +9733,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129565979</v>
+        <v>129565820</v>
       </c>
       <c r="B86" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443306</v>
+        <v>443109</v>
       </c>
       <c r="R86" t="n">
-        <v>6765458</v>
+        <v>6765024</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9845,10 +9845,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129566027</v>
+        <v>129565966</v>
       </c>
       <c r="B87" t="n">
-        <v>78750</v>
+        <v>79084</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443043</v>
+        <v>443432</v>
       </c>
       <c r="R87" t="n">
-        <v>6765047</v>
+        <v>6765347</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9952,10 +9952,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129565976</v>
+        <v>129566027</v>
       </c>
       <c r="B88" t="n">
-        <v>79084</v>
+        <v>78750</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9963,21 +9963,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443332</v>
+        <v>443043</v>
       </c>
       <c r="R88" t="n">
-        <v>6765403</v>
+        <v>6765047</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10059,45 +10059,52 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129565849</v>
+        <v>129565784</v>
       </c>
       <c r="B89" t="n">
-        <v>78841</v>
+        <v>56927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443033</v>
+        <v>443093</v>
       </c>
       <c r="R89" t="n">
-        <v>6765241</v>
+        <v>6765290</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10129,7 +10136,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10139,7 +10146,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10166,7 +10173,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129566005</v>
+        <v>129565976</v>
       </c>
       <c r="B90" t="n">
         <v>79084</v>
@@ -10201,10 +10208,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443160</v>
+        <v>443332</v>
       </c>
       <c r="R90" t="n">
-        <v>6765086</v>
+        <v>6765403</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10236,7 +10243,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10246,7 +10253,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10273,10 +10280,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129565956</v>
+        <v>129565849</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10284,21 +10291,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10308,10 +10315,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443366</v>
+        <v>443033</v>
       </c>
       <c r="R91" t="n">
-        <v>6765190</v>
+        <v>6765241</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10343,7 +10350,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10353,7 +10360,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10380,7 +10387,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129565932</v>
+        <v>129566005</v>
       </c>
       <c r="B92" t="n">
         <v>79084</v>
@@ -10415,10 +10422,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>442724</v>
+        <v>443160</v>
       </c>
       <c r="R92" t="n">
-        <v>6765212</v>
+        <v>6765086</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10450,7 +10457,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10460,7 +10467,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10487,7 +10494,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129565961</v>
+        <v>129565899</v>
       </c>
       <c r="B93" t="n">
         <v>79084</v>
@@ -10522,10 +10529,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443405</v>
+        <v>443088</v>
       </c>
       <c r="R93" t="n">
-        <v>6765244</v>
+        <v>6765090</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10557,7 +10564,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10567,7 +10574,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10594,10 +10601,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129565844</v>
+        <v>129565956</v>
       </c>
       <c r="B94" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10605,21 +10612,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10629,10 +10636,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443017</v>
+        <v>443366</v>
       </c>
       <c r="R94" t="n">
-        <v>6765118</v>
+        <v>6765190</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10664,7 +10671,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10674,7 +10681,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10701,7 +10708,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129565966</v>
+        <v>129565932</v>
       </c>
       <c r="B95" t="n">
         <v>79084</v>
@@ -10736,10 +10743,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443432</v>
+        <v>442724</v>
       </c>
       <c r="R95" t="n">
-        <v>6765347</v>
+        <v>6765212</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10771,7 +10778,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10781,7 +10788,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10808,52 +10815,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129565784</v>
+        <v>129565902</v>
       </c>
       <c r="B96" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443093</v>
+        <v>443010</v>
       </c>
       <c r="R96" t="n">
-        <v>6765290</v>
+        <v>6765160</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10922,7 +10922,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129565899</v>
+        <v>129565961</v>
       </c>
       <c r="B97" t="n">
         <v>79084</v>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443088</v>
+        <v>443405</v>
       </c>
       <c r="R97" t="n">
-        <v>6765090</v>
+        <v>6765244</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11029,10 +11029,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129565902</v>
+        <v>129565844</v>
       </c>
       <c r="B98" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11040,21 +11040,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11064,10 +11064,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443010</v>
+        <v>443017</v>
       </c>
       <c r="R98" t="n">
-        <v>6765160</v>
+        <v>6765118</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11136,10 +11136,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129565874</v>
+        <v>129565768</v>
       </c>
       <c r="B99" t="n">
-        <v>79084</v>
+        <v>79116</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11147,21 +11147,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>442679</v>
+        <v>442990</v>
       </c>
       <c r="R99" t="n">
-        <v>6764871</v>
+        <v>6765105</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11243,7 +11243,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129565868</v>
+        <v>129565874</v>
       </c>
       <c r="B100" t="n">
         <v>79084</v>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>442689</v>
+        <v>442679</v>
       </c>
       <c r="R100" t="n">
-        <v>6764832</v>
+        <v>6764871</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11350,10 +11350,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129565760</v>
+        <v>129565868</v>
       </c>
       <c r="B101" t="n">
-        <v>83055</v>
+        <v>79084</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11361,21 +11361,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11385,10 +11385,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>442682</v>
+        <v>442689</v>
       </c>
       <c r="R101" t="n">
-        <v>6764828</v>
+        <v>6764832</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11420,7 +11420,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11457,10 +11457,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129565870</v>
+        <v>129565760</v>
       </c>
       <c r="B102" t="n">
-        <v>79084</v>
+        <v>83055</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11468,21 +11468,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11492,10 +11492,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>442695</v>
+        <v>442682</v>
       </c>
       <c r="R102" t="n">
-        <v>6764852</v>
+        <v>6764828</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11564,10 +11564,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129565753</v>
+        <v>129565870</v>
       </c>
       <c r="B103" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11575,21 +11575,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11599,10 +11599,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443271</v>
+        <v>442695</v>
       </c>
       <c r="R103" t="n">
-        <v>6765126</v>
+        <v>6764852</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11671,10 +11671,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129565906</v>
+        <v>129565753</v>
       </c>
       <c r="B104" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11682,21 +11682,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11706,10 +11706,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>442852</v>
+        <v>443271</v>
       </c>
       <c r="R104" t="n">
-        <v>6765301</v>
+        <v>6765126</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11778,10 +11778,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129565749</v>
+        <v>129565906</v>
       </c>
       <c r="B105" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11789,21 +11789,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11813,10 +11813,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>442782</v>
+        <v>442852</v>
       </c>
       <c r="R105" t="n">
-        <v>6765271</v>
+        <v>6765301</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11858,12 +11858,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsyn</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11890,10 +11885,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129565768</v>
+        <v>129565749</v>
       </c>
       <c r="B106" t="n">
-        <v>79116</v>
+        <v>79703</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11901,21 +11896,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11925,10 +11920,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>442990</v>
+        <v>442782</v>
       </c>
       <c r="R106" t="n">
-        <v>6765105</v>
+        <v>6765271</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11960,7 +11955,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11970,7 +11965,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsyn</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11997,50 +11997,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129565821</v>
+        <v>129566023</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>78750</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443034</v>
+        <v>443207</v>
       </c>
       <c r="R107" t="n">
-        <v>6765053</v>
+        <v>6765081</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12072,7 +12067,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12082,7 +12077,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12649,45 +12649,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129566023</v>
+        <v>129565821</v>
       </c>
       <c r="B113" t="n">
-        <v>78750</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443207</v>
+        <v>443034</v>
       </c>
       <c r="R113" t="n">
-        <v>6765081</v>
+        <v>6765053</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12719,7 +12724,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12729,12 +12734,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12761,10 +12761,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129565992</v>
+        <v>129565775</v>
       </c>
       <c r="B114" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12772,21 +12772,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443143</v>
+        <v>443250</v>
       </c>
       <c r="R114" t="n">
-        <v>6765322</v>
+        <v>6765209</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12868,10 +12868,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129566008</v>
+        <v>129566030</v>
       </c>
       <c r="B115" t="n">
-        <v>79084</v>
+        <v>78750</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12879,21 +12879,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12903,10 +12903,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>442968</v>
+        <v>443283</v>
       </c>
       <c r="R115" t="n">
-        <v>6765088</v>
+        <v>6765488</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12975,10 +12975,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129565850</v>
+        <v>129565892</v>
       </c>
       <c r="B116" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12986,21 +12986,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13010,10 +13010,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443017</v>
+        <v>442831</v>
       </c>
       <c r="R116" t="n">
-        <v>6765114</v>
+        <v>6764873</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13082,10 +13082,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129565762</v>
+        <v>129565852</v>
       </c>
       <c r="B117" t="n">
-        <v>83055</v>
+        <v>78841</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13093,21 +13093,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13117,10 +13117,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>442861</v>
+        <v>443321</v>
       </c>
       <c r="R117" t="n">
-        <v>6764908</v>
+        <v>6765425</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13189,7 +13189,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129565755</v>
+        <v>129565756</v>
       </c>
       <c r="B118" t="n">
         <v>79703</v>
@@ -13224,10 +13224,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443282</v>
+        <v>443179</v>
       </c>
       <c r="R118" t="n">
-        <v>6765487</v>
+        <v>6765294</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13296,7 +13296,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129565949</v>
+        <v>129565926</v>
       </c>
       <c r="B119" t="n">
         <v>79084</v>
@@ -13331,10 +13331,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443110</v>
+        <v>442748</v>
       </c>
       <c r="R119" t="n">
-        <v>6765023</v>
+        <v>6765234</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13366,7 +13366,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13403,10 +13403,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129565800</v>
+        <v>129565992</v>
       </c>
       <c r="B120" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13414,39 +13414,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443020</v>
+        <v>443143</v>
       </c>
       <c r="R120" t="n">
-        <v>6764999</v>
+        <v>6765322</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13478,7 +13473,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13488,7 +13483,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13515,10 +13510,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129565775</v>
+        <v>129566008</v>
       </c>
       <c r="B121" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13526,21 +13521,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13550,10 +13545,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443250</v>
+        <v>442968</v>
       </c>
       <c r="R121" t="n">
-        <v>6765209</v>
+        <v>6765088</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13585,7 +13580,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13595,7 +13590,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13622,10 +13617,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129566030</v>
+        <v>129565850</v>
       </c>
       <c r="B122" t="n">
-        <v>78750</v>
+        <v>78841</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13633,21 +13628,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13657,10 +13652,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443283</v>
+        <v>443017</v>
       </c>
       <c r="R122" t="n">
-        <v>6765488</v>
+        <v>6765114</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13692,7 +13687,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13702,7 +13697,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13729,10 +13724,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129565892</v>
+        <v>129565762</v>
       </c>
       <c r="B123" t="n">
-        <v>79084</v>
+        <v>83055</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13740,21 +13735,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13764,10 +13759,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>442831</v>
+        <v>442861</v>
       </c>
       <c r="R123" t="n">
-        <v>6764873</v>
+        <v>6764908</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13799,7 +13794,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13809,7 +13804,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13836,10 +13831,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129565852</v>
+        <v>129565755</v>
       </c>
       <c r="B124" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13847,21 +13842,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13871,10 +13866,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443321</v>
+        <v>443282</v>
       </c>
       <c r="R124" t="n">
-        <v>6765425</v>
+        <v>6765487</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13906,7 +13901,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13916,7 +13911,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13943,10 +13938,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129565756</v>
+        <v>129565949</v>
       </c>
       <c r="B125" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13954,21 +13949,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13978,10 +13973,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443179</v>
+        <v>443110</v>
       </c>
       <c r="R125" t="n">
-        <v>6765294</v>
+        <v>6765023</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14013,7 +14008,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14023,7 +14018,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14050,10 +14045,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129565926</v>
+        <v>129565800</v>
       </c>
       <c r="B126" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14061,34 +14056,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>442748</v>
+        <v>443020</v>
       </c>
       <c r="R126" t="n">
-        <v>6765234</v>
+        <v>6764999</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -17501,50 +17501,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129565823</v>
+        <v>129565809</v>
       </c>
       <c r="B158" t="n">
-        <v>8450</v>
+        <v>79151</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>106545</v>
+        <v>637</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>443008</v>
+        <v>442863</v>
       </c>
       <c r="R158" t="n">
-        <v>6765154</v>
+        <v>6764893</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17576,7 +17571,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17586,7 +17581,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>20-tal bålar inom 10 m på fem olika granar.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17725,7 +17725,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129565967</v>
+        <v>129565989</v>
       </c>
       <c r="B160" t="n">
         <v>79084</v>
@@ -17760,10 +17760,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>443420</v>
+        <v>443256</v>
       </c>
       <c r="R160" t="n">
-        <v>6765366</v>
+        <v>6765342</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17795,7 +17795,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17832,7 +17832,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129565986</v>
+        <v>129565967</v>
       </c>
       <c r="B161" t="n">
         <v>79084</v>
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>443319</v>
+        <v>443420</v>
       </c>
       <c r="R161" t="n">
-        <v>6765391</v>
+        <v>6765366</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17902,7 +17902,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17939,7 +17939,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129565980</v>
+        <v>129565952</v>
       </c>
       <c r="B162" t="n">
         <v>79084</v>
@@ -17974,10 +17974,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>443299</v>
+        <v>443251</v>
       </c>
       <c r="R162" t="n">
-        <v>6765469</v>
+        <v>6765117</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18009,7 +18009,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18046,32 +18046,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129565809</v>
+        <v>129565933</v>
       </c>
       <c r="B163" t="n">
-        <v>79151</v>
+        <v>79084</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18081,10 +18081,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>442863</v>
+        <v>442711</v>
       </c>
       <c r="R163" t="n">
-        <v>6764893</v>
+        <v>6765211</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18126,12 +18126,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>20-tal bålar inom 10 m på fem olika granar.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18158,7 +18153,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129565989</v>
+        <v>129565928</v>
       </c>
       <c r="B164" t="n">
         <v>79084</v>
@@ -18193,10 +18188,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>443256</v>
+        <v>442782</v>
       </c>
       <c r="R164" t="n">
-        <v>6765342</v>
+        <v>6765222</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18228,7 +18223,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18238,7 +18233,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18265,7 +18260,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129565952</v>
+        <v>129565975</v>
       </c>
       <c r="B165" t="n">
         <v>79084</v>
@@ -18300,10 +18295,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>443251</v>
+        <v>443337</v>
       </c>
       <c r="R165" t="n">
-        <v>6765117</v>
+        <v>6765385</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18335,7 +18330,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18345,7 +18340,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18372,45 +18367,50 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129565933</v>
+        <v>129565823</v>
       </c>
       <c r="B166" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>442711</v>
+        <v>443008</v>
       </c>
       <c r="R166" t="n">
-        <v>6765211</v>
+        <v>6765154</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18452,7 +18452,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18479,7 +18479,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129565928</v>
+        <v>129565980</v>
       </c>
       <c r="B167" t="n">
         <v>79084</v>
@@ -18514,10 +18514,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>442782</v>
+        <v>443299</v>
       </c>
       <c r="R167" t="n">
-        <v>6765222</v>
+        <v>6765469</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18549,7 +18549,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18559,7 +18559,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18586,7 +18586,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129565975</v>
+        <v>129565986</v>
       </c>
       <c r="B168" t="n">
         <v>79084</v>
@@ -18621,10 +18621,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>443337</v>
+        <v>443319</v>
       </c>
       <c r="R168" t="n">
-        <v>6765385</v>
+        <v>6765391</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18656,7 +18656,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18693,7 +18693,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129565929</v>
+        <v>129565968</v>
       </c>
       <c r="B169" t="n">
         <v>79084</v>
@@ -18728,10 +18728,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>442823</v>
+        <v>443400</v>
       </c>
       <c r="R169" t="n">
-        <v>6765181</v>
+        <v>6765375</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18773,7 +18773,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18800,7 +18800,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129565910</v>
+        <v>129566012</v>
       </c>
       <c r="B170" t="n">
         <v>79084</v>
@@ -18835,10 +18835,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>442825</v>
+        <v>442827</v>
       </c>
       <c r="R170" t="n">
-        <v>6765266</v>
+        <v>6764880</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18870,7 +18870,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18907,45 +18907,50 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129565968</v>
+        <v>129565829</v>
       </c>
       <c r="B171" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>443400</v>
+        <v>443008</v>
       </c>
       <c r="R171" t="n">
-        <v>6765375</v>
+        <v>6765122</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18977,7 +18982,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18987,7 +18992,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19014,45 +19019,50 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129566012</v>
+        <v>129565828</v>
       </c>
       <c r="B172" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>442827</v>
+        <v>443021</v>
       </c>
       <c r="R172" t="n">
-        <v>6764880</v>
+        <v>6765053</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19084,7 +19094,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19094,7 +19104,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19121,7 +19131,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129565829</v>
+        <v>129565830</v>
       </c>
       <c r="B173" t="n">
         <v>8450</v>
@@ -19161,10 +19171,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>443008</v>
+        <v>443009</v>
       </c>
       <c r="R173" t="n">
-        <v>6765122</v>
+        <v>6765160</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19196,7 +19206,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19206,7 +19216,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19233,7 +19243,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129565828</v>
+        <v>129565822</v>
       </c>
       <c r="B174" t="n">
         <v>8450</v>
@@ -19264,7 +19274,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -19273,10 +19283,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>443021</v>
+        <v>443092</v>
       </c>
       <c r="R174" t="n">
-        <v>6765053</v>
+        <v>6765061</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19308,7 +19318,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19318,7 +19328,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19345,50 +19355,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129565830</v>
+        <v>129565929</v>
       </c>
       <c r="B175" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>443009</v>
+        <v>442823</v>
       </c>
       <c r="R175" t="n">
-        <v>6765160</v>
+        <v>6765181</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19420,7 +19425,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19430,7 +19435,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19457,50 +19462,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129565822</v>
+        <v>129565910</v>
       </c>
       <c r="B176" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>443092</v>
+        <v>442825</v>
       </c>
       <c r="R176" t="n">
-        <v>6765061</v>
+        <v>6765266</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19569,10 +19569,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129565787</v>
+        <v>129565973</v>
       </c>
       <c r="B177" t="n">
-        <v>57895</v>
+        <v>79084</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19580,39 +19580,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>443283</v>
+        <v>443383</v>
       </c>
       <c r="R177" t="n">
-        <v>6765488</v>
+        <v>6765415</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19644,7 +19639,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19654,7 +19649,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19681,7 +19676,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129565973</v>
+        <v>129566002</v>
       </c>
       <c r="B178" t="n">
         <v>79084</v>
@@ -19716,10 +19711,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>443383</v>
+        <v>443134</v>
       </c>
       <c r="R178" t="n">
-        <v>6765415</v>
+        <v>6765184</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19751,7 +19746,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19761,7 +19756,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19788,7 +19783,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129566002</v>
+        <v>129565879</v>
       </c>
       <c r="B179" t="n">
         <v>79084</v>
@@ -19823,10 +19818,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>443134</v>
+        <v>442749</v>
       </c>
       <c r="R179" t="n">
-        <v>6765184</v>
+        <v>6764886</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19858,7 +19853,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19868,7 +19863,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19895,7 +19890,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129565879</v>
+        <v>129565972</v>
       </c>
       <c r="B180" t="n">
         <v>79084</v>
@@ -19930,10 +19925,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>442749</v>
+        <v>443398</v>
       </c>
       <c r="R180" t="n">
-        <v>6764886</v>
+        <v>6765434</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19965,7 +19960,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19975,7 +19970,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20002,7 +19997,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129565972</v>
+        <v>129565927</v>
       </c>
       <c r="B181" t="n">
         <v>79084</v>
@@ -20037,10 +20032,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>443398</v>
+        <v>442770</v>
       </c>
       <c r="R181" t="n">
-        <v>6765434</v>
+        <v>6765225</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20072,7 +20067,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20082,7 +20077,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20109,7 +20104,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129565927</v>
+        <v>129565984</v>
       </c>
       <c r="B182" t="n">
         <v>79084</v>
@@ -20144,10 +20139,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>442770</v>
+        <v>443338</v>
       </c>
       <c r="R182" t="n">
-        <v>6765225</v>
+        <v>6765441</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20179,7 +20174,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20189,7 +20184,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20216,7 +20211,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129565984</v>
+        <v>129565912</v>
       </c>
       <c r="B183" t="n">
         <v>79084</v>
@@ -20251,10 +20246,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>443338</v>
+        <v>442776</v>
       </c>
       <c r="R183" t="n">
-        <v>6765441</v>
+        <v>6765280</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20286,7 +20281,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20296,7 +20291,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20323,7 +20318,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129565912</v>
+        <v>129565971</v>
       </c>
       <c r="B184" t="n">
         <v>79084</v>
@@ -20358,10 +20353,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>442776</v>
+        <v>443406</v>
       </c>
       <c r="R184" t="n">
-        <v>6765280</v>
+        <v>6765450</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20393,7 +20388,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20403,7 +20398,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20430,10 +20425,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129565971</v>
+        <v>129565806</v>
       </c>
       <c r="B185" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20441,34 +20436,39 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>443406</v>
+        <v>443430</v>
       </c>
       <c r="R185" t="n">
-        <v>6765450</v>
+        <v>6765200</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20537,10 +20537,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129565806</v>
+        <v>129565787</v>
       </c>
       <c r="B186" t="n">
-        <v>57734</v>
+        <v>57895</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20548,27 +20548,27 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -20577,10 +20577,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>443430</v>
+        <v>443283</v>
       </c>
       <c r="R186" t="n">
-        <v>6765200</v>
+        <v>6765488</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20612,7 +20612,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20975,45 +20975,50 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129566024</v>
+        <v>129565826</v>
       </c>
       <c r="B190" t="n">
-        <v>78750</v>
+        <v>8450</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>443088</v>
+        <v>443073</v>
       </c>
       <c r="R190" t="n">
-        <v>6765114</v>
+        <v>6765287</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21045,7 +21050,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21055,12 +21060,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>09:16</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsyn</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21087,10 +21087,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129565963</v>
+        <v>129566024</v>
       </c>
       <c r="B191" t="n">
-        <v>79084</v>
+        <v>78750</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21098,21 +21098,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21122,10 +21122,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>443410</v>
+        <v>443088</v>
       </c>
       <c r="R191" t="n">
-        <v>6765453</v>
+        <v>6765114</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21167,7 +21167,12 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsyn</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21194,7 +21199,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129565878</v>
+        <v>129565963</v>
       </c>
       <c r="B192" t="n">
         <v>79084</v>
@@ -21229,10 +21234,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>442745</v>
+        <v>443410</v>
       </c>
       <c r="R192" t="n">
-        <v>6764895</v>
+        <v>6765453</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21264,7 +21269,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21274,7 +21279,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21301,7 +21306,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129566001</v>
+        <v>129565878</v>
       </c>
       <c r="B193" t="n">
         <v>79084</v>
@@ -21336,10 +21341,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>443140</v>
+        <v>442745</v>
       </c>
       <c r="R193" t="n">
-        <v>6765218</v>
+        <v>6764895</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21371,7 +21376,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21381,7 +21386,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21408,7 +21413,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129566009</v>
+        <v>129566001</v>
       </c>
       <c r="B194" t="n">
         <v>79084</v>
@@ -21443,10 +21448,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>442846</v>
+        <v>443140</v>
       </c>
       <c r="R194" t="n">
-        <v>6764891</v>
+        <v>6765218</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21478,7 +21483,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21488,7 +21493,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21515,10 +21520,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129565771</v>
+        <v>129566009</v>
       </c>
       <c r="B195" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21526,21 +21531,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21550,10 +21555,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>443081</v>
+        <v>442846</v>
       </c>
       <c r="R195" t="n">
-        <v>6765117</v>
+        <v>6764891</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21585,7 +21590,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21595,7 +21600,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21622,10 +21627,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129565846</v>
+        <v>129565771</v>
       </c>
       <c r="B196" t="n">
-        <v>92021</v>
+        <v>79674</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21633,21 +21638,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6040186</v>
+        <v>229821</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21657,10 +21662,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>443405</v>
+        <v>443081</v>
       </c>
       <c r="R196" t="n">
-        <v>6765306</v>
+        <v>6765117</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21692,7 +21697,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21702,7 +21707,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21729,50 +21734,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129565826</v>
+        <v>129565846</v>
       </c>
       <c r="B197" t="n">
-        <v>8450</v>
+        <v>92021</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106545</v>
+        <v>6040186</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>443073</v>
+        <v>443405</v>
       </c>
       <c r="R197" t="n">
-        <v>6765287</v>
+        <v>6765306</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21804,7 +21804,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24098,7 +24098,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129565877</v>
+        <v>129565897</v>
       </c>
       <c r="B219" t="n">
         <v>79084</v>
@@ -24133,10 +24133,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>442708</v>
+        <v>443095</v>
       </c>
       <c r="R219" t="n">
-        <v>6764885</v>
+        <v>6765053</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24168,7 +24168,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24178,7 +24178,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24205,10 +24205,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129566028</v>
+        <v>129565877</v>
       </c>
       <c r="B220" t="n">
-        <v>78750</v>
+        <v>79084</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24216,21 +24216,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24240,10 +24240,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>442837</v>
+        <v>442708</v>
       </c>
       <c r="R220" t="n">
-        <v>6765272</v>
+        <v>6764885</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24275,7 +24275,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24312,10 +24312,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129565765</v>
+        <v>129566028</v>
       </c>
       <c r="B221" t="n">
-        <v>79116</v>
+        <v>78750</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24323,21 +24323,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24347,10 +24347,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>443303</v>
+        <v>442837</v>
       </c>
       <c r="R221" t="n">
-        <v>6765447</v>
+        <v>6765272</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24392,7 +24392,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24419,50 +24419,45 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129565748</v>
+        <v>129565765</v>
       </c>
       <c r="B222" t="n">
-        <v>5197</v>
+        <v>79116</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>443420</v>
+        <v>443303</v>
       </c>
       <c r="R222" t="n">
-        <v>6765200</v>
+        <v>6765447</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24494,7 +24489,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24504,7 +24499,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24531,50 +24526,45 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129565841</v>
+        <v>129565864</v>
       </c>
       <c r="B223" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>443266</v>
+        <v>442678</v>
       </c>
       <c r="R223" t="n">
-        <v>6765164</v>
+        <v>6764817</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24606,7 +24596,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24616,7 +24606,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24643,50 +24633,45 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129565831</v>
+        <v>129565958</v>
       </c>
       <c r="B224" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>443008</v>
+        <v>443398</v>
       </c>
       <c r="R224" t="n">
-        <v>6765171</v>
+        <v>6765189</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24718,7 +24703,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24728,7 +24713,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24755,50 +24740,45 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129565843</v>
+        <v>129565869</v>
       </c>
       <c r="B225" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>443077</v>
+        <v>442712</v>
       </c>
       <c r="R225" t="n">
-        <v>6765075</v>
+        <v>6764831</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24830,7 +24810,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24840,7 +24820,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24867,45 +24847,50 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129565864</v>
+        <v>129565748</v>
       </c>
       <c r="B226" t="n">
-        <v>79084</v>
+        <v>5197</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>442678</v>
+        <v>443420</v>
       </c>
       <c r="R226" t="n">
-        <v>6764817</v>
+        <v>6765200</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24937,7 +24922,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24947,7 +24932,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24974,45 +24959,50 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129565958</v>
+        <v>129565841</v>
       </c>
       <c r="B227" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>443398</v>
+        <v>443266</v>
       </c>
       <c r="R227" t="n">
-        <v>6765189</v>
+        <v>6765164</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25044,7 +25034,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25054,7 +25044,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25081,45 +25071,50 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129565897</v>
+        <v>129565831</v>
       </c>
       <c r="B228" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>443095</v>
+        <v>443008</v>
       </c>
       <c r="R228" t="n">
-        <v>6765053</v>
+        <v>6765171</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25151,7 +25146,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25161,7 +25156,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25188,45 +25183,50 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129565869</v>
+        <v>129565843</v>
       </c>
       <c r="B229" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Åsberget, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>442712</v>
+        <v>443077</v>
       </c>
       <c r="R229" t="n">
-        <v>6764831</v>
+        <v>6765075</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25258,7 +25258,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25268,7 +25268,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD229" t="b">

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126809464</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>126809240</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>126810889</v>
       </c>
       <c r="B4" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>126810668</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>126806087</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126809392</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>126856706</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>126856695</v>
       </c>
       <c r="B9" t="n">
-        <v>78776</v>
+        <v>78769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>126856530</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>126856688</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>91339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>126856670</v>
       </c>
       <c r="B12" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>126856681</v>
       </c>
       <c r="B13" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 50244-2025 artfynd.xlsx
+++ b/artfynd/A 50244-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126809464</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>126809240</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>126810889</v>
       </c>
       <c r="B4" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>126810668</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>126806087</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126809392</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>126856706</v>
       </c>
       <c r="B8" t="n">
-        <v>78770</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>126856695</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>78776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>126856530</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>126856688</v>
       </c>
       <c r="B11" t="n">
-        <v>91339</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>126856670</v>
       </c>
       <c r="B12" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>126856681</v>
       </c>
       <c r="B13" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
